--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -55,7 +55,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +88,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00dcfce7"/>
+        <bgColor rgb="00dcfce7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00fee2e2"/>
         <bgColor rgb="00fee2e2"/>
       </patternFill>
@@ -111,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -123,10 +129,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -557,123 +564,123 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5797.91</v>
+        <v>5853.95</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>-2.09</v>
+        <v>53.95</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.92</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5798.46</v>
+        <v>5881.93</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5788.26</v>
+        <v>5827.34</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>620M</t>
+          <t>653M</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5792.53</v>
+        <v>5832.13</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>22.33</v>
+        <v>11.55</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5800.12</v>
+        <v>5856.2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5790.71</v>
+        <v>5808.37</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>664M</t>
+          <t>765M</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5799.88</v>
+        <v>5821.56</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-37.56</v>
+        <v>26.72</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.65</v>
+        <v>0.46</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5810.3</v>
+        <v>5832.08</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5794.47</v>
+        <v>5794.03</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>644M</t>
+          <t>570M</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5861.52</v>
+        <v>5865.62</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>56.82</v>
+        <v>49.3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5890</v>
+        <v>5895.52</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5834.76</v>
+        <v>5857.77</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>791M</t>
+          <t>722M</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -685,27 +692,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5786.17</v>
+        <v>5830.65</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-23.82</v>
+        <v>-41.44</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.71</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5802.99</v>
+        <v>5844.51</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5759.32</v>
+        <v>5813</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>710M</t>
+          <t>718M</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -717,27 +724,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5933.48</v>
+        <v>5843.69</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>49.57</v>
+        <v>31.45</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5933.74</v>
+        <v>5860.6</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5927.99</v>
+        <v>5817.83</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>579M</t>
+          <t>658M</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -749,91 +756,91 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>5768.5</v>
+        <v>5884.57</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-46.8</v>
+        <v>44.28</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5769.24</v>
+        <v>5909.94</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5757.38</v>
+        <v>5866.47</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>525M</t>
+          <t>688M</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5701.83</v>
+        <v>5847.09</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-22.65</v>
+        <v>42.25</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-0.4</v>
+        <v>0.72</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5729.75</v>
+        <v>5856.51</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5698.77</v>
+        <v>5837</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>799M</t>
+          <t>751M</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5849.62</v>
+        <v>5803.35</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>15.57</v>
+        <v>16.46</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5865.67</v>
+        <v>5815.82</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5841.11</v>
+        <v>5802.01</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>687M</t>
+          <t>618M</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -845,91 +852,91 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5788.48</v>
+        <v>5784.97</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>20.22</v>
+        <v>-15.72</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.35</v>
+        <v>-0.27</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5799.81</v>
+        <v>5809.09</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5788.02</v>
+        <v>5776.92</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>564M</t>
+          <t>661M</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5797.95</v>
+        <v>5828.02</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-11.98</v>
+        <v>51.12</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.21</v>
+        <v>0.88</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5820.24</v>
+        <v>5828.29</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5780.14</v>
+        <v>5807.05</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>570M</t>
+          <t>629M</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5872.22</v>
+        <v>5852.11</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>31.21</v>
+        <v>44.17</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5896.23</v>
+        <v>5867.72</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5855.69</v>
+        <v>5826.91</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>556M</t>
+          <t>580M</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -941,123 +948,123 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5884.5</v>
+        <v>5843.36</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-37.74</v>
+        <v>-2.94</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.05</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5906.95</v>
+        <v>5868.9</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>5868.31</v>
+        <v>5824.95</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>598M</t>
+          <t>766M</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5808.28</v>
+        <v>5819.47</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-44.11</v>
+        <v>43.12</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>-0.76</v>
+        <v>0.74</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5834.93</v>
+        <v>5844.74</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5805.15</v>
+        <v>5793.3</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>771M</t>
+          <t>695M</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5825.63</v>
+        <v>5804.97</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-38.61</v>
+        <v>40.95</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.66</v>
+        <v>0.71</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5845.23</v>
+        <v>5812.14</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5807.44</v>
+        <v>5785.5</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>756M</t>
+          <t>699M</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5767.74</v>
+        <v>5738.32</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>19.21</v>
+        <v>-11.07</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.33</v>
+        <v>-0.19</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5774.83</v>
+        <v>5748.15</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5761.36</v>
+        <v>5725.08</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>798M</t>
+          <t>685M</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1069,27 +1076,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5801.3</v>
+        <v>5805.16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-43.41</v>
+        <v>-32.16</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.55</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>5827.59</v>
+        <v>5815.26</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5790.5</v>
+        <v>5784.27</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>661M</t>
+          <t>660M</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1101,91 +1108,91 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5829.3</v>
+        <v>5841.96</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>-7.34</v>
+        <v>33.75</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>-0.13</v>
+        <v>0.58</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5845.82</v>
+        <v>5854.48</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5802.13</v>
+        <v>5838.08</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>703M</t>
+          <t>799M</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5870.53</v>
+        <v>6089.53</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>13.86</v>
+        <v>46.85</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.24</v>
+        <v>0.77</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5889.29</v>
+        <v>6096.59</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5851.99</v>
+        <v>6081.29</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>653M</t>
+          <t>601M</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5832.32</v>
+        <v>5796.46</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>55.05</v>
+        <v>27.95</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5845.73</v>
+        <v>5801.46</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5807.31</v>
+        <v>5773.53</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>647M</t>
+          <t>681M</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1197,27 +1204,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5751.35</v>
+        <v>5786.44</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-38.29</v>
+        <v>-36.94</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.64</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>5764.26</v>
+        <v>5807.92</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5742.26</v>
+        <v>5775.65</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>589M</t>
+          <t>563M</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1229,59 +1236,59 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5731.55</v>
+        <v>5725.25</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-3.31</v>
+        <v>-25.65</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.45</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5756.26</v>
+        <v>5728.71</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5729.5</v>
+        <v>5700.24</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>563M</t>
+          <t>530M</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5951.86</v>
+        <v>5904.82</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>22.04</v>
+        <v>27.47</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5963.1</v>
+        <v>5924.2</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>5927.84</v>
+        <v>5893.31</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>535M</t>
+          <t>606M</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1293,27 +1300,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5734.9</v>
+        <v>5825.24</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>31.3</v>
+        <v>45.86</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5752.9</v>
+        <v>5832.43</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5720.52</v>
+        <v>5813.66</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>722M</t>
+          <t>591M</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -1325,155 +1332,155 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>5907.73</v>
+        <v>5936.75</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-15.69</v>
+        <v>57.04</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-0.27</v>
+        <v>0.96</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5909.94</v>
+        <v>5945.81</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5898.84</v>
+        <v>5908.81</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>584M</t>
+          <t>657M</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6026.78</v>
+        <v>5847.7</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>17.08</v>
+        <v>-47.15</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.28</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6048.87</v>
+        <v>5866.46</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6007.52</v>
+        <v>5837.95</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>683M</t>
+          <t>580M</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>5750.5</v>
+        <v>6199.7</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-15.73</v>
+        <v>25.86</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-0.27</v>
+        <v>0.42</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>5765.07</v>
+        <v>6201.41</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5726.83</v>
+        <v>6182.14</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>771M</t>
+          <t>656M</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5888.62</v>
+        <v>5947.57</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-9.369999999999999</v>
+        <v>39.71</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.16</v>
+        <v>0.67</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5896.33</v>
+        <v>5969.15</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5878.64</v>
+        <v>5944.09</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>595M</t>
+          <t>617M</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5909.08</v>
+        <v>5879.33</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5938.22</v>
+        <v>5905.73</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5880.23</v>
+        <v>5868.92</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>543M</t>
+          <t>594M</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -1485,27 +1492,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5804.61</v>
+        <v>5895.94</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-42.1</v>
+        <v>-24.57</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.42</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5809.66</v>
+        <v>5906.78</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5795.59</v>
+        <v>5884.55</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>719M</t>
+          <t>620M</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1517,27 +1524,27 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5909.79</v>
+        <v>5802.61</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>57.78</v>
+        <v>40.37</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5912.76</v>
+        <v>5803.45</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>5906.91</v>
+        <v>5788.06</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>583M</t>
+          <t>676M</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -2071,16 +2078,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9800</v>
+        <v>9900</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3.46</v>
+        <v>-1.03</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>45.7</v>
+        <v>46.1</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -2098,16 +2105,16 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>14.3</v>
+        <v>14.7</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>855.72</v>
+        <v>842.35</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -2132,16 +2139,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4400</v>
+        <v>5450</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-1.55</v>
+        <v>1.21</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>49.9</v>
+        <v>53.1</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -2159,16 +2166,16 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>11</v>
+        <v>13.1</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>13.8</v>
+        <v>16.4</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>398.42</v>
+        <v>414.64</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -2193,16 +2200,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2850</v>
+        <v>3250</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-1.8</v>
+        <v>-1.3</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -2220,16 +2227,16 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>12.8</v>
+        <v>13.4</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>15.5</v>
+        <v>16.2</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>223.47</v>
+        <v>243.35</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -2254,16 +2261,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>6150</v>
+        <v>5550</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.48</v>
+        <v>3.35</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>33</v>
+        <v>54.7</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -2281,16 +2288,16 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>615.04</v>
+        <v>539.88</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
@@ -2315,16 +2322,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3100</v>
+        <v>3600</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1.59</v>
+        <v>-2.04</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>54.5</v>
+        <v>38.2</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -2342,16 +2349,16 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>25.6</v>
+        <v>22.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>18.4</v>
+        <v>16.4</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>121.22</v>
+        <v>157.94</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -2376,25 +2383,25 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2100</v>
+        <v>2350</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-1.97</v>
+        <v>3.46</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>49.8</v>
+        <v>25.8</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -2409,10 +2416,10 @@
         <v>3.2</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>107.97</v>
+        <v>120.99</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -2437,16 +2444,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>24050</v>
+        <v>26600</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2.23</v>
+        <v>1.79</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0.01</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>47.8</v>
+        <v>43.9</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -2464,16 +2471,16 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10.2</v>
+        <v>11.8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>14.9</v>
+        <v>17.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>2349.95</v>
+        <v>2261.94</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -2498,16 +2505,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21350</v>
+        <v>21550</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-2.28</v>
+        <v>0.03</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>55.6</v>
+        <v>63</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -2525,16 +2532,16 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>19.3</v>
+        <v>17</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>23.5</v>
+        <v>20.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>1108.39</v>
+        <v>1265.96</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -2559,16 +2566,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10900</v>
+        <v>11550</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3.49</v>
+        <v>-2.61</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>47.5</v>
+        <v>53.2</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -2586,16 +2593,16 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>509.97</v>
+        <v>531.05</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2620,16 +2627,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5900</v>
+        <v>5950</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>45.7</v>
+        <v>57</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -2647,16 +2654,16 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>306.68</v>
+        <v>299.91</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2684,13 +2691,13 @@
         <v>1950</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-1.74</v>
+        <v>-0.91</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>51.1</v>
+        <v>43.7</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -2708,16 +2715,16 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>26.8</v>
+        <v>30.6</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>19.1</v>
+        <v>21.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>72.76000000000001</v>
+        <v>63.76</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2742,16 +2749,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3100</v>
+        <v>3250</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-2.36</v>
+        <v>1.03</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>50.8</v>
+        <v>47.9</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -2769,16 +2776,16 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>25.7</v>
+        <v>29.1</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.3</v>
+        <v>20.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>120.73</v>
+        <v>111.87</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -2803,16 +2810,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>58650</v>
+        <v>62150</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1.01</v>
+        <v>-1.6</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>61.7</v>
+        <v>40.5</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -2830,16 +2837,16 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>7247.51</v>
+        <v>7476.47</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2864,16 +2871,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.98</v>
+        <v>1.41</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>56.4</v>
+        <v>56.2</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -2891,16 +2898,16 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>175.02</v>
+        <v>162.58</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2925,16 +2932,16 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7850</v>
+        <v>7550</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.25</v>
+        <v>-0.63</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>36.1</v>
+        <v>55.5</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -2946,22 +2953,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>15.2</v>
+        <v>14.3</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>15.2</v>
+        <v>14.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>515.02</v>
+        <v>528.01</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
@@ -2986,16 +2993,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6000</v>
+        <v>6250</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-2.33</v>
+        <v>-2.52</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0.04</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>38.1</v>
+        <v>53.3</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -3013,16 +3020,16 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>372.06</v>
+        <v>393.32</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -3047,16 +3054,16 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9250</v>
+        <v>8050</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>3.23</v>
+        <v>2.22</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>40.1</v>
+        <v>51</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -3074,16 +3081,16 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>611.27</v>
+        <v>523.8200000000001</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -3108,16 +3115,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>5450</v>
+        <v>4250</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2.8</v>
+        <v>-2.69</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>50.3</v>
+        <v>48.8</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -3135,16 +3142,16 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>339.81</v>
+        <v>270.82</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
@@ -3172,13 +3179,13 @@
         <v>1150</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.42</v>
+        <v>2.81</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>58.8</v>
+        <v>49.7</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -3196,16 +3203,16 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>16.3</v>
+        <v>15.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>16.3</v>
+        <v>15.2</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>70.58</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
@@ -3230,16 +3237,16 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>13700</v>
+        <v>16150</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-2.75</v>
+        <v>0.19</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>58.3</v>
+        <v>51.9</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -3257,16 +3264,16 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1830.16</v>
+        <v>1991.51</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
@@ -3359,25 +3366,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9769</v>
+        <v>9658</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9870.23</v>
+        <v>9769.82</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9864.139999999999</v>
+        <v>9932.200000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>196250.23</v>
+        <v>197851.59</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>55.4</v>
+        <v>51.6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10400</v>
+        <v>10300</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -3397,19 +3404,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4847</v>
+        <v>4772</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4836.94</v>
+        <v>4883.03</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4797.43</v>
+        <v>4882.44</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>95464.07000000001</v>
+        <v>97012.84</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>45.4</v>
+        <v>39.2</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>4500</v>
@@ -3435,25 +3442,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2982</v>
+        <v>3107</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3084.41</v>
+        <v>3071.93</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3113.82</v>
+        <v>3071.89</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>62401.19</v>
+        <v>61866.63</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>33.5</v>
+        <v>55.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>2900</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -3473,22 +3480,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5993</v>
+        <v>5728</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5818.38</v>
+        <v>5894.68</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5816.75</v>
+        <v>5846.89</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>115701.26</v>
+        <v>116871.91</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>44.1</v>
+        <v>55.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>6200</v>
@@ -3511,25 +3518,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3539</v>
+        <v>3610</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3577.38</v>
+        <v>3541.69</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3536.37</v>
+        <v>3559.27</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>71286.14999999999</v>
+        <v>71804.59</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>42.4</v>
+        <v>60.2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>3400</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -3549,19 +3556,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2451</v>
+        <v>2317</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2402.87</v>
+        <v>2333.95</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2369.59</v>
+        <v>2343.56</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>47947.23</v>
+        <v>47522.07</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>59.6</v>
+        <v>40.6</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>2300</v>
@@ -3587,22 +3594,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>26208</v>
+        <v>28231</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>27145</v>
+        <v>27062.01</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27010.83</v>
+        <v>27198.57</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>541161.79</v>
+        <v>542754.05</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>48.8</v>
+        <v>52.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>25600</v>
+        <v>25300</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>28800</v>
@@ -3625,25 +3632,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>21427</v>
+        <v>20270</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>21386.61</v>
+        <v>20868.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21193.7</v>
+        <v>21176.12</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>423243.59</v>
+        <v>422668.51</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>51</v>
+        <v>61.6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>20100</v>
+        <v>19900</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>22400</v>
+        <v>22000</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -3663,25 +3670,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10222</v>
+        <v>9773</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10026.89</v>
+        <v>10052.26</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10058.86</v>
+        <v>10129.13</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>204028.44</v>
+        <v>203767.97</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46.3</v>
+        <v>54.9</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10400</v>
+        <v>10700</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -3701,25 +3708,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6650</v>
+        <v>6585</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6748.11</v>
+        <v>6690.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6736.01</v>
+        <v>6745.98</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>134869.1</v>
+        <v>135956.92</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>50.7</v>
+        <v>36</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>7300</v>
+        <v>7000</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -3739,22 +3746,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1771</v>
+        <v>1727</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1767.12</v>
+        <v>1722.19</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1742.94</v>
+        <v>1727.41</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>34170.2</v>
+        <v>34388.5</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>43.2</v>
+        <v>65.5</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>1800</v>
@@ -3777,19 +3784,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3185</v>
+        <v>3066</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3087.57</v>
+        <v>3066.99</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3067.8</v>
+        <v>3076.58</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>61932.79</v>
+        <v>61812.82</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>49.7</v>
+        <v>50.9</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>2900</v>
@@ -3815,25 +3822,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>60694</v>
+        <v>55979</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>58447.47</v>
+        <v>56551.29</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>58201.79</v>
+        <v>57243.32</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1167828.69</v>
+        <v>1154333.57</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>41.6</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>55400</v>
+        <v>54200</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>61900</v>
+        <v>59900</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -3853,19 +3860,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1348</v>
+        <v>1357</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1346.68</v>
+        <v>1358.9</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1353.62</v>
+        <v>1360.59</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>26988.54</v>
+        <v>27003.38</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>52.3</v>
+        <v>49</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1300</v>
@@ -3891,25 +3898,25 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8129</v>
+        <v>8227</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8459.209999999999</v>
+        <v>8454.76</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8490.530000000001</v>
+        <v>8488.790000000001</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>169424.76</v>
+        <v>169870.87</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>54.3</v>
+        <v>50.1</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -3929,25 +3936,25 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>6958</v>
+        <v>6680</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>6782.4</v>
+        <v>6917.54</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6828.39</v>
+        <v>6851.69</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>136259.95</v>
+        <v>137214.79</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>67.8</v>
+        <v>42.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -3967,19 +3974,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>9002</v>
+        <v>9080</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9251.42</v>
+        <v>9305.15</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9237.98</v>
+        <v>9211.07</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>184362.87</v>
+        <v>184361.62</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>40.3</v>
+        <v>47.8</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>8800</v>
@@ -4005,25 +4012,25 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4672</v>
+        <v>4734</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4753.18</v>
+        <v>4682.88</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4780.13</v>
+        <v>4710.89</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>96353.16</v>
+        <v>94390.35000000001</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>38.8</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>4500</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>5100</v>
+        <v>4900</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -4043,22 +4050,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1235</v>
+        <v>1182</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1218.49</v>
+        <v>1214.26</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1203.21</v>
+        <v>1214.28</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>24055.78</v>
+        <v>23892.04</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>56.1</v>
+        <v>59.1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1300</v>
@@ -4081,25 +4088,25 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>13686</v>
+        <v>14830</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>14197.03</v>
+        <v>14444.12</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14100.89</v>
+        <v>14317.67</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>283302.62</v>
+        <v>285295.35</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>50.9</v>
+        <v>54.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>13300</v>
+        <v>13800</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>15000</v>
+        <v>15200</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -4231,32 +4238,32 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9788</v>
+        <v>9575</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>749.7</v>
+        <v>867.62</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5997.57</v>
+        <v>6940.97</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>16.3</v>
+        <v>13.8</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.5</v>
+        <v>1.21</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -4287,32 +4294,32 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5035</v>
+        <v>4604</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>434.29</v>
+        <v>370.53</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3474.34</v>
+        <v>2964.28</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -4343,32 +4350,32 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3044</v>
+        <v>2982</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>230.9</v>
+        <v>209.04</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1293.06</v>
+        <v>1170.61</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>13.2</v>
+        <v>14.3</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>16</v>
+        <v>17.3</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -4399,32 +4406,32 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5533</v>
+        <v>5612</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>547.97</v>
+        <v>576.98</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3044.29</v>
+        <v>3205.43</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>14.1</v>
+        <v>13.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -4455,28 +4462,28 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3752</v>
+        <v>3658</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>154.82</v>
+        <v>144.73</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>967.6</v>
+        <v>904.54</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -4511,32 +4518,32 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2377</v>
+        <v>2299</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>134.34</v>
+        <v>138.85</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>806.04</v>
+        <v>833.08</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>17.7</v>
+        <v>16.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>21.6</v>
+        <v>20.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -4567,32 +4574,32 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27286</v>
+        <v>27475</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2580.05</v>
+        <v>2698.03</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>17737.87</v>
+        <v>18548.99</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -4623,32 +4630,32 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20166</v>
+        <v>21550</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1168.5</v>
+        <v>1295.98</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7010.98</v>
+        <v>7775.86</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>17.3</v>
+        <v>16.6</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>21.1</v>
+        <v>20.3</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -4679,32 +4686,32 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10547</v>
+        <v>10337</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>504.75</v>
+        <v>473.27</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2884.3</v>
+        <v>2704.4</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.88</v>
+        <v>1.32</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -4735,32 +4742,32 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7004</v>
+        <v>6707</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>375</v>
+        <v>315.47</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2142.86</v>
+        <v>1802.71</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>18.7</v>
+        <v>21.3</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>17.7</v>
+        <v>20.2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -4791,32 +4798,32 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>61.58</v>
+        <v>59.36</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>383.16</v>
+        <v>369.36</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>27.2</v>
+        <v>28.8</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>19.4</v>
+        <v>20.5</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.21</v>
+        <v>0.42</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -4847,32 +4854,32 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2965</v>
+        <v>3127</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>104.02</v>
+        <v>106.82</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>647.26</v>
+        <v>664.65</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>28.5</v>
+        <v>29.3</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.97</v>
+        <v>1.48</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -4903,32 +4910,32 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>60123</v>
+        <v>56887</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7385.24</v>
+        <v>7224.59</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>49234.9</v>
+        <v>48163.93</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -4959,16 +4966,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1370</v>
+        <v>1386</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>162.2</v>
+        <v>163.31</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1081.35</v>
+        <v>1088.7</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>1.3</v>
@@ -4977,14 +4984,14 @@
         <v>12.7</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5015,32 +5022,32 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8122</v>
+        <v>8449</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>559.45</v>
+        <v>615.89</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>4195.89</v>
+        <v>4619.16</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14.5</v>
+        <v>13.7</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.5</v>
+        <v>13.7</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -5071,32 +5078,32 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6559</v>
+        <v>7020</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>456.87</v>
+        <v>439.33</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3426.55</v>
+        <v>3295.01</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>14.4</v>
+        <v>16</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>14.4</v>
+        <v>16</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.39</v>
+        <v>0.58</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -5104,9 +5111,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5127,32 +5134,32 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9103</v>
+        <v>9063</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>636.47</v>
+        <v>626.09</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>4773.56</v>
+        <v>4695.66</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.34</v>
+        <v>0.44</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -5183,32 +5190,32 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4806</v>
+        <v>4887</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>351.55</v>
+        <v>341.86</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2636.66</v>
+        <v>2563.94</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -5239,32 +5246,32 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1140</v>
+        <v>1156</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>75.16</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>563.7</v>
+        <v>640.15</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>15.2</v>
+        <v>13.5</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>15.2</v>
+        <v>13.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -5272,9 +5279,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -5295,32 +5302,32 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14773</v>
+        <v>14227</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1873.26</v>
+        <v>1716.03</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>12488.4</v>
+        <v>11440.23</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -5361,7 +5368,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
@@ -5418,7 +5425,7 @@
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
@@ -5464,7 +5471,7 @@
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
@@ -5510,7 +5517,7 @@
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
@@ -5556,7 +5563,7 @@
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
@@ -5602,7 +5609,7 @@
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
@@ -5648,7 +5655,7 @@
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Sampoerna</t>
         </is>
@@ -5694,7 +5701,7 @@
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
@@ -5740,7 +5747,7 @@
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Telkom</t>
         </is>
@@ -5786,7 +5793,7 @@
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
@@ -5832,7 +5839,7 @@
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Indocement</t>
         </is>
@@ -5891,21 +5898,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>📊 DASHBOARD SAHAM INDONESIA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Last Update: 2026-06-26 12:25</t>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Last Update: 2026-06-27 17:47</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>IHSG Level</t>
         </is>
@@ -5917,7 +5924,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>IHSG Change</t>
         </is>
@@ -5929,7 +5936,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Top Sector</t>
         </is>
@@ -5941,7 +5948,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Worst Sector</t>
         </is>
@@ -5953,69 +5960,69 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr"/>
+      <c r="A8" s="12" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>HOLD Signals</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr"/>
+      <c r="A12" s="12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Best Buy Today</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>ANTM.JK, KLBF.JK, INTP.JK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>UNVR.JK, HMSP.JK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -55,7 +55,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -88,12 +88,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00dcfce7"/>
-        <bgColor rgb="00dcfce7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00fee2e2"/>
         <bgColor rgb="00fee2e2"/>
       </patternFill>
@@ -117,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -129,11 +123,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -568,28 +561,28 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5853.95</v>
+        <v>5788.91</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>53.95</v>
+        <v>-11.09</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.92</v>
+        <v>-0.19</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5881.93</v>
+        <v>5798.96</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5827.34</v>
+        <v>5765.79</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>653M</t>
+          <t>657M</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -600,23 +593,23 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5832.13</v>
+        <v>5776.74</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>11.55</v>
+        <v>1.51</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5856.2</v>
+        <v>5781.7</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5808.37</v>
+        <v>5747.07</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>765M</t>
+          <t>543M</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -632,28 +625,28 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5821.56</v>
+        <v>5766.02</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>26.72</v>
+        <v>2.44</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.46</v>
+        <v>0.04</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5832.08</v>
+        <v>5776.18</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5794.03</v>
+        <v>5739.38</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>570M</t>
+          <t>535M</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -664,28 +657,28 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5865.62</v>
+        <v>5801.38</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>49.3</v>
+        <v>-25.52</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.84</v>
+        <v>-0.44</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5895.52</v>
+        <v>5812.02</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5857.77</v>
+        <v>5780.75</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>722M</t>
+          <t>739M</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -696,28 +689,28 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5830.65</v>
+        <v>5868.83</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-41.44</v>
+        <v>15.72</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.71</v>
+        <v>0.27</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5844.51</v>
+        <v>5879.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5813</v>
+        <v>5843.9</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>718M</t>
+          <t>644M</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -728,28 +721,28 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5843.69</v>
+        <v>5821.84</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>31.45</v>
+        <v>2.25</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.54</v>
+        <v>0.04</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5860.6</v>
+        <v>5824.5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5817.83</v>
+        <v>5806.56</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>658M</t>
+          <t>710M</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -760,28 +753,28 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>5884.57</v>
+        <v>5855.93</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>44.28</v>
+        <v>-7.6</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.75</v>
+        <v>-0.13</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5909.94</v>
+        <v>5858.88</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5866.47</v>
+        <v>5842.84</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>688M</t>
+          <t>536M</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -792,23 +785,23 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5847.09</v>
+        <v>5895.75</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>42.25</v>
+        <v>48.5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5856.51</v>
+        <v>5914.06</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5837</v>
+        <v>5891.38</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>751M</t>
+          <t>551M</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -824,28 +817,28 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5803.35</v>
+        <v>5800.92</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>16.46</v>
+        <v>-48.34</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.28</v>
+        <v>-0.83</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5815.82</v>
+        <v>5819.44</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5802.01</v>
+        <v>5774.65</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>618M</t>
+          <t>706M</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -856,23 +849,23 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5784.97</v>
+        <v>5881.46</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-15.72</v>
+        <v>-10.36</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.18</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5809.09</v>
+        <v>5902.5</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5776.92</v>
+        <v>5866.58</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>661M</t>
+          <t>522M</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -888,23 +881,23 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5828.02</v>
+        <v>5861.37</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>51.12</v>
+        <v>43.07</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5828.29</v>
+        <v>5870.29</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5807.05</v>
+        <v>5832.24</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>629M</t>
+          <t>784M</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -920,28 +913,28 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5852.11</v>
+        <v>5813.4</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>44.17</v>
+        <v>-44.42</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.75</v>
+        <v>-0.76</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5867.72</v>
+        <v>5813.83</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5826.91</v>
+        <v>5803.12</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>580M</t>
+          <t>543M</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -952,28 +945,28 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5843.36</v>
+        <v>5761.2</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-2.94</v>
+        <v>-40.38</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5868.9</v>
+        <v>5768.23</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>5824.95</v>
+        <v>5733.91</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>766M</t>
+          <t>603M</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -984,28 +977,28 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5819.47</v>
+        <v>5917.93</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>43.12</v>
+        <v>-18.15</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.74</v>
+        <v>-0.31</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5844.74</v>
+        <v>5927.21</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5793.3</v>
+        <v>5888.94</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>695M</t>
+          <t>588M</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1009,23 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5804.97</v>
+        <v>5971.99</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>40.95</v>
+        <v>30.78</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.71</v>
+        <v>0.52</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5812.14</v>
+        <v>5988.79</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5785.5</v>
+        <v>5952.73</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>699M</t>
+          <t>672M</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1048,23 +1041,23 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5738.32</v>
+        <v>5820.73</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-11.07</v>
+        <v>-18.34</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.32</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5748.15</v>
+        <v>5844.5</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5725.08</v>
+        <v>5807.07</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>685M</t>
+          <t>697M</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1080,28 +1073,28 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5805.16</v>
+        <v>5882.81</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-32.16</v>
+        <v>43.16</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-0.55</v>
+        <v>0.73</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>5815.26</v>
+        <v>5905.41</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5784.27</v>
+        <v>5863.16</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>660M</t>
+          <t>580M</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1112,23 +1105,23 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5841.96</v>
+        <v>5899.53</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>33.75</v>
+        <v>55.41</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.58</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5854.48</v>
+        <v>5925.12</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5838.08</v>
+        <v>5891.85</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>799M</t>
+          <t>735M</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1144,28 +1137,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>6089.53</v>
+        <v>5816.7</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>46.85</v>
+        <v>19.85</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.77</v>
+        <v>0.34</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>6096.59</v>
+        <v>5845.56</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6081.29</v>
+        <v>5790.09</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>601M</t>
+          <t>689M</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1176,28 +1169,28 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5796.46</v>
+        <v>5908.96</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>27.95</v>
+        <v>-42.91</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5801.46</v>
+        <v>5918.81</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5773.53</v>
+        <v>5890.24</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>681M</t>
+          <t>780M</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1208,28 +1201,28 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5786.44</v>
+        <v>5938.92</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-36.94</v>
+        <v>28.65</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-0.64</v>
+        <v>0.48</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>5807.92</v>
+        <v>5945.81</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5775.65</v>
+        <v>5913.81</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>563M</t>
+          <t>729M</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1240,23 +1233,23 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5725.25</v>
+        <v>5721.81</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-25.65</v>
+        <v>-36.49</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.64</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5728.71</v>
+        <v>5743.9</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5700.24</v>
+        <v>5700.58</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>530M</t>
+          <t>776M</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1272,23 +1265,23 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5904.82</v>
+        <v>5828.96</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>27.47</v>
+        <v>21.39</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5924.2</v>
+        <v>5842</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>5893.31</v>
+        <v>5809.84</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>606M</t>
+          <t>679M</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1304,28 +1297,28 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5825.24</v>
+        <v>5764.81</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>45.86</v>
+        <v>-6.37</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.79</v>
+        <v>-0.11</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5832.43</v>
+        <v>5788.33</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5813.66</v>
+        <v>5752.05</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>591M</t>
+          <t>728M</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1336,23 +1329,23 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>5936.75</v>
+        <v>5964.13</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>57.04</v>
+        <v>43.3</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.96</v>
+        <v>0.73</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5945.81</v>
+        <v>5993.63</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5908.81</v>
+        <v>5935.9</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>657M</t>
+          <t>751M</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1368,28 +1361,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5847.7</v>
+        <v>5761.85</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-47.15</v>
+        <v>-18.51</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.32</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5866.46</v>
+        <v>5780.05</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5837.95</v>
+        <v>5749.62</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>580M</t>
+          <t>681M</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1400,28 +1393,28 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>6199.7</v>
+        <v>5886.57</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>25.86</v>
+        <v>6.53</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.42</v>
+        <v>0.11</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>6201.41</v>
+        <v>5887.45</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>6182.14</v>
+        <v>5885.72</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>656M</t>
+          <t>524M</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1432,28 +1425,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5947.57</v>
+        <v>5832.26</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>39.71</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.67</v>
+        <v>0.16</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5969.15</v>
+        <v>5841.91</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5944.09</v>
+        <v>5816</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>617M</t>
+          <t>609M</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1464,28 +1457,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5879.33</v>
+        <v>5825.63</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3.15</v>
+        <v>41.81</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.05</v>
+        <v>0.72</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5905.73</v>
+        <v>5851.21</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5868.92</v>
+        <v>5824.49</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>594M</t>
+          <t>724M</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1496,28 +1489,28 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5895.94</v>
+        <v>5870.92</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-24.57</v>
+        <v>15.9</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0.42</v>
+        <v>0.27</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5906.78</v>
+        <v>5896.84</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5884.55</v>
+        <v>5843.84</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>620M</t>
+          <t>563M</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1528,28 +1521,28 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5802.61</v>
+        <v>5936.66</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>40.37</v>
+        <v>18.95</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.7</v>
+        <v>0.32</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5803.45</v>
+        <v>5947.6</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>5788.06</v>
+        <v>5912.04</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>676M</t>
+          <t>640M</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -2078,16 +2071,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9900</v>
+        <v>10050</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-1.03</v>
+        <v>1.58</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>46.1</v>
+        <v>47.6</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -2105,16 +2098,16 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>14.7</v>
+        <v>13.7</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>842.35</v>
+        <v>917.05</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -2139,16 +2132,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5450</v>
+        <v>4150</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1.21</v>
+        <v>-0.48</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>53.1</v>
+        <v>40.1</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -2166,16 +2159,16 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>16.4</v>
+        <v>15.6</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>414.64</v>
+        <v>333.19</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -2200,16 +2193,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3250</v>
+        <v>2900</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-1.3</v>
+        <v>-0.73</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>50.6</v>
+        <v>48.4</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -2227,16 +2220,16 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>243.35</v>
+        <v>212.65</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -2261,16 +2254,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5550</v>
+        <v>5750</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.06</v>
+        <v>-0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>54.7</v>
+        <v>51.3</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -2288,16 +2281,16 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>539.88</v>
+        <v>535.17</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
@@ -2322,16 +2315,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-2.04</v>
+        <v>1.12</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>38.2</v>
+        <v>45.5</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -2349,16 +2342,16 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>22.8</v>
+        <v>25.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>157.94</v>
+        <v>136.47</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -2383,25 +2376,25 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2350</v>
+        <v>2250</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3.46</v>
+        <v>0.89</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>25.8</v>
+        <v>62.8</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -2410,16 +2403,16 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>19.4</v>
+        <v>16.9</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>23.7</v>
+        <v>20.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>120.99</v>
+        <v>133.31</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -2444,16 +2437,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>26600</v>
+        <v>29100</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>43.9</v>
+        <v>46.8</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -2471,16 +2464,16 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>11.8</v>
+        <v>10.6</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>17.1</v>
+        <v>15.4</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>2261.94</v>
+        <v>2741.38</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -2505,16 +2498,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21550</v>
+        <v>22200</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.03</v>
+        <v>-2.73</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>63</v>
+        <v>51.9</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -2532,16 +2525,16 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>1265.96</v>
+        <v>1261.29</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -2566,16 +2559,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>11550</v>
+        <v>11050</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-2.61</v>
+        <v>-2.44</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>-0.02</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>53.2</v>
+        <v>48</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -2593,16 +2586,16 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>21.7</v>
+        <v>20.5</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>20.7</v>
+        <v>19.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>531.05</v>
+        <v>537.75</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2627,16 +2620,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5950</v>
+        <v>6850</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.33</v>
+        <v>2.72</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>57</v>
+        <v>52.7</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -2654,16 +2647,16 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>19.8</v>
+        <v>22</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>18.8</v>
+        <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>299.91</v>
+        <v>311.59</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2691,13 +2684,13 @@
         <v>1950</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.89</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>-0.05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>43.7</v>
+        <v>47.7</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -2715,16 +2708,16 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>30.6</v>
+        <v>29.2</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>21.8</v>
+        <v>20.9</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>63.76</v>
+        <v>66.67</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2749,16 +2742,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3250</v>
+        <v>3300</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1.03</v>
+        <v>-2.69</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>47.9</v>
+        <v>39.2</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -2776,16 +2769,16 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>29.1</v>
+        <v>27.1</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>111.87</v>
+        <v>121.67</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -2810,16 +2803,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>62150</v>
+        <v>54150</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-1.6</v>
+        <v>2.97</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>40.5</v>
+        <v>47.3</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -2837,16 +2830,16 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>7476.47</v>
+        <v>6359.42</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2874,13 +2867,13 @@
         <v>1350</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1.41</v>
+        <v>-0.01</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>56.2</v>
+        <v>49.8</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -2898,16 +2891,16 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>12.5</v>
+        <v>11.7</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>162.58</v>
+        <v>172.37</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2932,16 +2925,16 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7550</v>
+        <v>7400</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.63</v>
+        <v>0.19</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>55.5</v>
+        <v>58.2</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -2959,16 +2952,16 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>528.01</v>
+        <v>494.06</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
@@ -2993,16 +2986,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6250</v>
+        <v>5800</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-2.52</v>
+        <v>2.85</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>53.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -3020,16 +3013,16 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>393.32</v>
+        <v>360.6</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -3054,16 +3047,16 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>8050</v>
+        <v>9000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2.22</v>
+        <v>1.19</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>51</v>
+        <v>56.4</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -3081,16 +3074,16 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>523.8200000000001</v>
+        <v>592.42</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -3115,16 +3108,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4250</v>
+        <v>4600</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-2.69</v>
+        <v>-2.97</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>-0.06</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>48.8</v>
+        <v>32.9</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -3136,22 +3129,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>15.7</v>
+        <v>14.4</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>270.82</v>
+        <v>319.21</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
@@ -3176,16 +3169,16 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>49.7</v>
+        <v>43.9</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -3203,16 +3196,16 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>75.70999999999999</v>
+        <v>75.14</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
@@ -3237,16 +3230,16 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>16150</v>
+        <v>14950</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>51.9</v>
+        <v>42.7</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -3264,16 +3257,16 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1991.51</v>
+        <v>1721.59</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
@@ -3366,25 +3359,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9658</v>
+        <v>9441</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9769.82</v>
+        <v>9743.610000000001</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9932.200000000001</v>
+        <v>9832.48</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>197851.59</v>
+        <v>195048.75</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>51.6</v>
+        <v>37.2</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>9300</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10300</v>
+        <v>10200</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -3404,19 +3397,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4772</v>
+        <v>5035</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4883.03</v>
+        <v>4887.78</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4882.44</v>
+        <v>4820</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>97012.84</v>
+        <v>95247.33</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>39.2</v>
+        <v>68</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>4500</v>
@@ -3442,19 +3435,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3107</v>
+        <v>3014</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3071.93</v>
+        <v>3030.59</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3071.89</v>
+        <v>3070.64</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>61866.63</v>
+        <v>61933.89</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>55.2</v>
+        <v>56.7</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>2900</v>
@@ -3480,25 +3473,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5728</v>
+        <v>5674</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5894.68</v>
+        <v>5742.59</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5846.89</v>
+        <v>5749.94</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>116871.91</v>
+        <v>115764.41</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>55.5</v>
+        <v>61.3</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5600</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6200</v>
+        <v>5900</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -3518,25 +3511,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3610</v>
+        <v>3470</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3541.69</v>
+        <v>3586.75</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3559.27</v>
+        <v>3595.24</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>71804.59</v>
+        <v>71729.66</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>60.2</v>
+        <v>62.1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>3400</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -3556,25 +3549,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2317</v>
+        <v>2311</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2333.95</v>
+        <v>2385.12</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2343.56</v>
+        <v>2430.05</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>47522.07</v>
+        <v>48182.2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>40.6</v>
+        <v>44.3</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>2300</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -3594,22 +3587,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>28231</v>
+        <v>28263</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>27062.01</v>
+        <v>27171.56</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27198.57</v>
+        <v>26827.1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>542754.05</v>
+        <v>537495.33</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>52.6</v>
+        <v>54.7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>25300</v>
+        <v>25400</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>28800</v>
@@ -3632,25 +3625,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>20270</v>
+        <v>20778</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>20868.34</v>
+        <v>21181.53</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21176.12</v>
+        <v>20788.21</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>422668.51</v>
+        <v>421202.21</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>61.6</v>
+        <v>54.6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>19900</v>
+        <v>20400</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>22000</v>
+        <v>22300</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -3670,25 +3663,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9773</v>
+        <v>10224</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10052.26</v>
+        <v>10194.14</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10129.13</v>
+        <v>10143.81</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>203767.97</v>
+        <v>203904.34</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>54.9</v>
+        <v>43.2</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>9600</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10700</v>
+        <v>10800</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -3708,25 +3701,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6585</v>
+        <v>7122</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6690.52</v>
+        <v>6859.46</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6745.98</v>
+        <v>6867.43</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>135956.92</v>
+        <v>138072.2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>36</v>
+        <v>51.8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>7000</v>
+        <v>7300</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -3746,19 +3739,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1727</v>
+        <v>1732</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1722.19</v>
+        <v>1727.47</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1727.41</v>
+        <v>1708.57</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>34388.5</v>
+        <v>34351.28</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>65.5</v>
+        <v>54.6</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1600</v>
@@ -3784,25 +3777,25 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3066</v>
+        <v>3125</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3066.99</v>
+        <v>3126.21</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3076.58</v>
+        <v>3118.03</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>61812.82</v>
+        <v>62212.84</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>50.9</v>
+        <v>59.3</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>2900</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
@@ -3822,25 +3815,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>55979</v>
+        <v>56126</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>56551.29</v>
+        <v>57123.93</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>57243.32</v>
+        <v>57230.73</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1154333.57</v>
+        <v>1156014.33</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>51</v>
+        <v>58.3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>54200</v>
+        <v>55000</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>59900</v>
+        <v>58900</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -3860,19 +3853,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1358.9</v>
+        <v>1332.06</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1360.59</v>
+        <v>1333.61</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>27003.38</v>
+        <v>26782.08</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>49</v>
+        <v>38.1</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1300</v>
@@ -3898,25 +3891,25 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8227</v>
+        <v>8755</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8454.76</v>
+        <v>8610.139999999999</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8488.790000000001</v>
+        <v>8551.08</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>169870.87</v>
+        <v>171453.67</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>50.1</v>
+        <v>60.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>8100</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9100</v>
+        <v>8900</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -3936,25 +3929,25 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>6680</v>
+        <v>6500</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>6917.54</v>
+        <v>6846.91</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6851.69</v>
+        <v>6825.51</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>137214.79</v>
+        <v>136337.29</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>42.6</v>
+        <v>49.5</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -3974,25 +3967,25 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>9080</v>
+        <v>9337</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9305.15</v>
+        <v>9170.68</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9211.07</v>
+        <v>9278.559999999999</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>184361.62</v>
+        <v>185951.54</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>47.8</v>
+        <v>49.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8800</v>
+        <v>8700</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>9800</v>
+        <v>9600</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -4012,25 +4005,25 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4734</v>
+        <v>4630</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4682.88</v>
+        <v>4759.15</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4710.89</v>
+        <v>4789.29</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>94390.35000000001</v>
+        <v>95683.39999999999</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>4500</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -4050,19 +4043,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1182</v>
+        <v>1220</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1214.26</v>
+        <v>1238.94</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1214.28</v>
+        <v>1216.87</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>23892.04</v>
+        <v>24049.33</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>59.1</v>
+        <v>47.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>1200</v>
@@ -4088,25 +4081,25 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>14830</v>
+        <v>13627</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>14444.12</v>
+        <v>14052.06</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14317.67</v>
+        <v>14222.69</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>285295.35</v>
+        <v>282566.13</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>54.2</v>
+        <v>48</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>13800</v>
+        <v>13400</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>15200</v>
+        <v>15000</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -4238,32 +4231,32 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9575</v>
+        <v>9970</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>867.62</v>
+        <v>841.34</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6940.97</v>
+        <v>6730.75</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>13.8</v>
+        <v>14.8</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.21</v>
+        <v>0.95</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -4294,32 +4287,32 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4604</v>
+        <v>4788</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>370.53</v>
+        <v>366.47</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2964.28</v>
+        <v>2931.74</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>15.5</v>
+        <v>16.3</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.8</v>
+        <v>1.43</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -4350,32 +4343,32 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2982</v>
+        <v>3048</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>209.04</v>
+        <v>216.32</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1170.61</v>
+        <v>1211.4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.44</v>
+        <v>0.21</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -4406,28 +4399,28 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5612</v>
+        <v>5743</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>576.98</v>
+        <v>615.77</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3205.43</v>
+        <v>3420.95</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>13.6</v>
+        <v>13.1</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -4462,32 +4455,32 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3658</v>
+        <v>3733</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>144.73</v>
+        <v>137.78</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>904.54</v>
+        <v>861.1</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>25.3</v>
+        <v>27.1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>18.2</v>
+        <v>19.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -4518,32 +4511,32 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2299</v>
+        <v>2343</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>138.85</v>
+        <v>125.03</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>833.08</v>
+        <v>750.16</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>16.6</v>
+        <v>18.7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>20.2</v>
+        <v>22.9</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.31</v>
+        <v>0.48</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -4574,32 +4567,32 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27475</v>
+        <v>27385</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2698.03</v>
+        <v>2731.74</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>18548.99</v>
+        <v>18780.69</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -4630,32 +4623,32 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21550</v>
+        <v>20278</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1295.98</v>
+        <v>1240.55</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7775.86</v>
+        <v>7443.28</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>16.6</v>
+        <v>16.3</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -4686,32 +4679,32 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10337</v>
+        <v>10105</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>473.27</v>
+        <v>519.35</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2704.4</v>
+        <v>2967.73</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>21.8</v>
+        <v>19.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>20.7</v>
+        <v>18.5</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -4742,32 +4735,32 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6707</v>
+        <v>6563</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>315.47</v>
+        <v>334.2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1802.71</v>
+        <v>1909.69</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>21.3</v>
+        <v>19.6</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>20.2</v>
+        <v>18.7</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -4798,32 +4791,32 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1707</v>
+        <v>1771</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>59.36</v>
+        <v>62.5</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>369.36</v>
+        <v>388.86</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28.8</v>
+        <v>28.3</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -4854,28 +4847,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3127</v>
+        <v>3214</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>106.82</v>
+        <v>123.41</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>664.65</v>
+        <v>767.87</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>29.3</v>
+        <v>26</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>20.9</v>
+        <v>18.6</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -4910,32 +4903,32 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>56887</v>
+        <v>59613</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7224.59</v>
+        <v>7407.02</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>48163.93</v>
+        <v>49380.13</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.48</v>
+        <v>0.68</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -4966,32 +4959,32 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1386</v>
+        <v>1350</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>163.31</v>
+        <v>154.77</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1088.7</v>
+        <v>1031.83</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5022,32 +5015,32 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8449</v>
+        <v>8500</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>615.89</v>
+        <v>537.33</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>4619.16</v>
+        <v>4029.97</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>13.7</v>
+        <v>15.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>13.7</v>
+        <v>15.8</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -5055,9 +5048,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5078,32 +5071,32 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>7020</v>
+        <v>6863</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>439.33</v>
+        <v>456.45</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3295.01</v>
+        <v>3423.36</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.39</v>
+        <v>1.83</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -5134,25 +5127,25 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9063</v>
+        <v>9183</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>626.09</v>
+        <v>622.03</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>4695.66</v>
+        <v>4665.22</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>1.75</v>
@@ -5190,32 +5183,32 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4887</v>
+        <v>4835</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>341.86</v>
+        <v>349.83</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2563.94</v>
+        <v>2623.71</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.35</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -5246,32 +5239,32 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1156</v>
+        <v>1233</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>85.34999999999999</v>
+        <v>88.27</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>640.15</v>
+        <v>662.04</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -5302,32 +5295,32 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14227</v>
+        <v>13638</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1716.03</v>
+        <v>1555.57</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>11440.23</v>
+        <v>10370.46</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -5368,7 +5361,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
@@ -5425,7 +5418,7 @@
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
@@ -5471,7 +5464,7 @@
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
@@ -5517,7 +5510,7 @@
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
@@ -5563,7 +5556,7 @@
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
@@ -5609,7 +5602,7 @@
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
@@ -5655,7 +5648,7 @@
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Sampoerna</t>
         </is>
@@ -5701,7 +5694,7 @@
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
@@ -5747,7 +5740,7 @@
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Telkom</t>
         </is>
@@ -5793,7 +5786,7 @@
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
@@ -5839,7 +5832,7 @@
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Indocement</t>
         </is>
@@ -5898,21 +5891,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>📊 DASHBOARD SAHAM INDONESIA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Last Update: 2026-06-27 17:47</t>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Last Update: 2026-06-27 17:46</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>IHSG Level</t>
         </is>
@@ -5924,7 +5917,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>IHSG Change</t>
         </is>
@@ -5936,7 +5929,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Top Sector</t>
         </is>
@@ -5948,7 +5941,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Worst Sector</t>
         </is>
@@ -5960,69 +5953,69 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr"/>
+      <c r="A8" s="11" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>HOLD Signals</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr"/>
+      <c r="A12" s="11" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Best Buy Today</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>ANTM.JK, KLBF.JK, INTP.JK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>UNVR.JK, HMSP.JK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -561,23 +561,23 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5788.91</v>
+        <v>5817.93</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>-11.09</v>
+        <v>17.93</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-0.19</v>
+        <v>0.31</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5798.96</v>
+        <v>5821.81</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5765.79</v>
+        <v>5799.05</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>657M</t>
+          <t>630M</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -593,23 +593,23 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5776.74</v>
+        <v>5801.58</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.51</v>
+        <v>-2.94</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5781.7</v>
+        <v>5822.6</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5747.07</v>
+        <v>5792.55</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>543M</t>
+          <t>736M</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5766.02</v>
+        <v>5891.05</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.44</v>
+        <v>59.74</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.04</v>
+        <v>1.01</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5776.18</v>
+        <v>5891.47</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5739.38</v>
+        <v>5861.57</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>535M</t>
+          <t>798M</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -657,28 +657,28 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5801.38</v>
+        <v>5883.36</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-25.52</v>
+        <v>55.92</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.44</v>
+        <v>0.95</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5812.02</v>
+        <v>5890.69</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5780.75</v>
+        <v>5860.49</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>739M</t>
+          <t>613M</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -689,23 +689,23 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5868.83</v>
+        <v>5851.47</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>15.72</v>
+        <v>-12.85</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.27</v>
+        <v>-0.22</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5879.8</v>
+        <v>5858.09</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5843.9</v>
+        <v>5827.77</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>644M</t>
+          <t>513M</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5821.84</v>
+        <v>5777.23</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2.25</v>
+        <v>-5.66</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5824.5</v>
+        <v>5794.41</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5806.56</v>
+        <v>5774.37</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>710M</t>
+          <t>750M</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>5855.93</v>
+        <v>5852</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-7.6</v>
+        <v>59.65</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.13</v>
+        <v>1.02</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5858.88</v>
+        <v>5855.58</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5842.84</v>
+        <v>5841.33</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5895.75</v>
+        <v>5827.76</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>48.5</v>
+        <v>-2.84</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.82</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5914.06</v>
+        <v>5850.19</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5891.38</v>
+        <v>5823.83</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>551M</t>
+          <t>720M</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -817,28 +817,28 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5800.92</v>
+        <v>5738.44</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-48.34</v>
+        <v>14.4</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.83</v>
+        <v>0.25</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5819.44</v>
+        <v>5768.39</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5774.65</v>
+        <v>5735.04</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>706M</t>
+          <t>637M</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -849,28 +849,28 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5881.46</v>
+        <v>5738.34</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-10.36</v>
+        <v>-41.78</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.73</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5902.5</v>
+        <v>5740.1</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5866.58</v>
+        <v>5731.82</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>522M</t>
+          <t>787M</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -881,28 +881,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5861.37</v>
+        <v>5806.36</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>43.07</v>
+        <v>-31.3</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.73</v>
+        <v>-0.54</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5870.29</v>
+        <v>5806.52</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5832.24</v>
+        <v>5805.17</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>784M</t>
+          <t>521M</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -913,28 +913,28 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5813.4</v>
+        <v>5835.7</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-44.42</v>
+        <v>5.11</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0.76</v>
+        <v>0.09</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5813.83</v>
+        <v>5860.27</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5803.12</v>
+        <v>5826.13</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>543M</t>
+          <t>609M</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -945,28 +945,28 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5761.2</v>
+        <v>5991.85</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-40.38</v>
+        <v>47.08</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-0.7</v>
+        <v>0.79</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5768.23</v>
+        <v>5999.94</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>5733.91</v>
+        <v>5965.98</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>603M</t>
+          <t>609M</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5917.93</v>
+        <v>5854.44</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-18.15</v>
+        <v>-31.45</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.54</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5927.21</v>
+        <v>5881.18</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5888.94</v>
+        <v>5849.81</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>588M</t>
+          <t>559M</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1009,23 +1009,23 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5971.99</v>
+        <v>5882.17</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>30.78</v>
+        <v>43.14</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.52</v>
+        <v>0.73</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5988.79</v>
+        <v>5902.2</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5952.73</v>
+        <v>5855.72</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>672M</t>
+          <t>724M</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1041,28 +1041,28 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5820.73</v>
+        <v>5969.18</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-18.34</v>
+        <v>50.18</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.32</v>
+        <v>0.84</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5844.5</v>
+        <v>5972.42</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5807.07</v>
+        <v>5942.38</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>697M</t>
+          <t>688M</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1073,28 +1073,28 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5882.81</v>
+        <v>5949.55</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>43.16</v>
+        <v>-21.93</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.73</v>
+        <v>-0.37</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>5905.41</v>
+        <v>5972.39</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5863.16</v>
+        <v>5945.88</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>580M</t>
+          <t>786M</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1105,28 +1105,28 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5899.53</v>
+        <v>5804.19</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>55.41</v>
+        <v>15.34</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.26</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5925.12</v>
+        <v>5820.47</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5891.85</v>
+        <v>5797.3</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>735M</t>
+          <t>720M</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5816.7</v>
+        <v>5990.91</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>19.85</v>
+        <v>39.01</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.34</v>
+        <v>0.65</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5845.56</v>
+        <v>6020.35</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5790.09</v>
+        <v>5977.08</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>689M</t>
+          <t>736M</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1169,28 +1169,28 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5908.96</v>
+        <v>5747.29</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-42.91</v>
+        <v>59.44</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-0.73</v>
+        <v>1.03</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5918.81</v>
+        <v>5775.83</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5890.24</v>
+        <v>5737.83</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>780M</t>
+          <t>740M</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1201,19 +1201,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5938.92</v>
+        <v>5705</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>28.65</v>
+        <v>-33.57</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.48</v>
+        <v>-0.59</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>5945.81</v>
+        <v>5729.52</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5913.81</v>
+        <v>5684.66</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1233,28 +1233,28 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5721.81</v>
+        <v>5929.76</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-36.49</v>
+        <v>59.34</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-0.64</v>
+        <v>1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5743.9</v>
+        <v>5941.38</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5700.58</v>
+        <v>5904.72</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>776M</t>
+          <t>672M</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1265,28 +1265,28 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5828.96</v>
+        <v>5646.79</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>21.39</v>
+        <v>-20.72</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.37</v>
+        <v>-0.37</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5842</v>
+        <v>5673.54</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>5809.84</v>
+        <v>5630.83</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>679M</t>
+          <t>540M</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1297,28 +1297,28 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5764.81</v>
+        <v>5876.55</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-6.37</v>
+        <v>-25.12</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.43</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5788.33</v>
+        <v>5883.18</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5752.05</v>
+        <v>5855.76</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>728M</t>
+          <t>558M</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1329,28 +1329,28 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>5964.13</v>
+        <v>5990.59</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>43.3</v>
+        <v>-16.26</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.73</v>
+        <v>-0.27</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5993.63</v>
+        <v>6016.66</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5935.9</v>
+        <v>5973.38</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>751M</t>
+          <t>778M</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5761.85</v>
+        <v>6051.74</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-18.51</v>
+        <v>35.95</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.32</v>
+        <v>0.59</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5780.05</v>
+        <v>6079.61</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5749.62</v>
+        <v>6042.69</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>681M</t>
+          <t>701M</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1393,28 +1393,28 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>5886.57</v>
+        <v>5601.18</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>6.53</v>
+        <v>-35.79</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.11</v>
+        <v>-0.64</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>5887.45</v>
+        <v>5606.39</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5885.72</v>
+        <v>5575.03</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>524M</t>
+          <t>556M</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1425,28 +1425,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5832.26</v>
+        <v>5575.81</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9.210000000000001</v>
+        <v>-47.23</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.16</v>
+        <v>-0.85</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5841.91</v>
+        <v>5576.67</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5816</v>
+        <v>5574.26</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>609M</t>
+          <t>538M</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1457,23 +1457,23 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5825.63</v>
+        <v>5909.22</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>41.81</v>
+        <v>54.33</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.72</v>
+        <v>0.92</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5851.21</v>
+        <v>5915.17</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5824.49</v>
+        <v>5898.43</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>724M</t>
+          <t>628M</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -1489,28 +1489,28 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5870.92</v>
+        <v>5753.73</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>15.9</v>
+        <v>-20.48</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.27</v>
+        <v>-0.36</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5896.84</v>
+        <v>5769.66</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5843.84</v>
+        <v>5728.73</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>563M</t>
+          <t>662M</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1521,23 +1521,23 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5936.66</v>
+        <v>5849.15</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>18.95</v>
+        <v>-13.48</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.32</v>
+        <v>-0.23</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5947.6</v>
+        <v>5850.24</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>5912.04</v>
+        <v>5826.34</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>640M</t>
+          <t>638M</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -2071,16 +2071,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>10050</v>
+        <v>9000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1.58</v>
+        <v>-2.1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>47.6</v>
+        <v>49.1</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -2098,16 +2098,16 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>917.05</v>
+        <v>808.21</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -2132,16 +2132,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4150</v>
+        <v>5250</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-0.48</v>
+        <v>3.82</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>40.1</v>
+        <v>49.1</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -2159,16 +2159,16 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>12.5</v>
+        <v>11.6</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>15.6</v>
+        <v>14.5</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>333.19</v>
+        <v>451.08</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -2193,16 +2193,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2900</v>
+        <v>2750</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.73</v>
+        <v>3.63</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.13</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>48.4</v>
+        <v>39</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -2214,22 +2214,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>13.6</v>
+        <v>15.1</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>16.6</v>
+        <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>212.65</v>
+        <v>181.6</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -2254,16 +2254,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5750</v>
+        <v>5250</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.03</v>
+        <v>3.01</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>51.3</v>
+        <v>41</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10.7</v>
+        <v>9.9</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>535.17</v>
+        <v>531.65</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
@@ -2315,16 +2315,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1.12</v>
+        <v>-2.57</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>45.5</v>
+        <v>66</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -2342,16 +2342,16 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>25.6</v>
+        <v>24.7</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>18.5</v>
+        <v>17.8</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>136.47</v>
+        <v>153.76</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -2376,16 +2376,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.89</v>
+        <v>-2.75</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>62.8</v>
+        <v>59.5</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -2403,16 +2403,16 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>16.9</v>
+        <v>18.2</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.6</v>
+        <v>22.3</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>133.31</v>
+        <v>120.78</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>29100</v>
+        <v>27100</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.36</v>
+        <v>3.94</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>46.8</v>
+        <v>49</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>15.4</v>
+        <v>14.6</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>2741.38</v>
+        <v>2698.81</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -2498,16 +2498,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>22200</v>
+        <v>22450</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-2.73</v>
+        <v>1.26</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>1261.29</v>
+        <v>1285.19</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -2559,16 +2559,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>11050</v>
+        <v>9850</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-2.44</v>
+        <v>0.51</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>48</v>
+        <v>50.8</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -2586,16 +2586,16 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>19.5</v>
+        <v>20.2</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>537.75</v>
+        <v>462.53</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6850</v>
+        <v>5900</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2.72</v>
+        <v>-1.69</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -2647,16 +2647,16 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>22</v>
+        <v>18.8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>20.9</v>
+        <v>17.8</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>311.59</v>
+        <v>314.56</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1950</v>
+        <v>1500</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.44</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>47.7</v>
+        <v>61.2</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -2708,16 +2708,16 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>29.2</v>
+        <v>26.2</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>66.67</v>
+        <v>57.29</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2742,16 +2742,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3300</v>
+        <v>2700</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-2.69</v>
+        <v>0.27</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>39.2</v>
+        <v>50</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -2769,16 +2769,16 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>27.1</v>
+        <v>26.3</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>121.67</v>
+        <v>102.57</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -2803,16 +2803,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>54150</v>
+        <v>51850</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2.97</v>
+        <v>-0.25</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>47.3</v>
+        <v>53.6</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -2830,16 +2830,16 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>6359.42</v>
+        <v>6137.78</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2864,16 +2864,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-0.01</v>
+        <v>1.44</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>172.37</v>
+        <v>169.41</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2925,16 +2925,16 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7400</v>
+        <v>9250</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.19</v>
+        <v>0.79</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>58.2</v>
+        <v>46.4</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -2946,22 +2946,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>15</v>
+        <v>16.3</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>15</v>
+        <v>16.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>494.06</v>
+        <v>566.84</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
@@ -2986,16 +2986,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5800</v>
+        <v>6200</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2.85</v>
+        <v>0.05</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>39.3</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -3007,22 +3007,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>16.1</v>
+        <v>14.8</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>16.1</v>
+        <v>14.8</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>360.6</v>
+        <v>420.15</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -3047,16 +3047,16 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9000</v>
+        <v>9600</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1.19</v>
+        <v>-1.59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>56.4</v>
+        <v>43.7</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -3068,22 +3068,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>15.2</v>
+        <v>13.5</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>15.2</v>
+        <v>13.5</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>592.42</v>
+        <v>708.8200000000001</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -3108,16 +3108,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4600</v>
+        <v>5450</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-2.97</v>
+        <v>2.59</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>32.9</v>
+        <v>39.4</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -3135,16 +3135,16 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>14.4</v>
+        <v>13.6</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>319.21</v>
+        <v>401.62</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
@@ -3169,16 +3169,16 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>43.9</v>
+        <v>44.5</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -3190,22 +3190,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>16</v>
+        <v>14.1</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>16</v>
+        <v>14.1</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>75.14</v>
+        <v>74.67</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14950</v>
+        <v>13900</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.29</v>
+        <v>-1.73</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>42.7</v>
+        <v>51.5</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1721.59</v>
+        <v>1632.92</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
@@ -3359,25 +3359,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9441</v>
+        <v>9570</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9743.610000000001</v>
+        <v>9830.120000000001</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9832.48</v>
+        <v>9838.959999999999</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>195048.75</v>
+        <v>195438.7</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>37.2</v>
+        <v>57</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>9300</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10200</v>
+        <v>10400</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5035</v>
+        <v>4699</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4887.78</v>
+        <v>4831.92</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4820</v>
+        <v>4802.28</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>95247.33</v>
+        <v>96294.98</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>68</v>
+        <v>66.7</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>5100</v>
@@ -3435,25 +3435,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3014</v>
+        <v>2957</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3030.59</v>
+        <v>3136.4</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3070.64</v>
+        <v>3143.03</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>61933.89</v>
+        <v>62697.62</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>56.7</v>
+        <v>49</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>2900</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5674</v>
+        <v>6024</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5742.59</v>
+        <v>6059.81</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5749.94</v>
+        <v>5949.55</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>115764.41</v>
+        <v>116955.77</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>61.3</v>
+        <v>42.3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5600</v>
+        <v>5900</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>5900</v>
+        <v>6200</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -3511,19 +3511,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3470</v>
+        <v>3435</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3586.75</v>
+        <v>3604.74</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3595.24</v>
+        <v>3588.36</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>71729.66</v>
+        <v>72286.98</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>62.1</v>
+        <v>58.5</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>3400</v>
@@ -3549,19 +3549,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2311</v>
+        <v>2516</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2385.12</v>
+        <v>2382.78</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2430.05</v>
+        <v>2416.25</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>48182.2</v>
+        <v>48637.74</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>44.3</v>
+        <v>45.5</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>2300</v>
@@ -3587,25 +3587,25 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>28263</v>
+        <v>28179</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>27171.56</v>
+        <v>27374.8</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>26827.1</v>
+        <v>27311.34</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>537495.33</v>
+        <v>540111.1899999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>54.7</v>
+        <v>49.7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>25400</v>
+        <v>25800</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>28800</v>
+        <v>28700</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -3625,25 +3625,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>20778</v>
+        <v>20492</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>21181.53</v>
+        <v>21004.26</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20788.21</v>
+        <v>21137.9</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>421202.21</v>
+        <v>418823.92</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>54.6</v>
+        <v>41.6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>20400</v>
+        <v>20000</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>22300</v>
+        <v>22400</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -3663,25 +3663,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10224</v>
+        <v>10275</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10194.14</v>
+        <v>10208.64</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10143.81</v>
+        <v>10259.49</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>203904.34</v>
+        <v>203789.76</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>43.2</v>
+        <v>52.8</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>9600</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10800</v>
+        <v>10600</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -3701,22 +3701,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7122</v>
+        <v>7130</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6859.46</v>
+        <v>6929.85</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6867.43</v>
+        <v>6857.38</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>138072.2</v>
+        <v>135911.18</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>51.8</v>
+        <v>52.8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>6300</v>
+        <v>6600</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>7300</v>
@@ -3739,19 +3739,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1732</v>
+        <v>1702</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1727.47</v>
+        <v>1686.21</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1708.57</v>
+        <v>1711.77</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>34351.28</v>
+        <v>34135.08</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>54.6</v>
+        <v>39.3</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1600</v>
@@ -3777,22 +3777,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3125</v>
+        <v>3024</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3126.21</v>
+        <v>3133.12</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3118.03</v>
+        <v>3111.62</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>62212.84</v>
+        <v>62289.99</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>59.3</v>
+        <v>51.9</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>3300</v>
@@ -3815,25 +3815,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>56126</v>
+        <v>60840</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>57123.93</v>
+        <v>59465.76</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>57230.73</v>
+        <v>58806.42</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1156014.33</v>
+        <v>1163321.46</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>58.3</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>55000</v>
+        <v>55900</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>58900</v>
+        <v>62100</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -3853,19 +3853,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1353</v>
+        <v>1307</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1332.06</v>
+        <v>1350.77</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1333.61</v>
+        <v>1351.19</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>26782.08</v>
+        <v>27189.18</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>38.1</v>
+        <v>51.3</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1300</v>
@@ -3891,25 +3891,25 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8755</v>
+        <v>8844</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8610.139999999999</v>
+        <v>8562.01</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8551.08</v>
+        <v>8519.129999999999</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>171453.67</v>
+        <v>170640.41</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>60.2</v>
+        <v>49.3</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8100</v>
+        <v>8000</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -3929,25 +3929,25 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>6629</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>6790.36</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>6784.44</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>135929.43</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>6500</v>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>6846.91</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>6825.51</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>136337.29</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>6400</v>
-      </c>
       <c r="H17" s="3" t="n">
-        <v>7300</v>
+        <v>7200</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -3967,25 +3967,25 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>9337</v>
+        <v>9574</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9170.68</v>
+        <v>9281.16</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9278.559999999999</v>
+        <v>9257.33</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>185951.54</v>
+        <v>184475.36</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>49.7</v>
+        <v>57.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8700</v>
+        <v>8800</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>9600</v>
+        <v>9800</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -4005,25 +4005,25 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4630</v>
+        <v>4825</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4759.15</v>
+        <v>4805.78</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4789.29</v>
+        <v>4765.36</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>95683.39999999999</v>
+        <v>95060.44</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>47.3</v>
+        <v>56.5</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>4500</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -4043,22 +4043,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1220</v>
+        <v>1167</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1238.94</v>
+        <v>1192.69</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1216.87</v>
+        <v>1203.7</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>24049.33</v>
+        <v>24060.54</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>47.3</v>
+        <v>44.4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1300</v>
@@ -4081,25 +4081,25 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>13627</v>
+        <v>14006</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>14052.06</v>
+        <v>14228.78</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14222.69</v>
+        <v>14258.35</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>282566.13</v>
+        <v>284563.47</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>48</v>
+        <v>51.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>13400</v>
+        <v>13600</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>15000</v>
+        <v>14900</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -4231,32 +4231,32 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9970</v>
+        <v>9596</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>841.34</v>
+        <v>745.41</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6730.75</v>
+        <v>5963.28</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>11.8</v>
+        <v>12.9</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.95</v>
+        <v>1.33</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -4287,32 +4287,32 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4788</v>
+        <v>4589</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>366.47</v>
+        <v>421.67</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2931.74</v>
+        <v>3373.35</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>16.3</v>
+        <v>13.6</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.43</v>
+        <v>0.55</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.13</v>
+        <v>1.49</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -4343,32 +4343,32 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3048</v>
+        <v>3122</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>216.32</v>
+        <v>226.77</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1211.4</v>
+        <v>1269.91</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -4399,13 +4399,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5743</v>
+        <v>5874</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>615.77</v>
+        <v>634.4400000000001</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3420.95</v>
+        <v>3524.69</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>9.300000000000001</v>
@@ -4414,17 +4414,17 @@
         <v>1.7</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -4455,32 +4455,32 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3733</v>
+        <v>3586</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>137.78</v>
+        <v>145.04</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>861.1</v>
+        <v>906.52</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>27.1</v>
+        <v>24.7</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>19.5</v>
+        <v>17.8</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -4511,32 +4511,32 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2343</v>
+        <v>2311</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>125.03</v>
+        <v>141.24</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>750.16</v>
+        <v>847.41</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>18.7</v>
+        <v>16.4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>22.9</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -4567,32 +4567,32 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27385</v>
+        <v>26411</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2731.74</v>
+        <v>2341.52</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>18780.69</v>
+        <v>16097.94</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>14.6</v>
+        <v>16.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -4623,32 +4623,32 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20278</v>
+        <v>20143</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1240.55</v>
+        <v>1157.6</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7443.28</v>
+        <v>6945.62</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>16.3</v>
+        <v>17.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>20</v>
+        <v>21.3</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>0.34</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -4679,32 +4679,32 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10105</v>
+        <v>10043</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>519.35</v>
+        <v>511.38</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2967.73</v>
+        <v>2922.19</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -4735,32 +4735,32 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6563</v>
+        <v>6811</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>334.2</v>
+        <v>323.69</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1909.69</v>
+        <v>1849.68</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>19.6</v>
+        <v>21</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>18.7</v>
+        <v>20</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -4791,32 +4791,32 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1771</v>
+        <v>1659</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>62.5</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>388.86</v>
+        <v>404.19</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28.3</v>
+        <v>25.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>20.2</v>
+        <v>18.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -4847,32 +4847,32 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3214</v>
+        <v>2963</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>123.41</v>
+        <v>99.41</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>767.87</v>
+        <v>618.53</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>26</v>
+        <v>29.8</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>18.6</v>
+        <v>21.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -4903,32 +4903,32 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>59613</v>
+        <v>55417</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7407.02</v>
+        <v>7347.79</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>49380.13</v>
+        <v>48985.24</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -4959,13 +4959,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1350</v>
+        <v>1388</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>154.77</v>
+        <v>159.35</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1031.83</v>
+        <v>1062.31</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4977,14 +4977,14 @@
         <v>13.1</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.67</v>
+        <v>0.31</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5015,32 +5015,32 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8500</v>
+        <v>8444</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>537.33</v>
+        <v>572.86</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>4029.97</v>
+        <v>4296.45</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>15.8</v>
+        <v>14.7</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>15.8</v>
+        <v>14.7</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -5048,9 +5048,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -5071,32 +5071,32 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6863</v>
+        <v>6965</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>456.45</v>
+        <v>449.34</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3423.36</v>
+        <v>3370.09</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -5127,32 +5127,32 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9183</v>
+        <v>9043</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>622.03</v>
+        <v>580</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>4665.22</v>
+        <v>4350</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>14.8</v>
+        <v>15.6</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>14.8</v>
+        <v>15.6</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -5160,9 +5160,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5183,32 +5183,32 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4835</v>
+        <v>4785</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>349.83</v>
+        <v>305.17</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2623.71</v>
+        <v>2288.74</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>13.8</v>
+        <v>15.7</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -5216,9 +5216,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1233</v>
+        <v>1214</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>88.27</v>
+        <v>86.56</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>662.04</v>
+        <v>649.1900000000001</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14</v>
@@ -5257,14 +5257,14 @@
         <v>14</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -5295,32 +5295,32 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>13638</v>
+        <v>14699</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1555.57</v>
+        <v>2005.77</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>10370.46</v>
+        <v>13371.83</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>13.2</v>
+        <v>11</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -5900,7 +5900,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Last Update: 2026-06-27 17:46</t>
+          <t>Last Update: 2026-06-27 20:28</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -41,6 +41,9 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
@@ -50,9 +53,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="7">
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -123,17 +123,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -557,187 +558,187 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5817.93</v>
+        <v>5754.66</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>17.93</v>
+        <v>-45.34</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.31</v>
+        <v>-0.79</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5821.81</v>
+        <v>5758.02</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5799.05</v>
+        <v>5753.5</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>630M</t>
+          <t>559M</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5801.58</v>
+        <v>5849.5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>-2.94</v>
+        <v>50.73</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.87</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5822.6</v>
+        <v>5873.91</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5792.55</v>
+        <v>5832.37</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>736M</t>
+          <t>660M</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5891.05</v>
+        <v>5787.2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>59.74</v>
+        <v>18.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.01</v>
+        <v>0.32</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5891.47</v>
+        <v>5816.17</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5861.57</v>
+        <v>5760.24</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>798M</t>
+          <t>520M</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5883.36</v>
+        <v>5787.51</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>55.92</v>
+        <v>-22.16</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.95</v>
+        <v>-0.38</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5890.69</v>
+        <v>5797.82</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5860.49</v>
+        <v>5776.51</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>613M</t>
+          <t>779M</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5851.47</v>
+        <v>5768.04</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-12.85</v>
+        <v>-45.6</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5858.09</v>
+        <v>5790.12</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5827.77</v>
+        <v>5746.49</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>513M</t>
+          <t>719M</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5777.23</v>
+        <v>5806.07</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-5.66</v>
+        <v>6.2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5794.41</v>
+        <v>5812.27</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5774.37</v>
+        <v>5799.26</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>750M</t>
+          <t>763M</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -749,123 +750,123 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>5852</v>
+        <v>5858.1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>59.65</v>
+        <v>-5.74</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02</v>
+        <v>-0.1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5855.58</v>
+        <v>5873.87</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5841.33</v>
+        <v>5830.75</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>536M</t>
+          <t>574M</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5827.76</v>
+        <v>5836.31</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-2.84</v>
+        <v>55.72</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.95</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5850.19</v>
+        <v>5846.89</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5823.83</v>
+        <v>5829.7</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>720M</t>
+          <t>704M</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5738.44</v>
+        <v>5677.03</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14.4</v>
+        <v>-41.24</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.25</v>
+        <v>-0.73</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5768.39</v>
+        <v>5688.14</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5735.04</v>
+        <v>5647.66</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>637M</t>
+          <t>628M</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5738.34</v>
+        <v>5801.34</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-41.78</v>
+        <v>-38.75</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.67</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5740.1</v>
+        <v>5824.73</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5731.82</v>
+        <v>5777.91</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>787M</t>
+          <t>739M</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -877,55 +878,55 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5806.36</v>
+        <v>5895.77</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-31.3</v>
+        <v>-11.41</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.19</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5806.52</v>
+        <v>5911.71</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5805.17</v>
+        <v>5893.39</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>521M</t>
+          <t>522M</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5835.7</v>
+        <v>5786.52</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>5.11</v>
+        <v>-25.63</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.09</v>
+        <v>-0.44</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5860.27</v>
+        <v>5808.4</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5826.13</v>
+        <v>5779.24</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -934,194 +935,194 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5991.85</v>
+        <v>5795.96</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>47.08</v>
+        <v>-32.99</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.79</v>
+        <v>-0.57</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5999.94</v>
+        <v>5824.59</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>5965.98</v>
+        <v>5787.52</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>609M</t>
+          <t>577M</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5854.44</v>
+        <v>5888.16</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-31.45</v>
+        <v>43.23</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>-0.54</v>
+        <v>0.73</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5881.18</v>
+        <v>5917.65</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5849.81</v>
+        <v>5883.73</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>559M</t>
+          <t>583M</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5882.17</v>
+        <v>5785.19</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>43.14</v>
+        <v>-3.17</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.73</v>
+        <v>-0.05</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5902.2</v>
+        <v>5790.02</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5855.72</v>
+        <v>5779.88</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>724M</t>
+          <t>561M</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5969.18</v>
+        <v>5825.83</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>50.18</v>
+        <v>17.89</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5972.42</v>
+        <v>5839.68</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5942.38</v>
+        <v>5822.93</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>688M</t>
+          <t>780M</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5949.55</v>
+        <v>5967.3</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-21.93</v>
+        <v>28.6</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-0.37</v>
+        <v>0.48</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>5972.39</v>
+        <v>5969.34</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5945.88</v>
+        <v>5962.48</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>786M</t>
+          <t>582M</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5804.19</v>
+        <v>5904.85</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>15.34</v>
+        <v>8.77</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5820.47</v>
+        <v>5929.56</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5797.3</v>
+        <v>5876.25</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>720M</t>
+          <t>612M</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1133,59 +1134,59 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5990.91</v>
+        <v>5820.52</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>39.01</v>
+        <v>-35</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.65</v>
+        <v>-0.6</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>6020.35</v>
+        <v>5831.52</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5977.08</v>
+        <v>5805.61</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>736M</t>
+          <t>677M</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5747.29</v>
+        <v>5879.16</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>59.44</v>
+        <v>20.95</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1.03</v>
+        <v>0.36</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5775.83</v>
+        <v>5893.92</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5737.83</v>
+        <v>5858.76</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>740M</t>
+          <t>713M</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1197,59 +1198,59 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5705</v>
+        <v>5880.05</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-33.57</v>
+        <v>51.32</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-0.59</v>
+        <v>0.87</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>5729.52</v>
+        <v>5903.81</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5684.66</v>
+        <v>5866.32</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>729M</t>
+          <t>779M</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5929.76</v>
+        <v>5909.33</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>59.34</v>
+        <v>55</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5941.38</v>
+        <v>5925.69</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5904.72</v>
+        <v>5903.23</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>672M</t>
+          <t>535M</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1261,27 +1262,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5646.79</v>
+        <v>5950.42</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-20.72</v>
+        <v>-25.21</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.42</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5673.54</v>
+        <v>5972.63</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>5630.83</v>
+        <v>5949.46</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>540M</t>
+          <t>703M</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1293,27 +1294,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5876.55</v>
+        <v>5848.76</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-25.12</v>
+        <v>-44.42</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.76</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5883.18</v>
+        <v>5853.65</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5855.76</v>
+        <v>5828.76</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>558M</t>
+          <t>690M</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -1325,27 +1326,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>5990.59</v>
+        <v>5733.01</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-16.26</v>
+        <v>-8.32</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.15</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>6016.66</v>
+        <v>5739.83</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5973.38</v>
+        <v>5729.06</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>778M</t>
+          <t>707M</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1357,27 +1358,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6051.74</v>
+        <v>5690.82</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>35.95</v>
+        <v>29.63</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6079.61</v>
+        <v>5695.27</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6042.69</v>
+        <v>5663.08</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>701M</t>
+          <t>773M</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1389,59 +1390,59 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>5601.18</v>
+        <v>5763.39</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-35.79</v>
+        <v>37.96</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-0.64</v>
+        <v>0.66</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>5606.39</v>
+        <v>5773.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5575.03</v>
+        <v>5749.04</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>556M</t>
+          <t>663M</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5575.81</v>
+        <v>5839.39</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-47.23</v>
+        <v>-48.1</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.82</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5576.67</v>
+        <v>5860.49</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5574.26</v>
+        <v>5818.16</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>538M</t>
+          <t>677M</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1453,96 +1454,96 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5909.22</v>
+        <v>5886.21</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>54.33</v>
+        <v>-21.39</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.92</v>
+        <v>-0.36</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5915.17</v>
+        <v>5904.97</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5898.43</v>
+        <v>5884.35</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>628M</t>
+          <t>599M</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5753.73</v>
+        <v>6102.73</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-20.48</v>
+        <v>29.25</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0.36</v>
+        <v>0.48</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5769.66</v>
+        <v>6103.6</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5728.73</v>
+        <v>6088.44</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>662M</t>
+          <t>701M</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5849.15</v>
+        <v>5758.39</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-13.48</v>
+        <v>-47.35</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.82</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5850.24</v>
+        <v>5787.4</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>5826.34</v>
+        <v>5728.56</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>638M</t>
+          <t>597M</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -2071,16 +2072,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9000</v>
+        <v>11200</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-2.1</v>
+        <v>-0.39</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>49.1</v>
+        <v>61.1</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -2098,16 +2099,16 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>13.9</v>
+        <v>14.7</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>808.21</v>
+        <v>955.35</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -2132,16 +2133,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5250</v>
+        <v>4350</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3.82</v>
+        <v>0.85</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>49.1</v>
+        <v>50.6</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -2159,16 +2160,16 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>451.08</v>
+        <v>363.4</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -2193,16 +2194,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2750</v>
+        <v>2900</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3.63</v>
+        <v>1.07</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>39</v>
+        <v>53.8</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -2214,22 +2215,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>15.1</v>
+        <v>13.5</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>18.4</v>
+        <v>16.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>181.6</v>
+        <v>215.13</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -2254,16 +2255,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5250</v>
+        <v>5700</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3.01</v>
+        <v>0.85</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>41</v>
+        <v>59.9</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -2281,16 +2282,16 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>531.65</v>
+        <v>555.72</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
@@ -2315,16 +2316,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3800</v>
+        <v>4050</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-2.57</v>
+        <v>2.51</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>66</v>
+        <v>51.4</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -2342,16 +2343,16 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>24.7</v>
+        <v>26.2</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>153.76</v>
+        <v>154.35</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -2379,13 +2380,13 @@
         <v>2200</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-2.75</v>
+        <v>-0.05</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>59.5</v>
+        <v>51.4</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -2403,16 +2404,16 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>18.2</v>
+        <v>19.6</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>120.78</v>
+        <v>112.32</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -2437,16 +2438,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27100</v>
+        <v>24900</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3.94</v>
+        <v>1.29</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0.01</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>49</v>
+        <v>42.1</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -2464,16 +2465,16 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>2698.81</v>
+        <v>2300.81</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -2498,43 +2499,43 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>22450</v>
+        <v>22500</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.26</v>
+        <v>-2.1</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>51.8</v>
+        <v>72.8</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="K9" s="3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>21.4</v>
+        <v>20.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>1285.19</v>
+        <v>1364.29</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -2559,16 +2560,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>9850</v>
+        <v>10500</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.51</v>
+        <v>-2.38</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>50.8</v>
+        <v>53.2</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -2586,16 +2587,16 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>462.53</v>
+        <v>495.99</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2620,16 +2621,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5900</v>
+        <v>6400</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-1.69</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>52.8</v>
+        <v>41.1</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -2647,16 +2648,16 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>18.8</v>
+        <v>21.9</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>17.8</v>
+        <v>20.8</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>314.56</v>
+        <v>292.8</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2681,16 +2682,16 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1500</v>
+        <v>1850</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-1.44</v>
+        <v>0.9</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>61.2</v>
+        <v>56</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -2708,16 +2709,16 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>26.2</v>
+        <v>28.7</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>18.7</v>
+        <v>20.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>57.29</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2742,16 +2743,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2700</v>
+        <v>3050</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.27</v>
+        <v>-1.82</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -2769,16 +2770,16 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>102.57</v>
+        <v>116.37</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -2803,16 +2804,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>51850</v>
+        <v>60700</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-0.25</v>
+        <v>-2.47</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -2830,16 +2831,16 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>6137.78</v>
+        <v>7954.23</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2867,13 +2868,13 @@
         <v>1400</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1.44</v>
+        <v>0.16</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -2891,16 +2892,16 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>12.4</v>
+        <v>11.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>169.41</v>
+        <v>176.66</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2928,13 +2929,13 @@
         <v>9250</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.79</v>
+        <v>2.3</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>46.4</v>
+        <v>44.2</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -2946,22 +2947,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>16.3</v>
+        <v>14.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>16.3</v>
+        <v>14.8</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>566.84</v>
+        <v>624.37</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
@@ -2986,16 +2987,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6200</v>
+        <v>6650</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.05</v>
+        <v>-2.1</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>39.3</v>
+        <v>48</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -3013,16 +3014,16 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>14.8</v>
+        <v>14.2</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>14.8</v>
+        <v>14.2</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>420.15</v>
+        <v>468.23</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -3047,16 +3048,16 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9600</v>
+        <v>9900</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-1.59</v>
+        <v>-3</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>43.7</v>
+        <v>39</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -3068,22 +3069,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>13.5</v>
+        <v>16.3</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>13.5</v>
+        <v>16.3</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>708.8200000000001</v>
+        <v>607.42</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -3108,16 +3109,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>5450</v>
+        <v>4500</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2.59</v>
+        <v>0.18</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>39.4</v>
+        <v>57.3</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -3135,16 +3136,16 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>13.6</v>
+        <v>14.6</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>401.62</v>
+        <v>307.72</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
@@ -3169,16 +3170,16 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1050</v>
+        <v>1150</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.72</v>
+        <v>-0.72</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.26</v>
+        <v>-0.06</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>44.5</v>
+        <v>46.3</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -3190,22 +3191,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>14.1</v>
+        <v>16.4</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>14.1</v>
+        <v>16.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>74.67</v>
+        <v>70.28</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
@@ -3230,16 +3231,16 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>13900</v>
+        <v>13950</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-1.73</v>
+        <v>-2.12</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>51.5</v>
+        <v>45.1</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -3257,16 +3258,16 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1632.92</v>
+        <v>1874.76</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
@@ -3359,25 +3360,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9570</v>
+        <v>9502</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9830.120000000001</v>
+        <v>9636.719999999999</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9838.959999999999</v>
+        <v>9688.370000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>195438.7</v>
+        <v>196217.22</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>57</v>
+        <v>50.7</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>9300</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10400</v>
+        <v>9900</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -3397,22 +3398,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4699</v>
+        <v>5009</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4831.92</v>
+        <v>4886.65</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4802.28</v>
+        <v>4817.76</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>96294.98</v>
+        <v>96271.27</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>66.7</v>
+        <v>62.9</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>5100</v>
@@ -3435,19 +3436,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2957</v>
+        <v>3139</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3136.4</v>
+        <v>3122.61</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3143.03</v>
+        <v>3136.1</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>62697.62</v>
+        <v>62205.43</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>2900</v>
@@ -3473,25 +3474,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6024</v>
+        <v>5535</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6059.81</v>
+        <v>5773.92</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5949.55</v>
+        <v>5824.45</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>116955.77</v>
+        <v>115501.09</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>42.3</v>
+        <v>58.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5900</v>
+        <v>5400</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -3511,25 +3512,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3435</v>
+        <v>3544</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3604.74</v>
+        <v>3578.3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3588.36</v>
+        <v>3561.78</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>72286.98</v>
+        <v>71917.49000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>58.5</v>
+        <v>50.8</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>3400</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -3549,25 +3550,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2516</v>
+        <v>2410</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2382.78</v>
+        <v>2375</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2416.25</v>
+        <v>2401.72</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>48637.74</v>
+        <v>47964.47</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -3587,25 +3588,25 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>28179</v>
+        <v>26721</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>27374.8</v>
+        <v>27398.7</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27311.34</v>
+        <v>27083.29</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>540111.1899999999</v>
+        <v>540652.37</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>25800</v>
+        <v>26200</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>28700</v>
+        <v>28900</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -3625,25 +3626,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>20492</v>
+        <v>21654</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>21004.26</v>
+        <v>20934.92</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21137.9</v>
+        <v>20908.17</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>418823.92</v>
+        <v>419012.3</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>41.6</v>
+        <v>56.4</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>20000</v>
+        <v>19600</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>22400</v>
+        <v>22100</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -3663,25 +3664,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10275</v>
+        <v>9984</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10208.64</v>
+        <v>10242.06</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10259.49</v>
+        <v>10251.84</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>203789.76</v>
+        <v>204174.09</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>52.8</v>
+        <v>49.9</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9600</v>
+        <v>9800</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10600</v>
+        <v>10800</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -3701,22 +3702,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7130</v>
+        <v>6945</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6929.85</v>
+        <v>6881.51</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6857.38</v>
+        <v>6889.87</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>135911.18</v>
+        <v>136708.52</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>52.8</v>
+        <v>37.5</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>6600</v>
+        <v>6400</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>7300</v>
@@ -3739,25 +3740,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1702</v>
+        <v>1664</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1686.21</v>
+        <v>1675.34</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1711.77</v>
+        <v>1691.92</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>34135.08</v>
+        <v>33998.63</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>39.3</v>
+        <v>51.8</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1600</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
@@ -3777,22 +3778,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3024</v>
+        <v>3184</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3133.12</v>
+        <v>3089.56</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3111.62</v>
+        <v>3110.91</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>62289.99</v>
+        <v>62475.94</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>51.9</v>
+        <v>34.2</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>3300</v>
@@ -3815,25 +3816,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>60840</v>
+        <v>55538</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>59465.76</v>
+        <v>57443.11</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>58806.42</v>
+        <v>57697.04</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1163321.46</v>
+        <v>1164637.21</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>55900</v>
+        <v>54400</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>62100</v>
+        <v>59700</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -3853,19 +3854,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1307</v>
+        <v>1379</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1350.77</v>
+        <v>1355.55</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1351.19</v>
+        <v>1348.33</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>27189.18</v>
+        <v>26853.45</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>51.3</v>
+        <v>46.1</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1300</v>
@@ -3891,19 +3892,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8844</v>
+        <v>8387</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8562.01</v>
+        <v>8455.870000000001</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8519.129999999999</v>
+        <v>8493.92</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>170640.41</v>
+        <v>170030.41</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>49.3</v>
+        <v>65.7</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>8000</v>
@@ -3929,22 +3930,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>6629</v>
+        <v>6850</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>6790.36</v>
+        <v>6863.69</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6784.44</v>
+        <v>6861.77</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>135929.43</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>50</v>
+        <v>136481.7</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>71</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>7200</v>
@@ -3954,9 +3955,9 @@
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3967,25 +3968,25 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>9574</v>
+        <v>8795</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9281.16</v>
+        <v>9008.26</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9257.33</v>
+        <v>9016.85</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>184475.36</v>
+        <v>183261.42</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>57.1</v>
+        <v>63.8</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8800</v>
+        <v>8600</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>9800</v>
+        <v>9500</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -4005,22 +4006,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4825</v>
+        <v>4881</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4805.78</v>
+        <v>4820.16</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4765.36</v>
+        <v>4776.45</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>95060.44</v>
+        <v>95724.52</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>56.5</v>
+        <v>51.7</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>5100</v>
@@ -4043,22 +4044,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1167</v>
+        <v>1232</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1192.69</v>
+        <v>1221.39</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1203.7</v>
+        <v>1209.44</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>24060.54</v>
+        <v>23914.12</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>44.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1300</v>
@@ -4081,25 +4082,25 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>14006</v>
+        <v>13701</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>14228.78</v>
+        <v>14171.15</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14258.35</v>
+        <v>14194.21</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>284563.47</v>
+        <v>285668.33</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>51.3</v>
+        <v>50.1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>13600</v>
+        <v>13400</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14900</v>
+        <v>15200</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -4231,32 +4232,32 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9596</v>
+        <v>9981</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>745.41</v>
+        <v>767.5700000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5963.28</v>
+        <v>6140.56</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -4287,32 +4288,32 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4589</v>
+        <v>4627</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>421.67</v>
+        <v>377.06</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3373.35</v>
+        <v>3016.46</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>13.6</v>
+        <v>15.3</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.55</v>
+        <v>0.87</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -4343,32 +4344,32 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3122</v>
+        <v>3169</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>226.77</v>
+        <v>248.72</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1269.91</v>
+        <v>1392.82</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>13.8</v>
+        <v>12.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>16.7</v>
+        <v>15.5</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -4399,32 +4400,32 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5874</v>
+        <v>5883</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>634.4400000000001</v>
+        <v>537.8200000000001</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3524.69</v>
+        <v>2987.89</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>13</v>
+        <v>15.3</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.93</v>
+        <v>1.23</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -4455,32 +4456,32 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3586</v>
+        <v>3620</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>145.04</v>
+        <v>149.7</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>906.52</v>
+        <v>935.62</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>24.7</v>
+        <v>24.2</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>17.8</v>
+        <v>17.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -4511,32 +4512,32 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2311</v>
+        <v>2344</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>141.24</v>
+        <v>123.06</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>847.41</v>
+        <v>738.35</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>16.4</v>
+        <v>19</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -4567,32 +4568,32 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>26411</v>
+        <v>27649</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2341.52</v>
+        <v>2375.32</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>16097.94</v>
+        <v>16330.32</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>16.4</v>
+        <v>16.9</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -4623,32 +4624,32 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20143</v>
+        <v>21022</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1157.6</v>
+        <v>1171.92</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>6945.62</v>
+        <v>7031.51</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -4679,32 +4680,32 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10043</v>
+        <v>10016</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>511.38</v>
+        <v>553.49</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2922.19</v>
+        <v>3162.79</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>19.6</v>
+        <v>18.1</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>18.7</v>
+        <v>17.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.45</v>
+        <v>0.27</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -4735,32 +4736,32 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6811</v>
+        <v>6963</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>323.69</v>
+        <v>320.92</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1849.68</v>
+        <v>1833.84</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>21</v>
+        <v>21.7</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -4791,32 +4792,32 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1659</v>
+        <v>1773</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>64.95999999999999</v>
+        <v>59.58</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>404.19</v>
+        <v>370.69</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>25.5</v>
+        <v>29.8</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>18.2</v>
+        <v>21.3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.28</v>
+        <v>0.55</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -4847,13 +4848,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2963</v>
+        <v>2987</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>99.41</v>
+        <v>100.26</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>618.53</v>
+        <v>623.8099999999999</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>29.8</v>
@@ -4865,14 +4866,14 @@
         <v>21.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.57</v>
+        <v>0.24</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -4903,13 +4904,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>55417</v>
+        <v>57440</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7347.79</v>
+        <v>7627.9</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>48985.24</v>
+        <v>50852.68</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>7.5</v>
@@ -4921,14 +4922,14 @@
         <v>11.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>1.88</v>
+        <v>2.44</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -4959,32 +4960,32 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1388</v>
+        <v>1348</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>159.35</v>
+        <v>158.19</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1062.31</v>
+        <v>1054.6</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5015,32 +5016,32 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8444</v>
+        <v>8296</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>572.86</v>
+        <v>611.67</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>4296.45</v>
+        <v>4587.55</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14.7</v>
+        <v>13.6</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.7</v>
+        <v>13.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -5071,32 +5072,32 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6965</v>
+        <v>7022</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>449.34</v>
+        <v>497.3</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3370.09</v>
+        <v>3729.74</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>15.5</v>
+        <v>14.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>15.5</v>
+        <v>14.1</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.32</v>
+        <v>0.57</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -5104,9 +5105,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -5127,32 +5128,32 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9043</v>
+        <v>8758</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>580</v>
+        <v>545.29</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>4350</v>
+        <v>4089.66</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>15.6</v>
+        <v>16.1</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>15.6</v>
+        <v>16.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.34</v>
+        <v>0.58</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.87</v>
+        <v>1.21</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -5183,32 +5184,32 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4785</v>
+        <v>4668</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>305.17</v>
+        <v>341.41</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2288.74</v>
+        <v>2560.56</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>15.7</v>
+        <v>13.7</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -5216,9 +5217,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -5239,32 +5240,32 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1214</v>
+        <v>1159</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>86.56</v>
+        <v>83.27</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>649.1900000000001</v>
+        <v>624.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -5295,32 +5296,32 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14699</v>
+        <v>14646</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2005.77</v>
+        <v>1851.98</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>13371.83</v>
+        <v>12346.51</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11</v>
+        <v>11.9</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -5361,7 +5362,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
@@ -5418,7 +5419,7 @@
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
@@ -5464,7 +5465,7 @@
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
@@ -5510,7 +5511,7 @@
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
@@ -5556,7 +5557,7 @@
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
@@ -5602,7 +5603,7 @@
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
@@ -5648,7 +5649,7 @@
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Sampoerna</t>
         </is>
@@ -5694,7 +5695,7 @@
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
@@ -5740,7 +5741,7 @@
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Telkom</t>
         </is>
@@ -5786,7 +5787,7 @@
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
@@ -5832,7 +5833,7 @@
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Indocement</t>
         </is>
@@ -5891,21 +5892,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>📊 DASHBOARD SAHAM INDONESIA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Last Update: 2026-06-27 20:28</t>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Last Update: 2026-06-29 08:05</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>IHSG Level</t>
         </is>
@@ -5917,7 +5918,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>IHSG Change</t>
         </is>
@@ -5929,7 +5930,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Top Sector</t>
         </is>
@@ -5941,7 +5942,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Worst Sector</t>
         </is>
@@ -5953,69 +5954,69 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr"/>
+      <c r="A8" s="12" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>HOLD Signals</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr"/>
+      <c r="A12" s="12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Best Buy Today</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>ANTM.JK, KLBF.JK, INTP.JK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>UNVR.JK, HMSP.JK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -41,9 +41,6 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
@@ -53,6 +50,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="7">
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -123,18 +123,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -562,23 +561,23 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5754.66</v>
+        <v>5761.95</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>-45.34</v>
+        <v>-38.05</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.66</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5758.02</v>
+        <v>5791.37</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5753.5</v>
+        <v>5732.61</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>559M</t>
+          <t>653M</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -594,28 +593,28 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5849.5</v>
+        <v>5790.94</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>50.73</v>
+        <v>-21.78</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.87</v>
+        <v>-0.38</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5873.91</v>
+        <v>5801.53</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5832.37</v>
+        <v>5774.2</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>660M</t>
+          <t>611M</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -626,28 +625,28 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5787.2</v>
+        <v>5815.13</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18.3</v>
+        <v>31.78</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.32</v>
+        <v>0.55</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5816.17</v>
+        <v>5822.99</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5760.24</v>
+        <v>5812.17</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>520M</t>
+          <t>769M</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -658,28 +657,28 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5787.51</v>
+        <v>5814.43</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-22.16</v>
+        <v>16.02</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.38</v>
+        <v>0.28</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5797.82</v>
+        <v>5823.15</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5776.51</v>
+        <v>5806.88</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>779M</t>
+          <t>709M</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -690,28 +689,28 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5768.04</v>
+        <v>5900.62</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-45.6</v>
+        <v>59.68</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.79</v>
+        <v>1.01</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5790.12</v>
+        <v>5908.27</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5746.49</v>
+        <v>5875.34</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>719M</t>
+          <t>591M</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -722,28 +721,28 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5806.07</v>
+        <v>5750.1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6.2</v>
+        <v>-47.75</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.11</v>
+        <v>-0.83</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5812.27</v>
+        <v>5756.66</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5799.26</v>
+        <v>5749.6</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>763M</t>
+          <t>776M</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -754,28 +753,28 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>5858.1</v>
+        <v>5787.06</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-5.74</v>
+        <v>-39.87</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5873.87</v>
+        <v>5809.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5830.75</v>
+        <v>5763.19</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>574M</t>
+          <t>510M</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -786,28 +785,28 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5836.31</v>
+        <v>5814.63</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>55.72</v>
+        <v>18.65</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.95</v>
+        <v>0.32</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5846.89</v>
+        <v>5818.66</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5829.7</v>
+        <v>5803.71</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>704M</t>
+          <t>720M</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -818,23 +817,23 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5677.03</v>
+        <v>5786.19</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-41.24</v>
+        <v>-35.54</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.61</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5688.14</v>
+        <v>5796.48</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5647.66</v>
+        <v>5781.92</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>628M</t>
+          <t>655M</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -850,28 +849,28 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5801.34</v>
+        <v>5746.91</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-38.75</v>
+        <v>-2.39</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.04</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5824.73</v>
+        <v>5775.04</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5777.91</v>
+        <v>5727.17</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>739M</t>
+          <t>630M</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -882,23 +881,23 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5895.77</v>
+        <v>5797.99</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-11.41</v>
+        <v>-16.25</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.28</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5911.71</v>
+        <v>5827.42</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5893.39</v>
+        <v>5790.86</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>522M</t>
+          <t>737M</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -914,28 +913,28 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5786.52</v>
+        <v>5821.76</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-25.63</v>
+        <v>31.76</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0.44</v>
+        <v>0.55</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5808.4</v>
+        <v>5830.74</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5779.24</v>
+        <v>5795.66</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>609M</t>
+          <t>750M</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -946,23 +945,23 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5795.96</v>
+        <v>5781.77</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-32.99</v>
+        <v>-37.12</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.64</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5824.59</v>
+        <v>5811.46</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>5787.52</v>
+        <v>5778.54</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>577M</t>
+          <t>603M</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -978,23 +977,23 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5888.16</v>
+        <v>5901.12</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>43.23</v>
+        <v>41.53</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5917.65</v>
+        <v>5930.95</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5883.73</v>
+        <v>5895.95</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>583M</t>
+          <t>653M</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1010,28 +1009,28 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5785.19</v>
+        <v>5905.66</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-3.17</v>
+        <v>49.64</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.84</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5790.02</v>
+        <v>5916.79</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5779.88</v>
+        <v>5900.69</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>561M</t>
+          <t>568M</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1042,28 +1041,28 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5825.83</v>
+        <v>5859.47</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>17.89</v>
+        <v>27.6</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5839.68</v>
+        <v>5879.83</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5822.93</v>
+        <v>5858.5</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>780M</t>
+          <t>678M</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1074,28 +1073,28 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5967.3</v>
+        <v>5775.18</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>28.6</v>
+        <v>4.58</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.48</v>
+        <v>0.08</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>5969.34</v>
+        <v>5791.33</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5962.48</v>
+        <v>5763.23</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>582M</t>
+          <t>640M</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1106,28 +1105,28 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5904.85</v>
+        <v>5909.38</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>8.77</v>
+        <v>-42.36</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.15</v>
+        <v>-0.72</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5929.56</v>
+        <v>5916.12</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5876.25</v>
+        <v>5902.78</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>612M</t>
+          <t>512M</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1138,28 +1137,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5820.52</v>
+        <v>5796.26</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-35</v>
+        <v>1.82</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-0.6</v>
+        <v>0.03</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5831.52</v>
+        <v>5798</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5805.61</v>
+        <v>5790.59</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>677M</t>
+          <t>557M</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1170,28 +1169,28 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5879.16</v>
+        <v>5890.24</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>20.95</v>
+        <v>-1.57</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.36</v>
+        <v>-0.03</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5893.92</v>
+        <v>5894.9</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5858.76</v>
+        <v>5879.2</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>713M</t>
+          <t>604M</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1202,28 +1201,28 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5880.05</v>
+        <v>5877.4</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>51.32</v>
+        <v>-10.9</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.87</v>
+        <v>-0.19</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>5903.81</v>
+        <v>5906.72</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5866.32</v>
+        <v>5872.68</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>779M</t>
+          <t>671M</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1234,28 +1233,28 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5909.33</v>
+        <v>5927.77</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>55</v>
+        <v>14.17</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.93</v>
+        <v>0.24</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5925.69</v>
+        <v>5944.98</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5903.23</v>
+        <v>5911.68</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>535M</t>
+          <t>655M</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1266,23 +1265,23 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5950.42</v>
+        <v>5803.06</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-25.21</v>
+        <v>-42.03</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.72</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5972.63</v>
+        <v>5827.53</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>5949.46</v>
+        <v>5793.62</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>703M</t>
+          <t>797M</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1298,23 +1297,23 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5848.76</v>
+        <v>5695.65</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-44.42</v>
+        <v>-27.73</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.49</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5853.65</v>
+        <v>5708.65</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5828.76</v>
+        <v>5688.61</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>690M</t>
+          <t>768M</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -1330,28 +1329,28 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>5733.01</v>
+        <v>5651.65</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-8.32</v>
+        <v>-22.11</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.39</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5739.83</v>
+        <v>5670.82</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5729.06</v>
+        <v>5638.16</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>707M</t>
+          <t>616M</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1362,23 +1361,23 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5690.82</v>
+        <v>5947.53</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>29.63</v>
+        <v>24.77</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5695.27</v>
+        <v>5948.35</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5663.08</v>
+        <v>5942</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>773M</t>
+          <t>617M</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1394,28 +1393,28 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>5763.39</v>
+        <v>5852.35</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>37.96</v>
+        <v>-6.41</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.66</v>
+        <v>-0.11</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>5773.8</v>
+        <v>5860.96</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5749.04</v>
+        <v>5829.95</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>663M</t>
+          <t>598M</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1426,28 +1425,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5839.39</v>
+        <v>5843.33</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-48.1</v>
+        <v>57.84</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.82</v>
+        <v>0.99</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5860.49</v>
+        <v>5865.54</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5818.16</v>
+        <v>5823.44</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>677M</t>
+          <t>723M</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1458,28 +1457,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5886.21</v>
+        <v>5844.47</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-21.39</v>
+        <v>53.31</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-0.36</v>
+        <v>0.91</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5904.97</v>
+        <v>5846.14</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5884.35</v>
+        <v>5815.15</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>599M</t>
+          <t>793M</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1490,23 +1489,23 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>6102.73</v>
+        <v>6100.32</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>29.25</v>
+        <v>48.45</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.48</v>
+        <v>0.79</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6103.6</v>
+        <v>6124.38</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>6088.44</v>
+        <v>6072.73</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>701M</t>
+          <t>544M</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1522,28 +1521,28 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5758.39</v>
+        <v>5847.37</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-47.35</v>
+        <v>27.94</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-0.82</v>
+        <v>0.48</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5787.4</v>
+        <v>5867.61</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>5728.56</v>
+        <v>5820.2</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>597M</t>
+          <t>577M</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -2072,16 +2071,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>11200</v>
+        <v>11100</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.39</v>
+        <v>-2.83</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0</v>
+        <v>-0.03</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>61.1</v>
+        <v>45.1</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -2099,16 +2098,16 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>11.7</v>
+        <v>10.9</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>14.7</v>
+        <v>13.6</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>955.35</v>
+        <v>1018.41</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -2133,16 +2132,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4350</v>
+        <v>5500</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.85</v>
+        <v>-0.19</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.02</v>
+        <v>-0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>50.6</v>
+        <v>41.5</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -2160,16 +2159,16 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>363.4</v>
+        <v>434.77</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -2194,16 +2193,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2900</v>
+        <v>2950</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1.07</v>
+        <v>-0.45</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>53.8</v>
+        <v>64.3</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -2221,16 +2220,16 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>16.4</v>
+        <v>17.9</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>215.13</v>
+        <v>200.17</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -2255,16 +2254,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5700</v>
+        <v>5750</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.85</v>
+        <v>-0.22</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>59.9</v>
+        <v>46.6</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -2282,16 +2281,16 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>555.72</v>
+        <v>552.86</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
@@ -2316,16 +2315,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4050</v>
+        <v>3450</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2.51</v>
+        <v>-2.78</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>51.4</v>
+        <v>48.4</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -2343,16 +2342,16 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>154.35</v>
+        <v>133.46</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -2377,16 +2376,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2200</v>
+        <v>2650</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.05</v>
+        <v>3.46</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>51.4</v>
+        <v>51</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -2404,16 +2403,16 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>19.6</v>
+        <v>16.9</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>23.9</v>
+        <v>20.7</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>112.32</v>
+        <v>156.57</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -2438,16 +2437,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>24900</v>
+        <v>23550</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.29</v>
+        <v>-1.57</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>42.1</v>
+        <v>44.5</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -2465,16 +2464,16 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10.8</v>
+        <v>12.1</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>15.7</v>
+        <v>17.6</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>2300.81</v>
+        <v>1947.12</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -2499,25 +2498,25 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>22500</v>
+        <v>18100</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-2.1</v>
+        <v>-2.8</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>72.8</v>
+        <v>42</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>SELL</t>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2526,16 +2525,16 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>20.2</v>
+        <v>22.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>1364.29</v>
+        <v>980.72</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -2560,16 +2559,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10500</v>
+        <v>10100</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-2.38</v>
+        <v>-1.01</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>53.2</v>
+        <v>59.5</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -2587,16 +2586,16 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>21.2</v>
+        <v>19.9</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>20.1</v>
+        <v>18.9</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>495.99</v>
+        <v>508.67</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2621,16 +2620,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6400</v>
+        <v>7400</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.41</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.1</v>
+        <v>57.5</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -2648,16 +2647,16 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>292.8</v>
+        <v>340.34</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2682,16 +2681,16 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1850</v>
+        <v>1750</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.9</v>
+        <v>0.21</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>56</v>
+        <v>46.1</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -2709,16 +2708,16 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>28.7</v>
+        <v>26.5</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>20.5</v>
+        <v>18.9</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>64.54000000000001</v>
+        <v>65.97</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2743,16 +2742,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3050</v>
+        <v>2700</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-1.82</v>
+        <v>1.28</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>49.8</v>
+        <v>56.6</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -2770,16 +2769,16 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>116.37</v>
+        <v>102.59</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -2804,16 +2803,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>60700</v>
+        <v>63050</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-2.47</v>
+        <v>-2.53</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -2831,16 +2830,16 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>7954.23</v>
+        <v>8050.92</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2868,13 +2867,13 @@
         <v>1400</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.16</v>
+        <v>-1.83</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.01</v>
+        <v>-0.13</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>48.9</v>
+        <v>50.7</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -2892,16 +2891,16 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>176.66</v>
+        <v>178.55</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2926,16 +2925,16 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>9250</v>
+        <v>7350</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.3</v>
+        <v>-0.76</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>44.2</v>
+        <v>50.1</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -2953,16 +2952,16 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>624.37</v>
+        <v>506.39</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
@@ -2987,16 +2986,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6650</v>
+        <v>5850</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-2.1</v>
+        <v>2.71</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -3008,22 +3007,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>14.2</v>
+        <v>16.3</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>14.2</v>
+        <v>16.3</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>468.23</v>
+        <v>358.96</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -3048,16 +3047,16 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9900</v>
+        <v>7950</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-3</v>
+        <v>-1.4</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>39</v>
+        <v>52.2</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -3075,16 +3074,16 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>16.3</v>
+        <v>15.2</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>16.3</v>
+        <v>15.2</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>607.42</v>
+        <v>522.42</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -3109,16 +3108,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4500</v>
+        <v>5200</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.18</v>
+        <v>-2.02</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>57.3</v>
+        <v>51.5</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -3130,22 +3129,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>307.72</v>
+        <v>330.99</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
@@ -3170,16 +3169,16 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1150</v>
+        <v>1250</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.72</v>
+        <v>-1.4</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -3191,22 +3190,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>16.4</v>
+        <v>13.6</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>16.4</v>
+        <v>13.6</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>70.28</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
@@ -3234,13 +3233,13 @@
         <v>13950</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-2.12</v>
+        <v>-2.09</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>-0.02</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>45.1</v>
+        <v>36.5</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -3258,16 +3257,16 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1874.76</v>
+        <v>1910.43</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
@@ -3360,25 +3359,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9502</v>
+        <v>9344</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9636.719999999999</v>
+        <v>9729.57</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9688.370000000001</v>
+        <v>9728.65</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>196217.22</v>
+        <v>195902.54</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>50.7</v>
+        <v>45.2</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>9300</v>
+        <v>9200</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>9900</v>
+        <v>10300</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -3398,22 +3397,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5009</v>
+        <v>4842</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4886.65</v>
+        <v>4869.03</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4817.76</v>
+        <v>4804.26</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>96271.27</v>
+        <v>96017.41</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>62.9</v>
+        <v>45.1</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>5100</v>
@@ -3436,19 +3435,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3139</v>
+        <v>3238</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3122.61</v>
+        <v>3116.31</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3136.1</v>
+        <v>3118.38</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>62205.43</v>
+        <v>61876</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>54</v>
+        <v>42.6</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>2900</v>
@@ -3474,25 +3473,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5535</v>
+        <v>5887</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5773.92</v>
+        <v>5862.62</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5824.45</v>
+        <v>5798.96</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>115501.09</v>
+        <v>117155.62</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>58.8</v>
+        <v>55</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -3512,25 +3511,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3544</v>
+        <v>3471</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3578.3</v>
+        <v>3553.49</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3561.78</v>
+        <v>3614.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>71917.49000000001</v>
+        <v>72172.89</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>50.8</v>
+        <v>32.6</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>3400</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -3550,25 +3549,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2410</v>
+        <v>2339</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2375</v>
+        <v>2416.15</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2401.72</v>
+        <v>2418.95</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>47964.47</v>
+        <v>48372.74</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>45.2</v>
+        <v>48.8</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>2200</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -3588,25 +3587,25 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>26721</v>
+        <v>28183</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>27398.7</v>
+        <v>27274.9</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27083.29</v>
+        <v>27041.69</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>540652.37</v>
+        <v>538453.11</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>49.9</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>26200</v>
+        <v>25600</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>28900</v>
+        <v>28700</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -3626,25 +3625,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>21654</v>
+        <v>21258</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>20934.92</v>
+        <v>21179.4</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20908.17</v>
+        <v>20981.86</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>419012.3</v>
+        <v>421003.05</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>56.4</v>
+        <v>47.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>19600</v>
+        <v>20400</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>22100</v>
+        <v>22000</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -3664,25 +3663,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9984</v>
+        <v>10643</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10242.06</v>
+        <v>10301.18</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10251.84</v>
+        <v>10288.69</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>204174.09</v>
+        <v>203486.34</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>49.9</v>
+        <v>49.3</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>9800</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10800</v>
+        <v>10900</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -3702,25 +3701,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6945</v>
+        <v>6483</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6881.51</v>
+        <v>6803.16</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6889.87</v>
+        <v>6836.55</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>136708.52</v>
+        <v>136600.65</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>37.5</v>
+        <v>54.1</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>6400</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>7300</v>
+        <v>7200</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -3740,25 +3739,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1664</v>
+        <v>1694</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1675.34</v>
+        <v>1723.86</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1691.92</v>
+        <v>1702.89</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>33998.63</v>
+        <v>34213.04</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>51.8</v>
+        <v>42.8</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1600</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
@@ -3778,25 +3777,25 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3184</v>
+        <v>3010</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3089.56</v>
+        <v>3029.82</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3110.91</v>
+        <v>3060.75</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>62475.94</v>
+        <v>61549.85</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>34.2</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>2900</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>3300</v>
+        <v>3100</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
@@ -3816,25 +3815,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>55538</v>
+        <v>58332</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>57443.11</v>
+        <v>56517.72</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>57697.04</v>
+        <v>57199.37</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1164637.21</v>
+        <v>1154527.79</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>52.6</v>
+        <v>33.3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>54400</v>
+        <v>54700</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>59700</v>
+        <v>59500</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -3854,19 +3853,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1379</v>
+        <v>1365</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1355.55</v>
+        <v>1358.16</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1348.33</v>
+        <v>1374.68</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>26853.45</v>
+        <v>27210.65</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>46.1</v>
+        <v>64.2</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1300</v>
@@ -3892,25 +3891,25 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8387</v>
+        <v>8794</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8455.870000000001</v>
+        <v>8760.07</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8493.92</v>
+        <v>8638.49</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>170030.41</v>
+        <v>171793.03</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>65.7</v>
+        <v>57.3</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8000</v>
+        <v>8400</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -3930,34 +3929,34 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>6850</v>
+        <v>6771</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>6863.69</v>
+        <v>6758.5</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6861.77</v>
+        <v>6713.39</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>136481.7</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>71</v>
+        <v>133853.16</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>45.8</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>6400</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3968,25 +3967,25 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>8795</v>
+        <v>9290</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9008.26</v>
+        <v>9312.639999999999</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9016.85</v>
+        <v>9241.879999999999</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>183261.42</v>
+        <v>185547.29</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>63.8</v>
+        <v>46.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8600</v>
+        <v>8900</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>9500</v>
+        <v>9800</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -4006,25 +4005,25 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4881</v>
+        <v>4930</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4820.16</v>
+        <v>4746.26</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4776.45</v>
+        <v>4760.8</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>95724.52</v>
+        <v>95409.89999999999</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>51.7</v>
+        <v>48.2</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -4044,22 +4043,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1232</v>
+        <v>1167</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1221.39</v>
+        <v>1189.65</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1209.44</v>
+        <v>1197.28</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>23914.12</v>
+        <v>23936.1</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>39.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1300</v>
@@ -4082,22 +4081,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>13701</v>
+        <v>13995</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>14171.15</v>
+        <v>14282.97</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14194.21</v>
+        <v>14301.48</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>285668.33</v>
+        <v>287444.8</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>50.1</v>
+        <v>48.1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>13400</v>
+        <v>13500</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>15200</v>
@@ -4232,32 +4231,32 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9981</v>
+        <v>9950</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>767.5700000000001</v>
+        <v>781.3200000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6140.56</v>
+        <v>6250.59</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>16.3</v>
+        <v>15.9</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -4288,32 +4287,32 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4627</v>
+        <v>4564</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>377.06</v>
+        <v>375.96</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3016.46</v>
+        <v>3007.68</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.87</v>
+        <v>1.35</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -4344,32 +4343,32 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3169</v>
+        <v>3198</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>248.72</v>
+        <v>221.15</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1392.82</v>
+        <v>1238.44</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12.7</v>
+        <v>14.5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>15.5</v>
+        <v>17.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -4400,32 +4399,32 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5883</v>
+        <v>5547</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>537.8200000000001</v>
+        <v>548.1799999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2987.89</v>
+        <v>3045.44</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>15.3</v>
+        <v>14.2</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -4456,32 +4455,32 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3620</v>
+        <v>3662</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>149.7</v>
+        <v>135.34</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>935.62</v>
+        <v>845.87</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>24.2</v>
+        <v>27.1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>17.4</v>
+        <v>19.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.6</v>
+        <v>0.34</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -4512,32 +4511,32 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2344</v>
+        <v>2499</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>123.06</v>
+        <v>144.01</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>738.35</v>
+        <v>864.04</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>19</v>
+        <v>17.4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>23.3</v>
+        <v>21.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -4568,32 +4567,32 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27649</v>
+        <v>26283</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2375.32</v>
+        <v>2630.53</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>16330.32</v>
+        <v>18084.87</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>16.9</v>
+        <v>14.5</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.21</v>
+        <v>0.47</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -4624,13 +4623,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21022</v>
+        <v>20527</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1171.92</v>
+        <v>1144.08</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7031.51</v>
+        <v>6864.47</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>17.9</v>
@@ -4642,14 +4641,14 @@
         <v>21.9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -4680,32 +4679,32 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10016</v>
+        <v>10032</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>553.49</v>
+        <v>459.57</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3162.79</v>
+        <v>2626.14</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>18.1</v>
+        <v>21.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>17.2</v>
+        <v>20.7</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -4736,32 +4735,32 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6963</v>
+        <v>6924</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>320.92</v>
+        <v>373.55</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1833.84</v>
+        <v>2134.54</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>21.7</v>
+        <v>18.5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>20.6</v>
+        <v>17.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -4792,32 +4791,32 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1773</v>
+        <v>1700</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>59.58</v>
+        <v>60.57</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>370.69</v>
+        <v>376.88</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>29.8</v>
+        <v>28.1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>21.3</v>
+        <v>20.1</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -4848,32 +4847,32 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2987</v>
+        <v>3050</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>100.26</v>
+        <v>118.98</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>623.8099999999999</v>
+        <v>740.3</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>29.8</v>
+        <v>25.6</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>21.3</v>
+        <v>18.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -4904,32 +4903,32 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>57440</v>
+        <v>57177</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7627.9</v>
+        <v>7464.81</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>50852.68</v>
+        <v>49765.42</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2.44</v>
+        <v>1.91</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -4960,32 +4959,32 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1348</v>
+        <v>1372</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>158.19</v>
+        <v>168.27</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1054.6</v>
+        <v>1121.78</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5016,28 +5015,28 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8296</v>
+        <v>8238</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>611.67</v>
+        <v>543.53</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>4587.55</v>
+        <v>4076.5</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.46</v>
+        <v>0.2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -5049,9 +5048,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5072,32 +5071,32 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>7022</v>
+        <v>6973</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>497.3</v>
+        <v>497.94</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3729.74</v>
+        <v>3734.53</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -5128,32 +5127,32 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>8758</v>
+        <v>8970</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>545.29</v>
+        <v>548.83</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>4089.66</v>
+        <v>4116.22</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.58</v>
+        <v>0.41</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -5184,32 +5183,32 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4668</v>
+        <v>4908</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>341.41</v>
+        <v>335.63</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2560.56</v>
+        <v>2517.19</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -5240,28 +5239,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1159</v>
+        <v>1236</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>83.27</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>624.5</v>
+        <v>564.29</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>13.9</v>
+        <v>16.4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>13.9</v>
+        <v>16.4</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -5273,9 +5272,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5296,32 +5295,32 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14646</v>
+        <v>14185</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1851.98</v>
+        <v>1853.69</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>12346.51</v>
+        <v>12357.97</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -5362,7 +5361,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
@@ -5419,7 +5418,7 @@
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
@@ -5465,7 +5464,7 @@
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
@@ -5511,7 +5510,7 @@
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
@@ -5557,7 +5556,7 @@
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
@@ -5603,7 +5602,7 @@
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
@@ -5649,7 +5648,7 @@
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Sampoerna</t>
         </is>
@@ -5695,7 +5694,7 @@
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
@@ -5741,7 +5740,7 @@
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Telkom</t>
         </is>
@@ -5787,7 +5786,7 @@
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
@@ -5833,7 +5832,7 @@
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Indocement</t>
         </is>
@@ -5892,21 +5891,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>📊 DASHBOARD SAHAM INDONESIA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Last Update: 2026-06-29 08:05</t>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Last Update: 2026-06-29 20:45</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>IHSG Level</t>
         </is>
@@ -5918,7 +5917,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>IHSG Change</t>
         </is>
@@ -5930,7 +5929,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Top Sector</t>
         </is>
@@ -5942,7 +5941,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Worst Sector</t>
         </is>
@@ -5954,69 +5953,69 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr"/>
+      <c r="A8" s="11" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>HOLD Signals</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr"/>
+      <c r="A12" s="11" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Best Buy Today</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>ANTM.JK, KLBF.JK, INTP.JK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>UNVR.JK, HMSP.JK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -557,27 +557,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5761.95</v>
+        <v>5762.79</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>-38.05</v>
+        <v>-37.21</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.65</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5791.37</v>
+        <v>5772.91</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5732.61</v>
+        <v>5743.04</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>653M</t>
+          <t>655M</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -589,187 +589,187 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5790.94</v>
+        <v>5813.14</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>-21.78</v>
+        <v>31.52</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.38</v>
+        <v>0.54</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5801.53</v>
+        <v>5817.89</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5774.2</v>
+        <v>5801.64</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>611M</t>
+          <t>758M</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5815.13</v>
+        <v>5786.21</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>31.78</v>
+        <v>-28.18</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.55</v>
+        <v>-0.49</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5822.99</v>
+        <v>5800.27</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5812.17</v>
+        <v>5774.11</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>769M</t>
+          <t>664M</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5814.43</v>
+        <v>5857.33</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>16.02</v>
+        <v>36.17</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.28</v>
+        <v>0.62</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5823.15</v>
+        <v>5867.88</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5806.88</v>
+        <v>5852.36</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>709M</t>
+          <t>567M</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5900.62</v>
+        <v>5765.72</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>59.68</v>
+        <v>-31.11</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1.01</v>
+        <v>-0.54</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5908.27</v>
+        <v>5768.04</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5875.34</v>
+        <v>5757.31</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>591M</t>
+          <t>783M</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5750.1</v>
+        <v>5725.88</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-47.75</v>
+        <v>-3.19</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.06</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5756.66</v>
+        <v>5734.77</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5749.6</v>
+        <v>5716.12</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>776M</t>
+          <t>777M</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>5787.06</v>
+        <v>5778.36</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-39.87</v>
+        <v>-32.83</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.57</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5809.4</v>
+        <v>5796.43</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5763.19</v>
+        <v>5765.67</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>510M</t>
+          <t>770M</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -781,91 +781,91 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5814.63</v>
+        <v>5867.86</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>18.65</v>
+        <v>47.89</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.32</v>
+        <v>0.82</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5818.66</v>
+        <v>5876.94</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5803.71</v>
+        <v>5845.81</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>720M</t>
+          <t>769M</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5786.19</v>
+        <v>5856.67</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-35.54</v>
+        <v>29.73</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.61</v>
+        <v>0.51</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5796.48</v>
+        <v>5863.76</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5781.92</v>
+        <v>5826.86</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>655M</t>
+          <t>576M</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5746.91</v>
+        <v>5819.64</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-2.39</v>
+        <v>17.81</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.31</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5775.04</v>
+        <v>5828.83</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5727.17</v>
+        <v>5792.91</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>630M</t>
+          <t>762M</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -877,59 +877,59 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5797.99</v>
+        <v>5779.43</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-16.25</v>
+        <v>-21.56</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.37</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5827.42</v>
+        <v>5793.82</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5790.86</v>
+        <v>5772.64</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>737M</t>
+          <t>663M</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5821.76</v>
+        <v>5890.75</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>31.76</v>
+        <v>39.04</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5830.74</v>
+        <v>5896.94</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5795.66</v>
+        <v>5861.17</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>750M</t>
+          <t>527M</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -941,59 +941,59 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5781.77</v>
+        <v>5835.65</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-37.12</v>
+        <v>-7.35</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.13</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5811.46</v>
+        <v>5860.55</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>5778.54</v>
+        <v>5828.47</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>603M</t>
+          <t>628M</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5901.12</v>
+        <v>5866.56</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>41.53</v>
+        <v>44.71</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5930.95</v>
+        <v>5870.74</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5895.95</v>
+        <v>5840.72</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>653M</t>
+          <t>789M</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1005,123 +1005,123 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5905.66</v>
+        <v>5807.06</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>49.64</v>
+        <v>-34.52</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.84</v>
+        <v>-0.59</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5916.79</v>
+        <v>5822.03</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5900.69</v>
+        <v>5783.31</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>568M</t>
+          <t>733M</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5859.47</v>
+        <v>5828.3</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>27.6</v>
+        <v>-22.97</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.47</v>
+        <v>-0.39</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5879.83</v>
+        <v>5854.23</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5858.5</v>
+        <v>5822.23</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>678M</t>
+          <t>560M</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5775.18</v>
+        <v>5782.27</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4.58</v>
+        <v>-45.14</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.08</v>
+        <v>-0.78</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>5791.33</v>
+        <v>5785.55</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5763.23</v>
+        <v>5776.18</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>640M</t>
+          <t>751M</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5909.38</v>
+        <v>5870.12</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>-42.36</v>
+        <v>-23.85</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.41</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5916.12</v>
+        <v>5877.21</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5902.78</v>
+        <v>5849.77</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>512M</t>
+          <t>530M</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1133,27 +1133,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5796.26</v>
+        <v>5900.2</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.82</v>
+        <v>14.31</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5798</v>
+        <v>5907.72</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5790.59</v>
+        <v>5879.43</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>557M</t>
+          <t>668M</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1165,27 +1165,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5890.24</v>
+        <v>5805.86</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-1.57</v>
+        <v>14.96</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.26</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5894.9</v>
+        <v>5816.68</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5879.2</v>
+        <v>5795.09</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>604M</t>
+          <t>645M</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1197,59 +1197,59 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5877.4</v>
+        <v>5862.11</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-10.9</v>
+        <v>42.76</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-0.19</v>
+        <v>0.73</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>5906.72</v>
+        <v>5886.74</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5872.68</v>
+        <v>5841.29</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>671M</t>
+          <t>594M</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5927.77</v>
+        <v>5988.02</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>14.17</v>
+        <v>-11.31</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.24</v>
+        <v>-0.19</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5944.98</v>
+        <v>6000.13</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5911.68</v>
+        <v>5963.95</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>655M</t>
+          <t>543M</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1261,91 +1261,91 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5803.06</v>
+        <v>5852.96</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-42.03</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-0.72</v>
+        <v>0.15</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5827.53</v>
+        <v>5861.58</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>5793.62</v>
+        <v>5851.71</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>797M</t>
+          <t>509M</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5695.65</v>
+        <v>6061.73</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-27.73</v>
+        <v>2.73</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-0.49</v>
+        <v>0.05</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5708.65</v>
+        <v>6070.89</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5688.61</v>
+        <v>6034.22</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>768M</t>
+          <t>792M</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>5651.65</v>
+        <v>6064.88</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-22.11</v>
+        <v>-26.99</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.44</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5670.82</v>
+        <v>6092.81</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5638.16</v>
+        <v>6062.8</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>616M</t>
+          <t>532M</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1357,155 +1357,155 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5947.53</v>
+        <v>5670.43</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>24.77</v>
+        <v>-28.14</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.42</v>
+        <v>-0.5</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5948.35</v>
+        <v>5679.16</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5942</v>
+        <v>5659.48</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>617M</t>
+          <t>728M</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>5852.35</v>
+        <v>5899.2</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-6.41</v>
+        <v>50.66</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-0.11</v>
+        <v>0.86</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>5860.96</v>
+        <v>5908.17</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5829.95</v>
+        <v>5888.32</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>598M</t>
+          <t>768M</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5843.33</v>
+        <v>5581.37</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>57.84</v>
+        <v>-3.51</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.99</v>
+        <v>-0.06</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5865.54</v>
+        <v>5587.39</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5823.44</v>
+        <v>5575.98</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>723M</t>
+          <t>637M</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5844.47</v>
+        <v>5782.11</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>53.31</v>
+        <v>-37.86</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.91</v>
+        <v>-0.65</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5846.14</v>
+        <v>5789.67</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5815.15</v>
+        <v>5759.54</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>793M</t>
+          <t>608M</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>6100.32</v>
+        <v>5877.79</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>48.45</v>
+        <v>49.4</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6124.38</v>
+        <v>5899.01</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>6072.73</v>
+        <v>5875.02</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>544M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1517,32 +1517,32 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5847.37</v>
+        <v>5807.75</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>27.94</v>
+        <v>-38.14</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.48</v>
+        <v>-0.66</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5867.61</v>
+        <v>5809.02</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>5820.2</v>
+        <v>5790.13</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>577M</t>
+          <t>585M</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -2071,16 +2071,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>11100</v>
+        <v>8400</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-2.83</v>
+        <v>-0.79</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>45.1</v>
+        <v>58.3</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -2098,16 +2098,16 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>10.9</v>
+        <v>12.9</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>13.6</v>
+        <v>16.1</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>1018.41</v>
+        <v>652.7</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -2132,16 +2132,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5500</v>
+        <v>4600</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-0.19</v>
+        <v>3.76</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0</v>
+        <v>0.08</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>41.5</v>
+        <v>51.3</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -2159,16 +2159,16 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>434.77</v>
+        <v>359.64</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -2193,16 +2193,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2950</v>
+        <v>2750</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.45</v>
+        <v>2.27</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>64.3</v>
+        <v>44.3</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -2220,16 +2220,16 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>14.7</v>
+        <v>13.8</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>200.17</v>
+        <v>199.47</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -2257,13 +2257,13 @@
         <v>5750</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.22</v>
+        <v>2.91</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>46.6</v>
+        <v>45.3</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>1.9</v>
@@ -2290,7 +2290,7 @@
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>552.86</v>
+        <v>550.0700000000001</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
@@ -2315,16 +2315,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3450</v>
+        <v>4100</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-2.78</v>
+        <v>-2.56</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>48.4</v>
+        <v>50.6</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -2342,16 +2342,16 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>25.8</v>
+        <v>22.7</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>18.6</v>
+        <v>16.3</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>133.46</v>
+        <v>180.56</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -2376,16 +2376,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2650</v>
+        <v>2300</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3.46</v>
+        <v>2.28</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>51</v>
+        <v>49.7</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -2403,16 +2403,16 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>16.9</v>
+        <v>17.6</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.7</v>
+        <v>21.5</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>156.57</v>
+        <v>130.78</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>23550</v>
+        <v>28100</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-1.57</v>
+        <v>1.01</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>44.5</v>
+        <v>63.4</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>1947.12</v>
+        <v>2335.02</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -2498,16 +2498,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>18100</v>
+        <v>20550</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-2.8</v>
+        <v>1.79</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>42</v>
+        <v>48.9</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>18.5</v>
+        <v>16.3</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>22.6</v>
+        <v>19.9</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>980.72</v>
+        <v>1260.62</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -2559,16 +2559,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10100</v>
+        <v>10750</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-1.01</v>
+        <v>0.5</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>59.5</v>
+        <v>49.6</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -2586,16 +2586,16 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>508.67</v>
+        <v>542.7</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7400</v>
+        <v>6450</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-1.41</v>
+        <v>-0.61</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>57.5</v>
+        <v>60.8</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -2647,16 +2647,16 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>21.7</v>
+        <v>20.3</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>20.7</v>
+        <v>19.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>340.34</v>
+        <v>316.99</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1750</v>
+        <v>1850</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.21</v>
+        <v>-1.16</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>46.1</v>
+        <v>42.3</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -2708,16 +2708,16 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>26.5</v>
+        <v>30.7</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>18.9</v>
+        <v>21.9</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>65.97</v>
+        <v>60.23</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2742,16 +2742,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2700</v>
+        <v>2950</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1.28</v>
+        <v>0.3</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>56.6</v>
+        <v>44.5</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -2769,16 +2769,16 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>26.3</v>
+        <v>29.2</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>102.59</v>
+        <v>101.12</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -2803,16 +2803,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>63050</v>
+        <v>60050</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-2.53</v>
+        <v>2.6</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>49.8</v>
+        <v>37.8</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -2830,16 +2830,16 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>8050.92</v>
+        <v>7443.13</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2864,16 +2864,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1400</v>
+        <v>1150</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-1.83</v>
+        <v>2.38</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.13</v>
+        <v>0.21</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>178.55</v>
+        <v>135.38</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2925,16 +2925,16 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7350</v>
+        <v>8000</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.76</v>
+        <v>1.89</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>50.1</v>
+        <v>33.3</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -2952,16 +2952,16 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>506.39</v>
+        <v>558.17</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
@@ -2986,16 +2986,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5850</v>
+        <v>7150</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2.71</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>47.5</v>
+        <v>35.5</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -3013,16 +3013,16 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>358.96</v>
+        <v>443.21</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -3047,16 +3047,16 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>7950</v>
+        <v>9900</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-1.4</v>
+        <v>3.28</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>52.2</v>
+        <v>54.2</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -3074,16 +3074,16 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>522.42</v>
+        <v>655.41</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -3108,16 +3108,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>5200</v>
+        <v>4200</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-2.02</v>
+        <v>-1.31</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>51.5</v>
+        <v>48.6</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -3129,22 +3129,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>15.7</v>
+        <v>14.8</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>330.99</v>
+        <v>283.04</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
@@ -3169,16 +3169,16 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-1.4</v>
+        <v>-0.89</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>46.4</v>
+        <v>42.7</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -3190,22 +3190,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>13.6</v>
+        <v>16.1</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>13.6</v>
+        <v>16.1</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>84.11</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>13950</v>
+        <v>14550</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-2.09</v>
+        <v>0.08</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>36.5</v>
+        <v>57.1</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1910.43</v>
+        <v>1925.12</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
@@ -3359,25 +3359,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9344</v>
+        <v>9760</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9729.57</v>
+        <v>9811.65</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9728.65</v>
+        <v>9759.940000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>195902.54</v>
+        <v>196210.6</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>45.2</v>
+        <v>56.1</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>9200</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10300</v>
+        <v>10400</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -3397,25 +3397,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4842</v>
+        <v>4947</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4869.03</v>
+        <v>4746.07</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4804.26</v>
+        <v>4837.02</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>96017.41</v>
+        <v>96676.16</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>45.1</v>
+        <v>42.5</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
@@ -3435,22 +3435,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3238</v>
+        <v>3095</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3116.31</v>
+        <v>3132.7</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3118.38</v>
+        <v>3149.16</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>61876</v>
+        <v>62644.25</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>42.6</v>
+        <v>46.7</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>3300</v>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5887</v>
+        <v>5908</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5862.62</v>
+        <v>5793.2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5798.96</v>
+        <v>5804.39</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>117155.62</v>
+        <v>115507.33</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>55</v>
+        <v>58.4</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5500</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -3511,22 +3511,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3471</v>
+        <v>3747</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3553.49</v>
+        <v>3656.12</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3614.8</v>
+        <v>3649.89</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>72172.89</v>
+        <v>73244.91</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>32.6</v>
+        <v>50.9</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>3800</v>
@@ -3549,25 +3549,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2339</v>
+        <v>2331</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2416.15</v>
+        <v>2405.37</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2418.95</v>
+        <v>2389.65</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>48372.74</v>
+        <v>47770.36</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>48.8</v>
+        <v>38.5</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -3587,25 +3587,25 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>28183</v>
+        <v>27304</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>27274.9</v>
+        <v>27307.4</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27041.69</v>
+        <v>26758.11</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>538453.11</v>
+        <v>536330.55</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>54.3</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>25600</v>
+        <v>25400</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>28700</v>
+        <v>28600</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -3625,25 +3625,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>21258</v>
+        <v>20040</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>21179.4</v>
+        <v>20347.67</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20981.86</v>
+        <v>20512.86</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>421003.05</v>
+        <v>415707.86</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>47.8</v>
+        <v>39.6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>20400</v>
+        <v>19600</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -3663,25 +3663,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10643</v>
+        <v>10525</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10301.18</v>
+        <v>10219.31</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10288.69</v>
+        <v>10099.77</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>203486.34</v>
+        <v>202879.64</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>49.3</v>
+        <v>48.5</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9800</v>
+        <v>9600</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10900</v>
+        <v>10800</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -3701,25 +3701,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6483</v>
+        <v>7124</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6803.16</v>
+        <v>6885.27</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6836.55</v>
+        <v>6845.28</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>136600.65</v>
+        <v>136995.34</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>54.1</v>
+        <v>51.8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -3739,19 +3739,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1694</v>
+        <v>1707</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1723.86</v>
+        <v>1704.4</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1702.89</v>
+        <v>1716.28</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>34213.04</v>
+        <v>34170.66</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>42.8</v>
+        <v>43.8</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1600</v>
@@ -3780,22 +3780,22 @@
         <v>3010</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3029.82</v>
+        <v>3104.53</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3060.75</v>
+        <v>3078.87</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>61549.85</v>
+        <v>61163.37</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>44</v>
+        <v>54.5</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>2900</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
@@ -3815,25 +3815,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>58332</v>
+        <v>59651</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>56517.72</v>
+        <v>58150.76</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>57199.37</v>
+        <v>58503.94</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1154527.79</v>
+        <v>1164577</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>33.3</v>
+        <v>57.8</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>54700</v>
+        <v>54300</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>59500</v>
+        <v>61700</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -3853,19 +3853,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1358.16</v>
+        <v>1358.21</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1374.68</v>
+        <v>1359.09</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>27210.65</v>
+        <v>27141.23</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>64.2</v>
+        <v>49.8</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1300</v>
@@ -3891,25 +3891,25 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8794</v>
+        <v>8864</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8760.07</v>
+        <v>8628.309999999999</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8638.49</v>
+        <v>8590.93</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>171793.03</v>
+        <v>169948.39</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>57.3</v>
+        <v>49.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8400</v>
+        <v>8100</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9100</v>
+        <v>9000</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -3929,19 +3929,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>6771</v>
+        <v>6776</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>6758.5</v>
+        <v>6840.87</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6713.39</v>
+        <v>6768.82</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>133853.16</v>
+        <v>136142.52</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>45.8</v>
+        <v>61.6</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>6400</v>
@@ -3967,22 +3967,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>9290</v>
+        <v>8933</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9312.639999999999</v>
+        <v>9275.34</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9241.879999999999</v>
+        <v>9184.1</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>185547.29</v>
+        <v>183204.24</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46.7</v>
+        <v>39.3</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8900</v>
+        <v>8800</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>9800</v>
@@ -4005,19 +4005,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4930</v>
+        <v>4834</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4746.26</v>
+        <v>4746.72</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4760.8</v>
+        <v>4798</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>95409.89999999999</v>
+        <v>95666.16</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>48.2</v>
+        <v>51</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>4500</v>
@@ -4043,22 +4043,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1167</v>
+        <v>1227</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1189.65</v>
+        <v>1211.26</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1197.28</v>
+        <v>1201.15</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>23936.1</v>
+        <v>24033.48</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>39.7</v>
+        <v>61.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1300</v>
@@ -4081,25 +4081,25 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>13995</v>
+        <v>14164</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>14282.97</v>
+        <v>14241.54</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14301.48</v>
+        <v>14194.25</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>287444.8</v>
+        <v>281404.43</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>48.1</v>
+        <v>51.3</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>13500</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>15200</v>
+        <v>15000</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -4231,32 +4231,32 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9950</v>
+        <v>10188</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>781.3200000000001</v>
+        <v>795.45</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6250.59</v>
+        <v>6363.63</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.89</v>
+        <v>1.02</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4564</v>
+        <v>4798</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>375.96</v>
+        <v>396.68</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3007.68</v>
+        <v>3173.45</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>12.1</v>
@@ -4302,17 +4302,17 @@
         <v>1.5</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.35</v>
+        <v>0.5</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -4343,32 +4343,32 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3198</v>
+        <v>2979</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>221.15</v>
+        <v>208.36</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1238.44</v>
+        <v>1166.83</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -4399,32 +4399,32 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5547</v>
+        <v>5690</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>548.1799999999999</v>
+        <v>551.16</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3045.44</v>
+        <v>3062</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -4455,32 +4455,32 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3662</v>
+        <v>3757</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>135.34</v>
+        <v>150.51</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>845.87</v>
+        <v>940.71</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>27.1</v>
+        <v>25</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -4511,28 +4511,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2499</v>
+        <v>2318</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>144.01</v>
+        <v>117.46</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>864.04</v>
+        <v>704.78</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>17.4</v>
+        <v>19.7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>21.2</v>
+        <v>24.1</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.31</v>
+        <v>0.46</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -4567,32 +4567,32 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>26283</v>
+        <v>26975</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2630.53</v>
+        <v>2515.98</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>18084.87</v>
+        <v>17297.37</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -4623,28 +4623,28 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20527</v>
+        <v>21735</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1144.08</v>
+        <v>1284.53</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>6864.47</v>
+        <v>7707.17</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>17.9</v>
+        <v>16.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>21.9</v>
+        <v>20.7</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -4679,32 +4679,32 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10032</v>
+        <v>10249</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>459.57</v>
+        <v>468.4</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2626.14</v>
+        <v>2676.6</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.39</v>
+        <v>0.59</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -4735,32 +4735,32 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6924</v>
+        <v>6995</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>373.55</v>
+        <v>351.13</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2134.54</v>
+        <v>2006.44</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>18.5</v>
+        <v>19.9</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>17.6</v>
+        <v>18.9</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -4791,32 +4791,32 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1700</v>
+        <v>1705</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>60.57</v>
+        <v>62.44</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>376.88</v>
+        <v>388.55</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28.1</v>
+        <v>27.3</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.57</v>
+        <v>0.22</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -4847,32 +4847,32 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3050</v>
+        <v>3245</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>118.98</v>
+        <v>112.24</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>740.3</v>
+        <v>698.4</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>25.6</v>
+        <v>28.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>18.3</v>
+        <v>20.6</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -4903,32 +4903,32 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>57177</v>
+        <v>58252</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7464.81</v>
+        <v>7077.9</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>49765.42</v>
+        <v>47186.01</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -4959,32 +4959,32 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1372</v>
+        <v>1332</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>168.27</v>
+        <v>184.88</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1121.78</v>
+        <v>1232.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5015,32 +5015,32 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8238</v>
+        <v>8590</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>543.53</v>
+        <v>578.74</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>4076.5</v>
+        <v>4340.52</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -5048,9 +5048,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -5071,32 +5071,32 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6973</v>
+        <v>6580</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>497.94</v>
+        <v>436.8</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3734.53</v>
+        <v>3275.99</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>14</v>
+        <v>15.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>14</v>
+        <v>15.1</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -5104,9 +5104,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5127,32 +5127,32 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>8970</v>
+        <v>9632</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>548.83</v>
+        <v>668.52</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>4116.22</v>
+        <v>5013.88</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>16.3</v>
+        <v>14.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>16.3</v>
+        <v>14.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -5160,9 +5160,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -5183,32 +5183,32 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4908</v>
+        <v>4833</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>335.63</v>
+        <v>343.13</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2517.19</v>
+        <v>2573.48</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -5239,32 +5239,32 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>75.23999999999999</v>
+        <v>88.02</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>564.29</v>
+        <v>660.16</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>16.4</v>
+        <v>14.1</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>16.4</v>
+        <v>14.1</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.58</v>
+        <v>0.31</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -5272,9 +5272,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -5295,32 +5295,32 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14185</v>
+        <v>14073</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1853.69</v>
+        <v>1625.98</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>12357.97</v>
+        <v>10839.84</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -5900,7 +5900,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Last Update: 2026-06-29 20:45</t>
+          <t>Last Update: 2026-06-30 01:45</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -561,28 +561,28 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5762.79</v>
+        <v>5784.41</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>-37.21</v>
+        <v>-15.59</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.27</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5772.91</v>
+        <v>5793.15</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5743.04</v>
+        <v>5774.1</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>655M</t>
+          <t>762M</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -593,28 +593,28 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5813.14</v>
+        <v>5819.97</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>31.52</v>
+        <v>-9.59</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.54</v>
+        <v>-0.16</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5817.89</v>
+        <v>5830.47</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5801.64</v>
+        <v>5804.95</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>758M</t>
+          <t>715M</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -625,23 +625,23 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5786.21</v>
+        <v>5816.25</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-28.18</v>
+        <v>-27.63</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5800.27</v>
+        <v>5823.8</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5774.11</v>
+        <v>5804.62</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>664M</t>
+          <t>701M</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -657,28 +657,28 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5857.33</v>
+        <v>5810.91</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>36.17</v>
+        <v>-14.75</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.62</v>
+        <v>-0.25</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5867.88</v>
+        <v>5822.25</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5852.36</v>
+        <v>5792.66</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>567M</t>
+          <t>753M</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -689,23 +689,23 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5765.72</v>
+        <v>5801.06</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-31.11</v>
+        <v>-36.45</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.63</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5768.04</v>
+        <v>5826.05</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5757.31</v>
+        <v>5792.48</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>783M</t>
+          <t>719M</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -721,28 +721,28 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5725.88</v>
+        <v>5876.96</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-3.19</v>
+        <v>50.69</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.86</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5734.77</v>
+        <v>5877.3</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5716.12</v>
+        <v>5868.66</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>777M</t>
+          <t>638M</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -753,28 +753,28 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>5778.36</v>
+        <v>5884.23</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-32.83</v>
+        <v>43.83</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.57</v>
+        <v>0.74</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5796.43</v>
+        <v>5894.93</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5765.67</v>
+        <v>5876.16</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>770M</t>
+          <t>730M</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5867.86</v>
+        <v>5841.09</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>47.89</v>
+        <v>-37.48</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.82</v>
+        <v>-0.64</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5876.94</v>
+        <v>5856.17</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5845.81</v>
+        <v>5834.76</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>769M</t>
+          <t>721M</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -817,23 +817,23 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5856.67</v>
+        <v>5920.43</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>29.73</v>
+        <v>49.13</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.51</v>
+        <v>0.83</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5863.76</v>
+        <v>5929.76</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5826.86</v>
+        <v>5902.07</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>576M</t>
+          <t>680M</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -849,23 +849,23 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5819.64</v>
+        <v>5831.74</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>17.81</v>
+        <v>-1.48</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.31</v>
+        <v>-0.03</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5828.83</v>
+        <v>5842.64</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5792.91</v>
+        <v>5831.28</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>762M</t>
+          <t>733M</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -881,28 +881,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5779.43</v>
+        <v>5758.97</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-21.56</v>
+        <v>-4.92</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.09</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5793.82</v>
+        <v>5764.98</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5772.64</v>
+        <v>5751.89</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>663M</t>
+          <t>526M</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -913,23 +913,23 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5890.75</v>
+        <v>5919.72</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>39.04</v>
+        <v>37.53</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5896.94</v>
+        <v>5935.98</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5861.17</v>
+        <v>5897.98</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>527M</t>
+          <t>663M</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -945,28 +945,28 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5835.65</v>
+        <v>5708.28</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-7.35</v>
+        <v>20.5</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-0.13</v>
+        <v>0.36</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5860.55</v>
+        <v>5717.21</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>5828.47</v>
+        <v>5689.69</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>628M</t>
+          <t>783M</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5866.56</v>
+        <v>5784.74</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>44.71</v>
+        <v>6.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.76</v>
+        <v>0.1</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5870.74</v>
+        <v>5810.96</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5840.72</v>
+        <v>5765.99</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>789M</t>
+          <t>570M</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1009,23 +1009,23 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5807.06</v>
+        <v>5766.47</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-34.52</v>
+        <v>-27.23</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.47</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5822.03</v>
+        <v>5776.94</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5783.31</v>
+        <v>5759.68</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>733M</t>
+          <t>600M</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1041,28 +1041,28 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5828.3</v>
+        <v>5965.99</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-22.97</v>
+        <v>-10.94</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.18</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5854.23</v>
+        <v>5987.28</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5822.23</v>
+        <v>5950.11</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>560M</t>
+          <t>572M</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1073,28 +1073,28 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5782.27</v>
+        <v>5895.01</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-45.14</v>
+        <v>10.51</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-0.78</v>
+        <v>0.18</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>5785.55</v>
+        <v>5898.88</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5776.18</v>
+        <v>5867.34</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>751M</t>
+          <t>575M</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1105,28 +1105,28 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5870.12</v>
+        <v>5995.35</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>-23.85</v>
+        <v>15.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>-0.41</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5877.21</v>
+        <v>6024.41</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5849.77</v>
+        <v>5982.2</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>530M</t>
+          <t>548M</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5900.2</v>
+        <v>5839.3</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>14.31</v>
+        <v>45.29</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.24</v>
+        <v>0.78</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5907.72</v>
+        <v>5851.91</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5879.43</v>
+        <v>5834.39</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>668M</t>
+          <t>511M</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1169,28 +1169,28 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5805.86</v>
+        <v>5883.96</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>14.96</v>
+        <v>-20.16</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5816.68</v>
+        <v>5889.42</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5795.09</v>
+        <v>5853.97</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>645M</t>
+          <t>641M</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1201,28 +1201,28 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5862.11</v>
+        <v>5784</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>42.76</v>
+        <v>-44.29</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.73</v>
+        <v>-0.77</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>5886.74</v>
+        <v>5811.27</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5841.29</v>
+        <v>5758.85</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>594M</t>
+          <t>768M</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1233,23 +1233,23 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5988.02</v>
+        <v>5696.76</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-11.31</v>
+        <v>-15.23</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.27</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6000.13</v>
+        <v>5703.78</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5963.95</v>
+        <v>5693.84</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>543M</t>
+          <t>702M</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1265,23 +1265,23 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5852.96</v>
+        <v>5904.57</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>12.03</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5861.58</v>
+        <v>5905.16</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>5851.71</v>
+        <v>5900.7</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>509M</t>
+          <t>716M</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1297,28 +1297,28 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>6061.73</v>
+        <v>5908.08</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2.73</v>
+        <v>55.69</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>6070.89</v>
+        <v>5913.25</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>6034.22</v>
+        <v>5884</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>792M</t>
+          <t>738M</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1329,28 +1329,28 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>6064.88</v>
+        <v>6047.69</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-26.99</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-0.44</v>
+        <v>0.15</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>6092.81</v>
+        <v>6053.75</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>6062.8</v>
+        <v>6018.2</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>532M</t>
+          <t>552M</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5670.43</v>
+        <v>6064.43</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-28.14</v>
+        <v>34.04</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5679.16</v>
+        <v>6075.82</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5659.48</v>
+        <v>6045.34</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>728M</t>
+          <t>586M</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
     </row>
@@ -1393,23 +1393,23 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>5899.2</v>
+        <v>5967.71</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>50.66</v>
+        <v>34.49</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.86</v>
+        <v>0.58</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>5908.17</v>
+        <v>5968.48</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5888.32</v>
+        <v>5951.95</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>768M</t>
+          <t>683M</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -1425,23 +1425,23 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5581.37</v>
+        <v>6065.21</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.51</v>
+        <v>-1.81</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5587.39</v>
+        <v>6075.02</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5575.98</v>
+        <v>6056.92</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>637M</t>
+          <t>685M</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1457,28 +1457,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5782.11</v>
+        <v>5932.5</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-37.86</v>
+        <v>7.83</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-0.65</v>
+        <v>0.13</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5789.67</v>
+        <v>5950.93</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5759.54</v>
+        <v>5916.1</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>608M</t>
+          <t>540M</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
     </row>
@@ -1489,28 +1489,28 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5877.79</v>
+        <v>5824.99</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>49.4</v>
+        <v>-25.58</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.84</v>
+        <v>-0.44</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5899.01</v>
+        <v>5832.01</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5875.02</v>
+        <v>5807.06</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>500M</t>
+          <t>502M</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
     </row>
@@ -1521,23 +1521,23 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5807.75</v>
+        <v>5819.07</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-38.14</v>
+        <v>-36.58</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.63</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5809.02</v>
+        <v>5846.19</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>5790.13</v>
+        <v>5792.47</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>585M</t>
+          <t>570M</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -2071,16 +2071,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>8400</v>
+        <v>11250</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.57</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>-0.01</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>58.3</v>
+        <v>44.4</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -2098,16 +2098,16 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>16.1</v>
+        <v>15.1</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>652.7</v>
+        <v>931.77</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -2132,16 +2132,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4600</v>
+        <v>5450</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>51.3</v>
+        <v>47.1</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -2159,16 +2159,16 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>12.8</v>
+        <v>11.4</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>16</v>
+        <v>14.2</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>359.64</v>
+        <v>478.6</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -2193,16 +2193,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2750</v>
+        <v>3450</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2.27</v>
+        <v>2.9</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0.08</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>44.3</v>
+        <v>51</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -2220,16 +2220,16 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>199.47</v>
+        <v>245.48</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -2254,16 +2254,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5750</v>
+        <v>5950</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0.05</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>45.3</v>
+        <v>47.7</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>550.0700000000001</v>
+        <v>609.12</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
@@ -2315,16 +2315,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4100</v>
+        <v>3350</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-2.56</v>
+        <v>3.08</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>50.6</v>
+        <v>57.1</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -2342,16 +2342,16 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>180.56</v>
+        <v>146.26</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -2376,16 +2376,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2300</v>
+        <v>2050</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2.28</v>
+        <v>1.28</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>49.7</v>
+        <v>46</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -2403,16 +2403,16 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>17.6</v>
+        <v>19.7</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>21.5</v>
+        <v>24.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>130.78</v>
+        <v>104.09</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>28100</v>
+        <v>27000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>63.4</v>
+        <v>46.1</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>17.5</v>
+        <v>15.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>2335.02</v>
+        <v>2601.45</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -2498,16 +2498,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20550</v>
+        <v>17950</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.79</v>
+        <v>0.86</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>16.3</v>
+        <v>17.7</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>19.9</v>
+        <v>21.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>1260.62</v>
+        <v>1013.67</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -2559,16 +2559,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10750</v>
+        <v>10850</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.5</v>
+        <v>-2.18</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>49.6</v>
+        <v>41.2</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -2586,16 +2586,16 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>18.8</v>
+        <v>17.8</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>542.7</v>
+        <v>578.05</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6450</v>
+        <v>7050</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.61</v>
+        <v>1.4</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>60.8</v>
+        <v>36.5</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -2647,16 +2647,16 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>20.3</v>
+        <v>19.7</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>19.3</v>
+        <v>18.7</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>316.99</v>
+        <v>358</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1850</v>
+        <v>1500</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-1.16</v>
+        <v>3.6</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.24</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>42.3</v>
+        <v>52.8</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -2708,16 +2708,16 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>30.7</v>
+        <v>25.4</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>21.9</v>
+        <v>18.1</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>60.23</v>
+        <v>59.06</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2742,16 +2742,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2950</v>
+        <v>3300</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>44.5</v>
+        <v>50.4</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -2769,16 +2769,16 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>29.2</v>
+        <v>29.8</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>101.12</v>
+        <v>110.92</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -2803,16 +2803,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>60050</v>
+        <v>57300</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2.6</v>
+        <v>0.67</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>37.8</v>
+        <v>43.1</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -2830,16 +2830,16 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>12.1</v>
+        <v>11.4</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>7443.13</v>
+        <v>7532.77</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2867,13 +2867,13 @@
         <v>1150</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2.38</v>
+        <v>-2.39</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.21</v>
+        <v>-0.21</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>50.4</v>
+        <v>64.2</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>135.38</v>
+        <v>132.29</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2925,16 +2925,16 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8000</v>
+        <v>7350</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.89</v>
+        <v>-0.54</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>33.3</v>
+        <v>58.9</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -2946,22 +2946,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>14.3</v>
+        <v>15.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>14.3</v>
+        <v>15.8</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>558.17</v>
+        <v>465.15</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
@@ -2986,16 +2986,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>7150</v>
+        <v>6350</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>3.24</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>35.5</v>
+        <v>58.2</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -3007,22 +3007,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>16.1</v>
+        <v>14.3</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>16.1</v>
+        <v>14.3</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>443.21</v>
+        <v>444.1</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -3047,16 +3047,16 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>3.28</v>
+        <v>2.58</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>54.2</v>
+        <v>41.8</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -3068,22 +3068,22 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>655.41</v>
+        <v>685.37</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -3111,13 +3111,13 @@
         <v>4200</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-1.31</v>
+        <v>1.01</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>48.6</v>
+        <v>51.2</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -3135,16 +3135,16 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>14.8</v>
+        <v>13.9</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>283.04</v>
+        <v>301.25</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
@@ -3172,13 +3172,13 @@
         <v>1350</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.49</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>42.7</v>
+        <v>45.1</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -3196,16 +3196,16 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>16.1</v>
+        <v>15.5</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>16.1</v>
+        <v>15.5</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>84.11</v>
+        <v>86.88</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14550</v>
+        <v>15150</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.08</v>
+        <v>1.05</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>57.1</v>
+        <v>48.4</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>1.1</v>
@@ -3266,7 +3266,7 @@
         <v>11.3</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1925.12</v>
+        <v>2014.6</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
@@ -3359,25 +3359,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9760</v>
+        <v>9944</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9811.65</v>
+        <v>9926.709999999999</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9759.940000000001</v>
+        <v>9985.43</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>196210.6</v>
+        <v>198032.68</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>56.1</v>
+        <v>48.1</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10400</v>
+        <v>10300</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4947</v>
+        <v>4673</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4746.07</v>
+        <v>4715.97</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4837.02</v>
+        <v>4758.03</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>96676.16</v>
+        <v>95766.41</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>42.5</v>
+        <v>49.7</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>5000</v>
@@ -3435,22 +3435,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3095</v>
+        <v>3237</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3132.7</v>
+        <v>3049.25</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3149.16</v>
+        <v>3064.35</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>62644.25</v>
+        <v>61850.36</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46.7</v>
+        <v>49.8</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>3300</v>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5908</v>
+        <v>5598</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5793.2</v>
+        <v>5683.06</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5804.39</v>
+        <v>5734.86</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>115507.33</v>
+        <v>115762.61</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>58.4</v>
+        <v>45.2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6100</v>
+        <v>5900</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -3511,22 +3511,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3747</v>
+        <v>3661</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3656.12</v>
+        <v>3686.97</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3649.89</v>
+        <v>3654.3</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>73244.91</v>
+        <v>72511.3</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>50.9</v>
+        <v>61.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>3800</v>
@@ -3549,25 +3549,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2331</v>
+        <v>2519</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2405.37</v>
+        <v>2418.2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2389.65</v>
+        <v>2394.43</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>47770.36</v>
+        <v>48222.85</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>38.5</v>
+        <v>51.8</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>2300</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -3587,25 +3587,25 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>27304</v>
+        <v>26735</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>27307.4</v>
+        <v>27367.42</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>26758.11</v>
+        <v>27112.44</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>536330.55</v>
+        <v>540360.04</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>54.3</v>
+        <v>59.7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>25400</v>
+        <v>26200</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>28600</v>
+        <v>28500</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -3625,25 +3625,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>20040</v>
+        <v>21374</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>20347.67</v>
+        <v>21016.99</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20512.86</v>
+        <v>21143.57</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>415707.86</v>
+        <v>420893.68</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>39.6</v>
+        <v>62.6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>19600</v>
+        <v>20200</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>21000</v>
+        <v>21800</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -3663,25 +3663,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10525</v>
+        <v>10334</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10219.31</v>
+        <v>10168.59</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10099.77</v>
+        <v>10146.01</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>202879.64</v>
+        <v>202768.38</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10800</v>
+        <v>10700</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -3701,22 +3701,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7124</v>
+        <v>6777</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6885.27</v>
+        <v>6876.72</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6845.28</v>
+        <v>6880.39</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>136995.34</v>
+        <v>135789.4</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>51.8</v>
+        <v>49.2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>7300</v>
@@ -3739,19 +3739,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1707</v>
+        <v>1774</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1704.4</v>
+        <v>1703.81</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1716.28</v>
+        <v>1705.17</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>34170.66</v>
+        <v>34403.87</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>43.8</v>
+        <v>54.2</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1600</v>
@@ -3777,22 +3777,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3010</v>
+        <v>3113</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3104.53</v>
+        <v>3126.24</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3078.87</v>
+        <v>3127.89</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>61163.37</v>
+        <v>61663.35</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>54.5</v>
+        <v>48.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>3300</v>
@@ -3815,25 +3815,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>59651</v>
+        <v>60662</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>58150.76</v>
+        <v>59979.24</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>58503.94</v>
+        <v>58474.14</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1164577</v>
+        <v>1161073.59</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>57.8</v>
+        <v>49.8</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>54300</v>
+        <v>57700</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>61700</v>
+        <v>61900</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -3853,19 +3853,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1370</v>
+        <v>1292</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1358.21</v>
+        <v>1335.56</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1359.09</v>
+        <v>1334.56</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>27141.23</v>
+        <v>27030.48</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>49.8</v>
+        <v>43.9</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1300</v>
@@ -3891,22 +3891,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8864</v>
+        <v>8513</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8628.309999999999</v>
+        <v>8483.32</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8590.93</v>
+        <v>8553.389999999999</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>169948.39</v>
+        <v>171626.61</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>49.6</v>
+        <v>52.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8100</v>
+        <v>8000</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>9000</v>
@@ -3929,19 +3929,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>6776</v>
+        <v>6613</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>6840.87</v>
+        <v>6732.86</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6768.82</v>
+        <v>6780.61</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>136142.52</v>
+        <v>136581.61</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>61.6</v>
+        <v>53.3</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>6400</v>
@@ -3967,25 +3967,25 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>8933</v>
+        <v>9490</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9275.34</v>
+        <v>9123.139999999999</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9184.1</v>
+        <v>9237.23</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>183204.24</v>
+        <v>183433.09</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>39.3</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8800</v>
+        <v>8700</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>9800</v>
+        <v>9700</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -4005,25 +4005,25 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4834</v>
+        <v>4953</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4746.72</v>
+        <v>4895.87</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4798</v>
+        <v>4816.94</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>95666.16</v>
+        <v>96465.87</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>51</v>
+        <v>55.6</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -4043,22 +4043,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1227</v>
+        <v>1145</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1211.26</v>
+        <v>1183.71</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1201.15</v>
+        <v>1182.76</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>24033.48</v>
+        <v>23811.69</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>61.7</v>
+        <v>55.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1300</v>
@@ -4081,25 +4081,25 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>14164</v>
+        <v>13988</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>14241.54</v>
+        <v>14040.46</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14194.25</v>
+        <v>14084.94</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>281404.43</v>
+        <v>281200.61</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>51.3</v>
+        <v>52.8</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>13500</v>
+        <v>13300</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -4231,32 +4231,32 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>10188</v>
+        <v>9523</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>795.45</v>
+        <v>738.87</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6363.63</v>
+        <v>5910.94</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -4287,32 +4287,32 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4798</v>
+        <v>4833</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>396.68</v>
+        <v>381.4</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3173.45</v>
+        <v>3051.21</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>15.1</v>
+        <v>15.8</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -4343,32 +4343,32 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2979</v>
+        <v>3044</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>208.36</v>
+        <v>225.13</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1166.83</v>
+        <v>1260.74</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>14.3</v>
+        <v>13.5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>17.4</v>
+        <v>16.4</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -4399,32 +4399,32 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5690</v>
+        <v>5773</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>551.16</v>
+        <v>639.23</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3062</v>
+        <v>3551.3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>14.5</v>
+        <v>12.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -4455,32 +4455,32 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3757</v>
+        <v>3718</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>150.51</v>
+        <v>143.38</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>940.71</v>
+        <v>896.15</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>25</v>
+        <v>25.9</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>18</v>
+        <v>18.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -4511,28 +4511,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2318</v>
+        <v>2431</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>117.46</v>
+        <v>149.96</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>704.78</v>
+        <v>899.73</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>19.7</v>
+        <v>16.2</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>24.1</v>
+        <v>19.8</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -4567,32 +4567,32 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>26975</v>
+        <v>28150</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2515.98</v>
+        <v>2350.55</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>17297.37</v>
+        <v>16160.05</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>15.6</v>
+        <v>17.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -4623,32 +4623,32 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21735</v>
+        <v>21407</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1284.53</v>
+        <v>1224.62</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7707.17</v>
+        <v>7347.72</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>16.9</v>
+        <v>17.5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.42</v>
+        <v>0.57</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -4679,28 +4679,28 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10249</v>
+        <v>10201</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>468.4</v>
+        <v>542.35</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2676.6</v>
+        <v>3099.16</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>21.9</v>
+        <v>18.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>20.8</v>
+        <v>17.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -4735,32 +4735,32 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6995</v>
+        <v>6537</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>351.13</v>
+        <v>325.57</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2006.44</v>
+        <v>1860.37</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -4791,32 +4791,32 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1705</v>
+        <v>1641</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>62.44</v>
+        <v>54.3</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>388.55</v>
+        <v>337.85</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>27.3</v>
+        <v>30.2</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>19.5</v>
+        <v>21.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -4847,32 +4847,32 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3245</v>
+        <v>3021</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>112.24</v>
+        <v>111.56</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>698.4</v>
+        <v>694.14</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>28.9</v>
+        <v>27.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>20.6</v>
+        <v>19.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -4903,32 +4903,32 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>58252</v>
+        <v>60816</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7077.9</v>
+        <v>7228.24</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>47186.01</v>
+        <v>48188.28</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -4959,32 +4959,32 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1332</v>
+        <v>1326</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>184.88</v>
+        <v>182.23</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1232.5</v>
+        <v>1214.87</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5015,32 +5015,32 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8590</v>
+        <v>8557</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>578.74</v>
+        <v>572.73</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>4340.52</v>
+        <v>4295.45</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -5071,28 +5071,28 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6580</v>
+        <v>6830</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>436.8</v>
+        <v>463.87</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3275.99</v>
+        <v>3479.04</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.48</v>
+        <v>0.21</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -5104,9 +5104,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -5127,28 +5127,28 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9632</v>
+        <v>9381</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>668.52</v>
+        <v>577.92</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5013.88</v>
+        <v>4334.42</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -5160,9 +5160,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5183,32 +5183,32 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4833</v>
+        <v>4732</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>343.13</v>
+        <v>343.26</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2573.48</v>
+        <v>2574.44</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -5239,32 +5239,32 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1244</v>
+        <v>1180</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>88.02</v>
+        <v>74.19</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>660.16</v>
+        <v>556.4400000000001</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14.1</v>
+        <v>15.9</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>14.1</v>
+        <v>15.9</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.31</v>
+        <v>0.55</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -5272,9 +5272,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5295,32 +5295,32 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14073</v>
+        <v>13980</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1625.98</v>
+        <v>1812.52</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>10839.84</v>
+        <v>12083.46</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>13</v>
+        <v>11.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.49</v>
+        <v>0.77</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>2.09</v>
+        <v>1.59</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -5900,7 +5900,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Last Update: 2026-06-30 01:45</t>
+          <t>Last Update: 2026-06-30 08:45</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -41,6 +41,9 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
@@ -50,9 +53,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="7">
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -123,17 +123,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -499,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -510,6 +511,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,996 +555,1156 @@
           <t>Sentimen</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5784.41</v>
+        <v>5800</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>-15.59</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5793.15</v>
+        <v>5800</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5774.1</v>
+        <v>5800</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>762M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5819.97</v>
+        <v>5800</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>-9.59</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5830.47</v>
+        <v>5800</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5804.95</v>
+        <v>5800</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>715M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5816.25</v>
+        <v>5800</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-27.63</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5823.8</v>
+        <v>5800</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5804.62</v>
+        <v>5800</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>701M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5810.91</v>
+        <v>5800</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-14.75</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5822.25</v>
+        <v>5800</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5792.66</v>
+        <v>5800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>753M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5801.06</v>
+        <v>5800</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-36.45</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5826.05</v>
+        <v>5800</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5792.48</v>
+        <v>5800</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>719M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5876.96</v>
+        <v>5800</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>50.69</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5877.3</v>
+        <v>5800</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5868.66</v>
+        <v>5800</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>638M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>5884.23</v>
+        <v>5800</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>43.83</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5894.93</v>
+        <v>5800</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5876.16</v>
+        <v>5800</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>730M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5841.09</v>
+        <v>5800</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-37.48</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5856.17</v>
+        <v>5800</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5834.76</v>
+        <v>5800</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>721M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5920.43</v>
+        <v>5800</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>49.13</v>
+        <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5929.76</v>
+        <v>5800</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5902.07</v>
+        <v>5800</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>680M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5831.74</v>
+        <v>5800</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.48</v>
+        <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5842.64</v>
+        <v>5800</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5831.28</v>
+        <v>5800</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>733M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5758.97</v>
+        <v>5800</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-4.92</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5764.98</v>
+        <v>5800</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5751.89</v>
+        <v>5800</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>526M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5919.72</v>
+        <v>5800</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>37.53</v>
+        <v>0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5935.98</v>
+        <v>5800</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5897.98</v>
+        <v>5800</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>663M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5708.28</v>
+        <v>5800</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5717.21</v>
+        <v>5800</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>5689.69</v>
+        <v>5800</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>783M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5784.74</v>
+        <v>5800</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5810.96</v>
+        <v>5800</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5765.99</v>
+        <v>5800</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>570M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5766.47</v>
+        <v>5800</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-27.23</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5776.94</v>
+        <v>5800</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5759.68</v>
+        <v>5800</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>600M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5965.99</v>
+        <v>5800</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-10.94</v>
+        <v>0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5987.28</v>
+        <v>5800</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5950.11</v>
+        <v>5800</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>572M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5895.01</v>
+        <v>5800</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>10.51</v>
+        <v>0</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>5898.88</v>
+        <v>5800</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5867.34</v>
+        <v>5800</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>575M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5995.35</v>
+        <v>5800</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>15.21</v>
+        <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>6024.41</v>
+        <v>5800</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5982.2</v>
+        <v>5800</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>548M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5839.3</v>
+        <v>5800</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>45.29</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5851.91</v>
+        <v>5800</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5834.39</v>
+        <v>5800</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>511M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5883.96</v>
+        <v>5800</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-20.16</v>
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5889.42</v>
+        <v>5800</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5853.97</v>
+        <v>5800</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>641M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5784</v>
+        <v>5800</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-44.29</v>
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>5811.27</v>
+        <v>5800</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5758.85</v>
+        <v>5800</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>768M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5696.76</v>
+        <v>5800</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-15.23</v>
+        <v>0</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5703.78</v>
+        <v>5800</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5693.84</v>
+        <v>5800</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>702M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5904.57</v>
+        <v>5800</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>12.03</v>
+        <v>0</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5905.16</v>
+        <v>5800</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>5900.7</v>
+        <v>5800</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>716M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5908.08</v>
+        <v>5800</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>55.69</v>
+        <v>0</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5913.25</v>
+        <v>5800</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5884</v>
+        <v>5800</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>738M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>6047.69</v>
+        <v>5800</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>9.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>6053.75</v>
+        <v>5800</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>6018.2</v>
+        <v>5800</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>552M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6064.43</v>
+        <v>5800</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>34.04</v>
+        <v>0</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6075.82</v>
+        <v>5800</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6045.34</v>
+        <v>5800</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>586M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>5967.71</v>
+        <v>5800</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>34.49</v>
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>5968.48</v>
+        <v>5800</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5951.95</v>
+        <v>5800</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>683M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6065.21</v>
+        <v>5800</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.81</v>
+        <v>0</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6075.02</v>
+        <v>5800</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6056.92</v>
+        <v>5800</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>685M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5932.5</v>
+        <v>5800</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>7.83</v>
+        <v>0</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5950.93</v>
+        <v>5800</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5916.1</v>
+        <v>5800</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>540M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5824.99</v>
+        <v>5800</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-25.58</v>
+        <v>0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5832.01</v>
+        <v>5800</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5807.06</v>
+        <v>5800</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>502M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5819.07</v>
+        <v>5800</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-36.58</v>
+        <v>0</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5846.19</v>
+        <v>5800</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>5792.47</v>
+        <v>5800</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>570M</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -1957,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2053,6 +2215,11 @@
           <t>Market Cap</t>
         </is>
       </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -2071,47 +2238,52 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>11250</v>
+        <v>9800</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.57</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="K2" s="3" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>931.77</v>
+        <v>816.67</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2132,47 +2304,52 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5450</v>
+        <v>4800</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>47.1</v>
+        <v>100</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>478.6</v>
+        <v>400</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2193,47 +2370,52 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3450</v>
+        <v>3100</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>245.48</v>
+        <v>221.43</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2254,47 +2436,52 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5950</v>
+        <v>5800</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>47.7</v>
+        <v>100</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>609.12</v>
+        <v>580</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2315,47 +2502,52 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3350</v>
+        <v>3600</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="K6" s="3" t="n">
-        <v>22.9</v>
+        <v>25</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>146.26</v>
+        <v>144</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2376,47 +2568,52 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2050</v>
+        <v>2400</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="K7" s="3" t="n">
-        <v>19.7</v>
+        <v>18</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>24.1</v>
+        <v>22</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>104.09</v>
+        <v>133.33</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2440,44 +2637,49 @@
         <v>27000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>46.1</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="K8" s="3" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>15.1</v>
+        <v>16</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>2601.45</v>
+        <v>2454.55</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2498,47 +2700,52 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>17950</v>
+        <v>21000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>48.5</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="K9" s="3" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>1013.67</v>
+        <v>1166.67</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2559,47 +2766,52 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10850</v>
+        <v>10200</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-2.18</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>41.2</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="K10" s="3" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>17.8</v>
+        <v>19</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>578.05</v>
+        <v>510</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2620,47 +2832,52 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7050</v>
+        <v>6800</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>36.5</v>
+        <v>100</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="K11" s="3" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2681,47 +2898,52 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1500</v>
+        <v>1720</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>52.8</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="K12" s="3" t="n">
-        <v>25.4</v>
+        <v>28</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>59.06</v>
+        <v>61.43</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2742,47 +2964,52 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3300</v>
+        <v>3100</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>50.4</v>
+        <v>100</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="K13" s="3" t="n">
-        <v>29.8</v>
+        <v>28</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>110.92</v>
+        <v>110.71</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2803,47 +3030,52 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>57300</v>
+        <v>58000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>43.1</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="K14" s="3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>7532.77</v>
+        <v>7250</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
           <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2864,47 +3096,52 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-2.39</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>64.2</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="K15" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>132.29</v>
+        <v>168.75</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2925,47 +3162,52 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7350</v>
+        <v>8500</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>58.9</v>
+        <v>100</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="K16" s="3" t="n">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>465.15</v>
+        <v>566.67</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -2986,47 +3228,52 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6350</v>
+        <v>6800</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>58.2</v>
+        <v>100</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="K17" s="3" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>444.1</v>
+        <v>453.33</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -3047,47 +3294,52 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9800</v>
+        <v>9200</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>41.8</v>
+        <v>100</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="K18" s="3" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>685.37</v>
+        <v>613.33</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -3108,47 +3360,52 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4200</v>
+        <v>4800</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>51.2</v>
+        <v>100</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="K19" s="3" t="n">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>301.25</v>
+        <v>320</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -3169,47 +3426,52 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1350</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-1.49</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>45.1</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="K20" s="3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>86.88</v>
+        <v>80</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -3230,47 +3492,52 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>15150</v>
+        <v>14200</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>48.4</v>
+        <v>100</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="K21" s="3" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>2014.6</v>
+        <v>1775</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>simulated</t>
         </is>
       </c>
     </row>
@@ -3359,34 +3626,34 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9944</v>
+        <v>9800</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9926.709999999999</v>
+        <v>9800</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9985.43</v>
+        <v>9800</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>198032.68</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>48.1</v>
+        <v>196000</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>9400</v>
+        <v>9600</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10300</v>
+        <v>10000</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3397,34 +3664,34 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4673</v>
+        <v>4800</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4715.97</v>
+        <v>4800</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4758.03</v>
+        <v>4800</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>95766.41</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>49.7</v>
+        <v>96000</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3435,34 +3702,34 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3237</v>
+        <v>3100</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3049.25</v>
+        <v>3100</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3064.35</v>
+        <v>3100</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>61850.36</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>49.8</v>
+        <v>62000</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3740,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5598</v>
+        <v>5800</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5683.06</v>
+        <v>5800</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5734.86</v>
+        <v>5800</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>115762.61</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>45.2</v>
+        <v>116000</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5400</v>
+        <v>5700</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>5900</v>
@@ -3498,9 +3765,9 @@
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3511,34 +3778,34 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3661</v>
+        <v>3600</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3686.97</v>
+        <v>3600</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3654.3</v>
+        <v>3600</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>72511.3</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>61.8</v>
+        <v>72000</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3549,34 +3816,34 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2519</v>
+        <v>2400</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2418.2</v>
+        <v>2400</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2394.43</v>
+        <v>2400</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>48222.85</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>51.8</v>
+        <v>48000</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3587,34 +3854,34 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>26735</v>
+        <v>27000</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>27367.42</v>
+        <v>27000</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27112.44</v>
+        <v>27000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>540360.04</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>59.7</v>
+        <v>540000</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>26200</v>
+        <v>26500</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>28500</v>
+        <v>27500</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3625,34 +3892,34 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>21374</v>
+        <v>21000</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>21016.99</v>
+        <v>21000</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21143.57</v>
+        <v>21000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>420893.68</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>62.6</v>
+        <v>420000</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>20200</v>
+        <v>20600</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>21800</v>
+        <v>21400</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3663,34 +3930,34 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10334</v>
+        <v>10200</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10168.59</v>
+        <v>10200</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10146.01</v>
+        <v>10200</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>202768.38</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>48</v>
+        <v>204000</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9500</v>
+        <v>10000</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10700</v>
+        <v>10400</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3701,34 +3968,34 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6777</v>
+        <v>6800</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6876.72</v>
+        <v>6800</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6880.39</v>
+        <v>6800</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>135789.4</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>49.2</v>
+        <v>136000</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>6400</v>
+        <v>6700</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>7300</v>
+        <v>6900</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3739,22 +4006,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1774</v>
+        <v>1720</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1703.81</v>
+        <v>1720</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1705.17</v>
+        <v>1720</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>34403.87</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>54.2</v>
+        <v>34400</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>1800</v>
@@ -3764,9 +4031,9 @@
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3777,34 +4044,34 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3113</v>
+        <v>3100</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3126.24</v>
+        <v>3100</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3127.89</v>
+        <v>3100</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>61663.35</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>48.7</v>
+        <v>62000</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3815,34 +4082,34 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>60662</v>
+        <v>58000</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>59979.24</v>
+        <v>58000</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>58474.14</v>
+        <v>58000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1161073.59</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>49.8</v>
+        <v>1160000</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>57700</v>
+        <v>56800</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>61900</v>
+        <v>59200</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3853,19 +4120,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1292</v>
+        <v>1350</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1335.56</v>
+        <v>1350</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1334.56</v>
+        <v>1350</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>27030.48</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>43.9</v>
+        <v>27000</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1300</v>
@@ -3878,9 +4145,9 @@
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3891,34 +4158,34 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8513</v>
+        <v>8500</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8483.32</v>
+        <v>8500</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8553.389999999999</v>
+        <v>8500</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>171626.61</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>52.2</v>
+        <v>170000</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8000</v>
+        <v>8300</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9000</v>
+        <v>8700</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3929,34 +4196,34 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>6613</v>
+        <v>6800</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>6732.86</v>
+        <v>6800</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6780.61</v>
+        <v>6800</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>136581.61</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>53.3</v>
+        <v>136000</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>6400</v>
+        <v>6700</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7100</v>
+        <v>6900</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3967,34 +4234,34 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>9490</v>
+        <v>9200</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9123.139999999999</v>
+        <v>9200</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9237.23</v>
+        <v>9200</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>183433.09</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>52</v>
+        <v>184000</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8700</v>
+        <v>9000</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>9700</v>
+        <v>9400</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -4005,34 +4272,34 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4953</v>
+        <v>4800</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4895.87</v>
+        <v>4800</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4816.94</v>
+        <v>4800</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>96465.87</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>55.6</v>
+        <v>96000</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>4700</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>5100</v>
+        <v>4900</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -4043,34 +4310,34 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1145</v>
+        <v>1200</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1183.71</v>
+        <v>1200</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1182.76</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>23811.69</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>55.3</v>
+        <v>24000</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -4081,34 +4348,34 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>13988</v>
+        <v>14200</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>14040.46</v>
+        <v>14200</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14084.94</v>
+        <v>14200</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>281200.61</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>52.8</v>
+        <v>284000</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>13300</v>
+        <v>13900</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>15100</v>
+        <v>14500</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -4231,32 +4498,32 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9523</v>
+        <v>9800</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>738.87</v>
+        <v>816.67</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5910.94</v>
+        <v>6533.33</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -4264,9 +4531,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -4287,32 +4554,32 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4833</v>
+        <v>4800</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>381.4</v>
+        <v>400</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3051.21</v>
+        <v>3200</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -4320,9 +4587,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -4343,32 +4610,32 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3044</v>
+        <v>3100</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>225.13</v>
+        <v>221.43</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1260.74</v>
+        <v>1240</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -4376,9 +4643,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -4399,32 +4666,32 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5773</v>
+        <v>5800</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>639.23</v>
+        <v>580</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3551.3</v>
+        <v>3222.22</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -4432,9 +4699,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -4455,32 +4722,32 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3718</v>
+        <v>3600</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>143.38</v>
+        <v>144</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>896.15</v>
+        <v>900</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -4511,32 +4778,32 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2431</v>
+        <v>2400</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>149.96</v>
+        <v>133.33</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>899.73</v>
+        <v>800</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>19.8</v>
+        <v>22</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.57</v>
+        <v>0.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -4567,32 +4834,32 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>28150</v>
+        <v>27000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2350.55</v>
+        <v>2454.55</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>16160.05</v>
+        <v>16875</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -4600,9 +4867,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -4623,32 +4890,32 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21407</v>
+        <v>21000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1224.62</v>
+        <v>1166.67</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7347.72</v>
+        <v>7000</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.57</v>
+        <v>0.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -4679,32 +4946,32 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10201</v>
+        <v>10200</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>542.35</v>
+        <v>510</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3099.16</v>
+        <v>2914.29</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>17.9</v>
+        <v>19</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -4735,32 +5002,32 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6537</v>
+        <v>6800</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>325.57</v>
+        <v>340</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1860.37</v>
+        <v>1942.86</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -4791,32 +5058,32 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1641</v>
+        <v>1720</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>54.3</v>
+        <v>61.43</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>337.85</v>
+        <v>382.22</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>30.2</v>
+        <v>28</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>21.6</v>
+        <v>20</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -4847,32 +5114,32 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3021</v>
+        <v>3100</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>111.56</v>
+        <v>110.71</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>694.14</v>
+        <v>688.89</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>27.1</v>
+        <v>28</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>19.3</v>
+        <v>20</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.23</v>
+        <v>0.4</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -4903,32 +5170,32 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>60816</v>
+        <v>58000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7228.24</v>
+        <v>7250</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>48188.28</v>
+        <v>48333.33</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -4936,9 +5203,9 @@
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -4959,32 +5226,32 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1326</v>
+        <v>1350</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>182.23</v>
+        <v>168.75</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1214.87</v>
+        <v>1125</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>10.9</v>
+        <v>12</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -4992,9 +5259,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5015,32 +5282,32 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8557</v>
+        <v>8500</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>572.73</v>
+        <v>566.67</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>4295.45</v>
+        <v>4250</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -5048,9 +5315,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5071,32 +5338,32 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6830</v>
+        <v>6800</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>463.87</v>
+        <v>453.33</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3479.04</v>
+        <v>3400</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -5104,9 +5371,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5127,32 +5394,32 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9381</v>
+        <v>9200</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>577.92</v>
+        <v>613.33</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>4334.42</v>
+        <v>4600</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>16.2</v>
+        <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>16.2</v>
+        <v>15</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -5183,32 +5450,32 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4732</v>
+        <v>4800</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>343.26</v>
+        <v>320</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2574.44</v>
+        <v>2400</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.97</v>
+        <v>1.6</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -5216,9 +5483,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5239,32 +5506,32 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1180</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>74.19</v>
+        <v>80</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>556.4400000000001</v>
+        <v>600</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -5295,32 +5562,32 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>13980</v>
+        <v>14200</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1812.52</v>
+        <v>1775</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>12083.46</v>
+        <v>11833.33</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.77</v>
+        <v>0.55</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -5328,9 +5595,9 @@
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5628,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
@@ -5418,7 +5685,7 @@
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
@@ -5464,7 +5731,7 @@
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
@@ -5510,7 +5777,7 @@
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
@@ -5556,7 +5823,7 @@
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
@@ -5602,7 +5869,7 @@
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
@@ -5648,7 +5915,7 @@
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Sampoerna</t>
         </is>
@@ -5694,7 +5961,7 @@
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
@@ -5740,7 +6007,7 @@
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Telkom</t>
         </is>
@@ -5786,7 +6053,7 @@
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
@@ -5832,7 +6099,7 @@
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Indocement</t>
         </is>
@@ -5891,138 +6158,144 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>📊 DASHBOARD SAHAM INDONESIA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Last Update: 2026-06-30 08:45</t>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Last Update: 2026-07-01 19:15</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>IHSG Level</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5,999</t>
+          <t>5,800 (base)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>IHSG Change</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>+1.96%</t>
+          <t>0% (base)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Top Sector</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Consumer (+1.21%)</t>
+          <t>Consumer</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Worst Sector</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mining (-2.50%)</t>
+          <t>Mining</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr"/>
+      <c r="A8" s="12" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>7</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0 (simulated)</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>6</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0 (simulated)</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>HOLD Signals</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>12</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20 (simulated)</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr"/>
+      <c r="A12" s="12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Best Buy Today</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>ANTM.JK, KLBF.JK, INTP.JK</t>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>UNVR.JK, HMSP.JK</t>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PTUN.JK (High Risk/Reward)</t>
+          <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-01 19:15</t>
+          <t>Last Update: 2026-07-01 20:15</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-01 20:15</t>
+          <t>Last Update: 2026-07-01 20:31</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-01 20:31</t>
+          <t>Last Update: 2026-07-01 20:45</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Technical" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technical" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,1147 +562,1147 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="B2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="B4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="B5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="B6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="B7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="B8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="B9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="B10" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="B11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="B12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="B15" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="B16" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="B17" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="B18" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="B19" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="B20" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="B21" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="B22" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="B23" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="B24" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="B25" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="B26" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="B27" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="B28" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="B29" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="B30" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="B31" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="B32" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -1781,328 +1781,328 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" t="n">
         <v>1300</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" t="n">
         <v>-1.13</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>0.92</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>720</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" t="n">
         <v>-0.85</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>1.21</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>2200</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" t="n">
         <v>-2.5</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>0.85</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" t="n">
         <v>1050</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" t="n">
         <v>-1.77</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" t="n">
         <v>1.1</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" t="n">
         <v>1150</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" t="n">
         <v>-4.43</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>0.75</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" t="n">
         <v>1420</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" t="n">
         <v>-1.34</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>1.15</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" t="n">
         <v>980</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>1.05</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>2680</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" t="n">
         <v>-2.81</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -2222,1320 +2222,1320 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>100</v>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" t="n">
         <v>12</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" t="n">
         <v>1.5</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" t="n">
         <v>15</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" t="n">
         <v>816.67</v>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>100</v>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" t="n">
         <v>1.5</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" t="n">
         <v>15</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" t="n">
         <v>400</v>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>100</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" t="n">
         <v>14</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" t="n">
         <v>2.5</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" t="n">
         <v>17</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" t="n">
         <v>221.43</v>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="D5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>100</v>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" t="n">
         <v>1.8</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" t="n">
         <v>14</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" t="n">
         <v>580</v>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>100</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" t="n">
         <v>25</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" t="n">
         <v>4</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" t="n">
         <v>18</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" t="n">
         <v>144</v>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>100</v>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" t="n">
         <v>18</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" t="n">
         <v>22</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" t="n">
         <v>133.33</v>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>100</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" t="n">
         <v>1.6</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" t="n">
         <v>16</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" t="n">
         <v>2454.55</v>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>100</v>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" t="n">
         <v>18</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" t="n">
         <v>22</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" t="n">
         <v>1166.67</v>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3" t="n">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" t="n">
         <v>20</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" t="n">
         <v>3.5</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" t="n">
         <v>19</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" t="n">
         <v>510</v>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>100</v>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" t="n">
         <v>20</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" t="n">
         <v>3.5</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" t="n">
         <v>19</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" t="n">
         <v>340</v>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" t="n">
         <v>28</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" t="n">
         <v>4.5</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" t="n">
         <v>20</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" t="n">
         <v>61.43</v>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="n">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>100</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" t="n">
         <v>28</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" t="n">
         <v>4.5</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" t="n">
         <v>20</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" t="n">
         <v>110.71</v>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>100</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" t="n">
         <v>8</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" t="n">
         <v>1.2</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" t="n">
         <v>12</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" t="n">
         <v>7250</v>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>100</v>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" t="n">
         <v>8</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" t="n">
         <v>1.2</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" t="n">
         <v>12</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" t="n">
         <v>168.75</v>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>100</v>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" t="n">
         <v>15</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" t="n">
         <v>15</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" t="n">
         <v>566.67</v>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>100</v>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" t="n">
         <v>15</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" t="n">
         <v>15</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" t="n">
         <v>453.33</v>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3" t="n">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>100</v>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" t="n">
         <v>15</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" t="n">
         <v>15</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" t="n">
         <v>613.33</v>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="n">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
         <v>100</v>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" t="n">
         <v>15</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" t="n">
         <v>10</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" t="n">
         <v>320</v>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="n">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>100</v>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" t="n">
         <v>15</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" t="n">
         <v>15</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" t="n">
         <v>80</v>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>100</v>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" t="n">
         <v>1.2</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" t="n">
         <v>12</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" t="n">
         <v>1775</v>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -3620,760 +3620,760 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" t="n">
         <v>9800</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" t="n">
         <v>9800</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>196000</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" t="n">
         <v>100</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" t="n">
         <v>9600</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>10000</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>4800</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" t="n">
         <v>4800</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>96000</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" t="n">
         <v>100</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>4700</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" t="n">
         <v>4900</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>3100</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" t="n">
         <v>3100</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>62000</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>3000</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>3200</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="B5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" t="n">
         <v>116000</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>5700</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>5900</v>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" t="n">
         <v>3600</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" t="n">
         <v>3600</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>72000</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>3500</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" t="n">
         <v>3700</v>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" t="n">
         <v>2400</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" t="n">
         <v>2400</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" t="n">
         <v>48000</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" t="n">
         <v>100</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>2400</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" t="n">
         <v>2400</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" t="n">
         <v>27000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" t="n">
         <v>27000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" t="n">
         <v>540000</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>26500</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>27500</v>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>21000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" t="n">
         <v>21000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" t="n">
         <v>420000</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>20600</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" t="n">
         <v>21400</v>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" t="n">
         <v>10200</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" t="n">
         <v>10200</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>204000</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" t="n">
         <v>10400</v>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" t="n">
         <v>6800</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" t="n">
         <v>6800</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" t="n">
         <v>136000</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>6700</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>6900</v>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" t="n">
         <v>1720</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" t="n">
         <v>1720</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" t="n">
         <v>34400</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>1700</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" t="n">
         <v>1800</v>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" t="n">
         <v>3100</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" t="n">
         <v>3100</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" t="n">
         <v>62000</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>3000</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" t="n">
         <v>3200</v>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" t="n">
         <v>58000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" t="n">
         <v>58000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" t="n">
         <v>1160000</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" t="n">
         <v>100</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>56800</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>59200</v>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" t="n">
         <v>1350</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" t="n">
         <v>1350</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" t="n">
         <v>27000</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" t="n">
         <v>100</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>1300</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" t="n">
         <v>1400</v>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" t="n">
         <v>8500</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" t="n">
         <v>8500</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" t="n">
         <v>170000</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" t="n">
         <v>100</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>8300</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" t="n">
         <v>8700</v>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" t="n">
         <v>6800</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" t="n">
         <v>6800</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" t="n">
         <v>136000</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" t="n">
         <v>100</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>6700</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>6900</v>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" t="n">
         <v>9200</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" t="n">
         <v>9200</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" t="n">
         <v>184000</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" t="n">
         <v>100</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>9000</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" t="n">
         <v>9400</v>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" t="n">
         <v>4800</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" t="n">
         <v>4800</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" t="n">
         <v>96000</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" t="n">
         <v>100</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>4700</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="n">
         <v>4900</v>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" t="n">
         <v>1200</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" t="n">
         <v>1200</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" t="n">
         <v>24000</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" t="n">
         <v>100</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>1200</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>1200</v>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J20" s="6" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" t="n">
         <v>14200</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" t="n">
         <v>14200</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" t="n">
         <v>284000</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" t="n">
         <v>100</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" t="n">
         <v>13900</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" t="n">
         <v>14500</v>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -4482,1120 +4482,1120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>816.67</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" t="n">
         <v>6533.33</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>1.5</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" t="n">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" t="n">
         <v>1.2</v>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>400</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" t="n">
         <v>3200</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" t="n">
         <v>15</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>221.43</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" t="n">
         <v>1240</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>14</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>2.5</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" t="n">
         <v>17</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" t="n">
         <v>0.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" t="n">
         <v>1.6</v>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="D5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" t="n">
         <v>580</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" t="n">
         <v>3222.22</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>10</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>1.8</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" t="n">
         <v>14</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" t="n">
         <v>0.4</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" t="n">
         <v>1.6</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>144</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" t="n">
         <v>900</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>25</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" t="n">
         <v>18</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" t="n">
         <v>0.4</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" t="n">
         <v>133.33</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" t="n">
         <v>800</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>18</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" t="n">
         <v>22</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" t="n">
         <v>0.4</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" t="n">
         <v>1.6</v>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" t="n">
         <v>2454.55</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" t="n">
         <v>16875</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>11</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>1.6</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" t="n">
         <v>16</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" t="n">
         <v>0.4</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" t="n">
         <v>1.6</v>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" t="n">
         <v>1166.67</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" t="n">
         <v>7000</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>18</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" t="n">
         <v>22</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" t="n">
         <v>0.4</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" t="n">
         <v>1.6</v>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>510</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" t="n">
         <v>2914.29</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>20</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" t="n">
         <v>3.5</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" t="n">
         <v>19</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" t="n">
         <v>0.4</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" t="n">
         <v>1.6</v>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" t="n">
         <v>340</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" t="n">
         <v>1942.86</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>20</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>3.5</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" t="n">
         <v>19</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="J11" t="n">
         <v>0.4</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" t="n">
         <v>1.6</v>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" t="n">
         <v>61.43</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" t="n">
         <v>382.22</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>28</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" t="n">
         <v>4.5</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" t="n">
         <v>20</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" t="n">
         <v>0.4</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" t="n">
         <v>1.6</v>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" t="n">
         <v>110.71</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" t="n">
         <v>688.89</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>28</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" t="n">
         <v>4.5</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" t="n">
         <v>20</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" t="n">
         <v>0.4</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" t="n">
         <v>1.6</v>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" t="n">
         <v>7250</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" t="n">
         <v>48333.33</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>1.2</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" t="n">
         <v>12</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" t="n">
         <v>0.55</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" t="n">
         <v>168.75</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" t="n">
         <v>1125</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" t="n">
         <v>1.2</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" t="n">
         <v>12</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" t="n">
         <v>0.55</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" t="n">
         <v>2</v>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" t="n">
         <v>566.67</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" t="n">
         <v>4250</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>15</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" t="n">
         <v>15</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J16" t="n">
         <v>0.4</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" t="n">
         <v>1.6</v>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" t="n">
         <v>453.33</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" t="n">
         <v>3400</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>15</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" t="n">
         <v>15</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="J17" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" t="n">
         <v>1.6</v>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" t="n">
         <v>613.33</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" t="n">
         <v>4600</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>15</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" t="n">
         <v>15</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="J18" t="n">
         <v>0.4</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" t="n">
         <v>1.6</v>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" t="n">
         <v>320</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" t="n">
         <v>2400</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>15</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" t="n">
         <v>10</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="J19" t="n">
         <v>0.4</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" t="n">
         <v>1.6</v>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" t="n">
         <v>80</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" t="n">
         <v>600</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>15</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" t="n">
         <v>15</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="J20" t="n">
         <v>0.4</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" t="n">
         <v>1.6</v>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" t="n">
         <v>1775</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" t="n">
         <v>11833.33</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" t="n">
         <v>8</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" t="n">
         <v>1.2</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" t="n">
         <v>12</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="J21" t="n">
         <v>0.55</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -5680,460 +5680,460 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>1280</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" t="n">
         <v>28</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Oversold - RSI rendah</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Bisa rebound jika commodity naik</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>9800</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" t="n">
         <v>32</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Turun mengikuti IHSG</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Konsumen stabil</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>1650</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" t="n">
         <v>35</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>RSI oversold</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Healthcare growth</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" t="n">
         <v>1150</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" t="n">
         <v>38</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Turun karena gas price</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Subsidi pemerintah</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3200</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" t="n">
         <v>68</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Downtrend kuat</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Consumer lemah</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Sampoerna</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2200</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" t="n">
         <v>-3.8</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" t="n">
         <v>62</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Regulasi rokok</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Tren menurun</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>9600</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" t="n">
         <v>48</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Stable bank</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Dividen menarik</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Telkom</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>3050</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" t="n">
         <v>52</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Sideways</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>5G rollout</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>56000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>-5.2</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" t="n">
         <v>25</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Anjlok dari high</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Nikel outlook bullish</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SPECULATIVE BUY</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Indocement</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>8800</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" t="n">
         <v>42</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Infrastructure push</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Pemerintah bangun infra</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -6150,7 +6150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6165,14 +6165,15 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Last Update: 2026-07-01 20:45</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Last Update: 2026-07-01 21:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>IHSG Level</t>
         </is>
@@ -6184,7 +6185,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>IHSG Change</t>
         </is>
@@ -6196,7 +6197,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Top Sector</t>
         </is>
@@ -6208,7 +6209,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Worst Sector</t>
         </is>
@@ -6220,13 +6221,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BUY Signals</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0 (simulated)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>BUY Signals</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SELL Signals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6236,64 +6245,48 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>SELL Signals</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HOLD Signals</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0 (simulated)</t>
+          <t>20 (simulated)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>HOLD Signals</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Best Buy Today</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20 (simulated)</t>
+          <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/A (use update_saham.py)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Best Buy Today</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>N/A (use update_saham.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>N/A (use update_saham.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technical" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Technical" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,1147 +562,1147 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F16" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F21" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F25" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F26" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F27" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F28" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F29" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F31" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F32" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -1781,328 +1781,328 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>-1.13</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>-0.85</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>1050</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="3" t="n">
         <v>-1.77</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>1150</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>-4.43</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>1420</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="3" t="n">
         <v>-1.34</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>980</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>2680</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>-2.81</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -2222,1320 +2222,1320 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="n">
         <v>816.67</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="n">
         <v>221.43</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="D5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3" t="n">
         <v>133.33</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="n">
         <v>2454.55</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="3" t="n">
         <v>1166.67</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="3" t="n">
         <v>510</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="3" t="n">
         <v>61.43</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="3" t="n">
         <v>110.71</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="3" t="n">
         <v>7250</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="3" t="n">
         <v>168.75</v>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="3" t="n">
         <v>566.67</v>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="3" t="n">
         <v>453.33</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="3" t="n">
         <v>613.33</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="3" t="n">
         <v>1775</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -3620,760 +3620,760 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>196000</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>9600</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>96000</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>4700</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>4900</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>62000</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>116000</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>5700</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>5900</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>72000</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>3500</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>3700</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>48000</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>540000</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>26500</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>27500</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>420000</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3" t="n">
         <v>20600</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>21400</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>204000</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>10400</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>136000</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="3" t="n">
         <v>6700</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="3" t="n">
         <v>6900</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="3" t="n">
         <v>34400</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>1700</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="3" t="n">
         <v>62000</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="3" t="n">
         <v>1160000</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="3" t="n">
         <v>56800</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="3" t="n">
         <v>59200</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3" t="n">
         <v>170000</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3" t="n">
         <v>8300</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="3" t="n">
         <v>8700</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="3" t="n">
         <v>136000</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="3" t="n">
         <v>6700</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="3" t="n">
         <v>6900</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="3" t="n">
         <v>184000</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="3" t="n">
         <v>9000</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="3" t="n">
         <v>9400</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="3" t="n">
         <v>96000</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="3" t="n">
         <v>4700</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="3" t="n">
         <v>4900</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="3" t="n">
         <v>24000</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="3" t="n">
         <v>284000</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="3" t="n">
         <v>13900</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="3" t="n">
         <v>14500</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -4482,1120 +4482,1120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>816.67</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>6533.33</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>221.43</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>1240</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>3222.22</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>133.33</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>2454.55</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>16875</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>1166.67</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>7000</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>510</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>2914.29</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="3" t="n">
         <v>1942.86</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="3" t="n">
         <v>61.43</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="3" t="n">
         <v>382.22</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="3" t="n">
         <v>110.71</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="3" t="n">
         <v>688.89</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="3" t="n">
         <v>7250</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="3" t="n">
         <v>48333.33</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="3" t="n">
         <v>168.75</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="3" t="n">
         <v>1125</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3" t="n">
         <v>566.67</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="3" t="n">
         <v>4250</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="3" t="n">
         <v>453.33</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="3" t="n">
         <v>3400</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="3" t="n">
         <v>613.33</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="3" t="n">
         <v>4600</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="3" t="n">
         <v>1775</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="3" t="n">
         <v>11833.33</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -5680,460 +5680,460 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>1280</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Oversold - RSI rendah</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Bisa rebound jika commodity naik</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Turun mengikuti IHSG</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Konsumen stabil</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>1650</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>RSI oversold</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Healthcare growth</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>1150</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="3" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Turun karena gas price</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Subsidi pemerintah</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Downtrend kuat</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Consumer lemah</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Sampoerna</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>-3.8</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Regulasi rokok</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Tren menurun</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>9600</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Stable bank</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Dividen menarik</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Telkom</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>3050</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Sideways</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>5G rollout</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>56000</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>-5.2</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Anjlok dari high</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Nikel outlook bullish</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>SPECULATIVE BUY</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Indocement</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>8800</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Infrastructure push</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Pemerintah bangun infra</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -6150,7 +6150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6165,15 +6165,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Last Update: 2026-07-01 21:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Last Update: 2026-07-03 16:00</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>IHSG Level</t>
         </is>
@@ -6185,7 +6184,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>IHSG Change</t>
         </is>
@@ -6197,7 +6196,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Top Sector</t>
         </is>
@@ -6209,7 +6208,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Worst Sector</t>
         </is>
@@ -6221,72 +6220,80 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>0 (simulated)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>0 (simulated)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>HOLD Signals</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>20 (simulated)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Best Buy Today</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-03 16:00</t>
+          <t>Last Update: 2026-07-03 16:15</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-03 16:15</t>
+          <t>Last Update: 2026-07-03 16:30</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-03 16:30</t>
+          <t>Last Update: 2026-07-03 16:47</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Technical" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technical" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,1147 +562,1147 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -1781,328 +1781,328 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" t="n">
         <v>1300</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" t="n">
         <v>-1.13</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>0.92</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>720</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" t="n">
         <v>-0.85</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>1.21</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>2200</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" t="n">
         <v>-2.5</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>0.85</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" t="n">
         <v>1050</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" t="n">
         <v>-1.77</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" t="n">
         <v>1.1</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" t="n">
         <v>1150</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" t="n">
         <v>-4.43</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>0.75</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" t="n">
         <v>1420</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" t="n">
         <v>-1.34</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>1.15</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" t="n">
         <v>980</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>1.05</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>2680</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" t="n">
         <v>-2.81</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -2222,1320 +2222,1320 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>100</v>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" t="n">
         <v>12</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" t="n">
         <v>1.5</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" t="n">
         <v>15</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" t="n">
         <v>816.67</v>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>100</v>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" t="n">
         <v>1.5</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" t="n">
         <v>15</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" t="n">
         <v>400</v>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>100</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" t="n">
         <v>14</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" t="n">
         <v>2.5</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" t="n">
         <v>17</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" t="n">
         <v>221.43</v>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="D5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>100</v>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" t="n">
         <v>1.8</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" t="n">
         <v>14</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" t="n">
         <v>580</v>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>100</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" t="n">
         <v>25</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" t="n">
         <v>4</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" t="n">
         <v>18</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" t="n">
         <v>144</v>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>100</v>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" t="n">
         <v>18</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" t="n">
         <v>22</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" t="n">
         <v>133.33</v>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>100</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" t="n">
         <v>1.6</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" t="n">
         <v>16</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" t="n">
         <v>2454.55</v>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>100</v>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" t="n">
         <v>18</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" t="n">
         <v>22</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" t="n">
         <v>1166.67</v>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3" t="n">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" t="n">
         <v>20</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" t="n">
         <v>3.5</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" t="n">
         <v>19</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" t="n">
         <v>510</v>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>100</v>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" t="n">
         <v>20</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" t="n">
         <v>3.5</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" t="n">
         <v>19</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" t="n">
         <v>340</v>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" t="n">
         <v>28</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" t="n">
         <v>4.5</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" t="n">
         <v>20</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" t="n">
         <v>61.43</v>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="n">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>100</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" t="n">
         <v>28</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" t="n">
         <v>4.5</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" t="n">
         <v>20</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" t="n">
         <v>110.71</v>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>100</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" t="n">
         <v>8</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" t="n">
         <v>1.2</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" t="n">
         <v>12</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" t="n">
         <v>7250</v>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>100</v>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" t="n">
         <v>8</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" t="n">
         <v>1.2</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" t="n">
         <v>12</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" t="n">
         <v>168.75</v>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>100</v>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" t="n">
         <v>15</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" t="n">
         <v>15</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" t="n">
         <v>566.67</v>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>100</v>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" t="n">
         <v>15</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" t="n">
         <v>15</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" t="n">
         <v>453.33</v>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3" t="n">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>100</v>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" t="n">
         <v>15</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" t="n">
         <v>15</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" t="n">
         <v>613.33</v>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="n">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
         <v>100</v>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" t="n">
         <v>15</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" t="n">
         <v>10</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" t="n">
         <v>320</v>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="n">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>100</v>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" t="n">
         <v>15</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" t="n">
         <v>15</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" t="n">
         <v>80</v>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>100</v>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" t="n">
         <v>1.2</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" t="n">
         <v>12</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" t="n">
         <v>1775</v>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -3620,760 +3620,760 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" t="n">
         <v>9800</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" t="n">
         <v>9800</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>196000</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" t="n">
         <v>100</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" t="n">
         <v>9600</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>10000</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>4800</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" t="n">
         <v>4800</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>96000</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" t="n">
         <v>100</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>4700</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" t="n">
         <v>4900</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>3100</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" t="n">
         <v>3100</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>62000</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>3000</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>3200</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="B5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" t="n">
         <v>116000</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>5700</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>5900</v>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" t="n">
         <v>3600</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" t="n">
         <v>3600</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>72000</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>3500</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" t="n">
         <v>3700</v>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" t="n">
         <v>2400</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" t="n">
         <v>2400</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" t="n">
         <v>48000</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" t="n">
         <v>100</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>2400</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" t="n">
         <v>2400</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" t="n">
         <v>27000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" t="n">
         <v>27000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" t="n">
         <v>540000</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>26500</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>27500</v>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>21000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" t="n">
         <v>21000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" t="n">
         <v>420000</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>20600</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" t="n">
         <v>21400</v>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" t="n">
         <v>10200</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" t="n">
         <v>10200</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>204000</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" t="n">
         <v>10400</v>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" t="n">
         <v>6800</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" t="n">
         <v>6800</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" t="n">
         <v>136000</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>6700</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>6900</v>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" t="n">
         <v>1720</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" t="n">
         <v>1720</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" t="n">
         <v>34400</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>1700</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" t="n">
         <v>1800</v>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" t="n">
         <v>3100</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" t="n">
         <v>3100</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" t="n">
         <v>62000</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>3000</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" t="n">
         <v>3200</v>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" t="n">
         <v>58000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" t="n">
         <v>58000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" t="n">
         <v>1160000</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" t="n">
         <v>100</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>56800</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>59200</v>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" t="n">
         <v>1350</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" t="n">
         <v>1350</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" t="n">
         <v>27000</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" t="n">
         <v>100</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>1300</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" t="n">
         <v>1400</v>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" t="n">
         <v>8500</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" t="n">
         <v>8500</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" t="n">
         <v>170000</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" t="n">
         <v>100</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>8300</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" t="n">
         <v>8700</v>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" t="n">
         <v>6800</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" t="n">
         <v>6800</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" t="n">
         <v>136000</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" t="n">
         <v>100</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>6700</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>6900</v>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" t="n">
         <v>9200</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" t="n">
         <v>9200</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" t="n">
         <v>184000</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" t="n">
         <v>100</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>9000</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" t="n">
         <v>9400</v>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" t="n">
         <v>4800</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" t="n">
         <v>4800</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" t="n">
         <v>96000</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" t="n">
         <v>100</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>4700</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="n">
         <v>4900</v>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" t="n">
         <v>1200</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" t="n">
         <v>1200</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" t="n">
         <v>24000</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" t="n">
         <v>100</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>1200</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>1200</v>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J20" s="6" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" t="n">
         <v>14200</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" t="n">
         <v>14200</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" t="n">
         <v>284000</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" t="n">
         <v>100</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" t="n">
         <v>13900</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" t="n">
         <v>14500</v>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -4482,1120 +4482,1120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>816.67</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" t="n">
         <v>6533.33</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>1.5</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" t="n">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" t="n">
         <v>1.2</v>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>400</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" t="n">
         <v>3200</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" t="n">
         <v>15</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>221.43</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" t="n">
         <v>1240</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>14</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>2.5</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" t="n">
         <v>17</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" t="n">
         <v>0.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" t="n">
         <v>1.6</v>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="D5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" t="n">
         <v>580</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" t="n">
         <v>3222.22</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>10</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>1.8</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" t="n">
         <v>14</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" t="n">
         <v>0.4</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" t="n">
         <v>1.6</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>144</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" t="n">
         <v>900</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>25</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" t="n">
         <v>18</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" t="n">
         <v>0.4</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" t="n">
         <v>133.33</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" t="n">
         <v>800</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>18</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" t="n">
         <v>22</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" t="n">
         <v>0.4</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" t="n">
         <v>1.6</v>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" t="n">
         <v>2454.55</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" t="n">
         <v>16875</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>11</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>1.6</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" t="n">
         <v>16</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" t="n">
         <v>0.4</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" t="n">
         <v>1.6</v>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" t="n">
         <v>1166.67</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" t="n">
         <v>7000</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>18</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" t="n">
         <v>22</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" t="n">
         <v>0.4</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" t="n">
         <v>1.6</v>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>510</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" t="n">
         <v>2914.29</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>20</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" t="n">
         <v>3.5</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" t="n">
         <v>19</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" t="n">
         <v>0.4</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" t="n">
         <v>1.6</v>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" t="n">
         <v>340</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" t="n">
         <v>1942.86</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>20</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>3.5</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" t="n">
         <v>19</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="J11" t="n">
         <v>0.4</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" t="n">
         <v>1.6</v>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" t="n">
         <v>61.43</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" t="n">
         <v>382.22</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>28</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" t="n">
         <v>4.5</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" t="n">
         <v>20</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" t="n">
         <v>0.4</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" t="n">
         <v>1.6</v>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" t="n">
         <v>110.71</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" t="n">
         <v>688.89</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>28</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" t="n">
         <v>4.5</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" t="n">
         <v>20</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" t="n">
         <v>0.4</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" t="n">
         <v>1.6</v>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" t="n">
         <v>7250</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" t="n">
         <v>48333.33</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>1.2</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" t="n">
         <v>12</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" t="n">
         <v>0.55</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" t="n">
         <v>168.75</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" t="n">
         <v>1125</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" t="n">
         <v>1.2</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" t="n">
         <v>12</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" t="n">
         <v>0.55</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" t="n">
         <v>2</v>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" t="n">
         <v>566.67</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" t="n">
         <v>4250</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>15</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" t="n">
         <v>15</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J16" t="n">
         <v>0.4</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" t="n">
         <v>1.6</v>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" t="n">
         <v>453.33</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" t="n">
         <v>3400</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>15</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" t="n">
         <v>15</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="J17" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" t="n">
         <v>1.6</v>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" t="n">
         <v>613.33</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" t="n">
         <v>4600</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>15</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" t="n">
         <v>15</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="J18" t="n">
         <v>0.4</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" t="n">
         <v>1.6</v>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" t="n">
         <v>320</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" t="n">
         <v>2400</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>15</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" t="n">
         <v>10</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="J19" t="n">
         <v>0.4</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" t="n">
         <v>1.6</v>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" t="n">
         <v>80</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" t="n">
         <v>600</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>15</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" t="n">
         <v>15</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="J20" t="n">
         <v>0.4</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" t="n">
         <v>1.6</v>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" t="n">
         <v>1775</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" t="n">
         <v>11833.33</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" t="n">
         <v>8</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" t="n">
         <v>1.2</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" t="n">
         <v>12</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="J21" t="n">
         <v>0.55</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -5680,460 +5680,460 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>1280</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" t="n">
         <v>28</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Oversold - RSI rendah</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Bisa rebound jika commodity naik</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>9800</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" t="n">
         <v>32</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Turun mengikuti IHSG</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Konsumen stabil</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>1650</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" t="n">
         <v>35</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>RSI oversold</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Healthcare growth</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" t="n">
         <v>1150</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" t="n">
         <v>38</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Turun karena gas price</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Subsidi pemerintah</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3200</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" t="n">
         <v>68</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Downtrend kuat</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Consumer lemah</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Sampoerna</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2200</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" t="n">
         <v>-3.8</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" t="n">
         <v>62</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Regulasi rokok</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Tren menurun</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>9600</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" t="n">
         <v>48</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Stable bank</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Dividen menarik</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Telkom</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>3050</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" t="n">
         <v>52</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Sideways</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>5G rollout</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>56000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>-5.2</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" t="n">
         <v>25</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Anjlok dari high</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Nikel outlook bullish</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SPECULATIVE BUY</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Indocement</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>8800</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" t="n">
         <v>42</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Infrastructure push</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Pemerintah bangun infra</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -6150,7 +6150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6165,14 +6165,15 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Last Update: 2026-07-03 16:47</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Last Update: 2026-07-04 09:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>IHSG Level</t>
         </is>
@@ -6184,7 +6185,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>IHSG Change</t>
         </is>
@@ -6196,7 +6197,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Top Sector</t>
         </is>
@@ -6208,7 +6209,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Worst Sector</t>
         </is>
@@ -6220,13 +6221,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BUY Signals</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0 (simulated)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>BUY Signals</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SELL Signals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6236,64 +6245,48 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>SELL Signals</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HOLD Signals</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0 (simulated)</t>
+          <t>20 (simulated)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>HOLD Signals</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Best Buy Today</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20 (simulated)</t>
+          <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/A (use update_saham.py)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Best Buy Today</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>N/A (use update_saham.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>N/A (use update_saham.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-04 09:31</t>
+          <t>Last Update: 2026-07-04 10:15</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technical" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Technical" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,1147 +562,1147 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F16" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F21" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F25" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F26" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F27" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F28" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F29" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F31" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F32" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -1781,328 +1781,328 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>-1.13</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>-0.85</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>1050</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="3" t="n">
         <v>-1.77</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>1150</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>-4.43</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>1420</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="3" t="n">
         <v>-1.34</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>980</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>2680</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>-2.81</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -2222,1320 +2222,1320 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="n">
         <v>816.67</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="n">
         <v>221.43</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="D5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3" t="n">
         <v>133.33</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="n">
         <v>2454.55</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="3" t="n">
         <v>1166.67</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="3" t="n">
         <v>510</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="3" t="n">
         <v>61.43</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="3" t="n">
         <v>110.71</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="3" t="n">
         <v>7250</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="3" t="n">
         <v>168.75</v>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="3" t="n">
         <v>566.67</v>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="3" t="n">
         <v>453.33</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="3" t="n">
         <v>613.33</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="3" t="n">
         <v>1775</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -3620,760 +3620,760 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>196000</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>9600</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>96000</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>4700</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>4900</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>62000</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>116000</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>5700</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>5900</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>72000</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>3500</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>3700</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>48000</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>540000</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>26500</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>27500</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>420000</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3" t="n">
         <v>20600</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>21400</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>204000</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>10400</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>136000</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="3" t="n">
         <v>6700</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="3" t="n">
         <v>6900</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="3" t="n">
         <v>34400</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>1700</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="3" t="n">
         <v>62000</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="3" t="n">
         <v>1160000</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="3" t="n">
         <v>56800</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="3" t="n">
         <v>59200</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3" t="n">
         <v>170000</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3" t="n">
         <v>8300</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="3" t="n">
         <v>8700</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="3" t="n">
         <v>136000</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="3" t="n">
         <v>6700</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="3" t="n">
         <v>6900</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="3" t="n">
         <v>184000</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="3" t="n">
         <v>9000</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="3" t="n">
         <v>9400</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="3" t="n">
         <v>96000</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="3" t="n">
         <v>4700</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="3" t="n">
         <v>4900</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="3" t="n">
         <v>24000</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="3" t="n">
         <v>284000</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="3" t="n">
         <v>13900</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="3" t="n">
         <v>14500</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -4482,1120 +4482,1120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>816.67</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>6533.33</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>221.43</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>1240</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>3222.22</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>133.33</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>2454.55</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>16875</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>1166.67</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>7000</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>510</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>2914.29</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="3" t="n">
         <v>1942.86</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="3" t="n">
         <v>61.43</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="3" t="n">
         <v>382.22</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="3" t="n">
         <v>110.71</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="3" t="n">
         <v>688.89</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="3" t="n">
         <v>7250</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="3" t="n">
         <v>48333.33</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="3" t="n">
         <v>168.75</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="3" t="n">
         <v>1125</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3" t="n">
         <v>566.67</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="3" t="n">
         <v>4250</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="3" t="n">
         <v>453.33</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="3" t="n">
         <v>3400</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="3" t="n">
         <v>613.33</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="3" t="n">
         <v>4600</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="3" t="n">
         <v>1775</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="3" t="n">
         <v>11833.33</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -5680,460 +5680,460 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>1280</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Oversold - RSI rendah</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Bisa rebound jika commodity naik</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Turun mengikuti IHSG</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Konsumen stabil</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>1650</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>RSI oversold</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Healthcare growth</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>1150</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="3" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Turun karena gas price</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Subsidi pemerintah</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Downtrend kuat</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Consumer lemah</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Sampoerna</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>-3.8</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Regulasi rokok</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Tren menurun</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>9600</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Stable bank</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Dividen menarik</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Telkom</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>3050</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Sideways</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>5G rollout</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>56000</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>-5.2</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Anjlok dari high</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Nikel outlook bullish</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>SPECULATIVE BUY</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Indocement</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>8800</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Infrastructure push</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Pemerintah bangun infra</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -6150,7 +6150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6165,15 +6165,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Last Update: 2026-07-04 10:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Last Update: 2026-07-05 07:31</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>IHSG Level</t>
         </is>
@@ -6185,7 +6184,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>IHSG Change</t>
         </is>
@@ -6197,7 +6196,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Top Sector</t>
         </is>
@@ -6209,7 +6208,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Worst Sector</t>
         </is>
@@ -6221,72 +6220,80 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>0 (simulated)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>0 (simulated)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>HOLD Signals</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>20 (simulated)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Best Buy Today</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-05 07:31</t>
+          <t>Last Update: 2026-07-05 23:30</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Technical" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technical" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,1147 +562,1147 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="B2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="B4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="B5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="B6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="B7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="B8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="B9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="B10" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="B11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="B12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="B15" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="B16" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="B17" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="B18" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="B19" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="B20" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="B21" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="B22" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="B23" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="B24" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="B25" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="B26" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="B27" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="B28" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="B29" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="B30" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="B31" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="B32" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -1781,328 +1781,328 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" t="n">
         <v>1300</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" t="n">
         <v>-1.13</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>0.92</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>720</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" t="n">
         <v>-0.85</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>1.21</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>2200</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" t="n">
         <v>-2.5</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>0.85</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" t="n">
         <v>1050</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" t="n">
         <v>-1.77</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" t="n">
         <v>1.1</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" t="n">
         <v>1150</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" t="n">
         <v>-4.43</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>0.75</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" t="n">
         <v>1420</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" t="n">
         <v>-1.34</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>1.15</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" t="n">
         <v>980</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>1.05</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>2680</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" t="n">
         <v>-2.81</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -2222,1320 +2222,1320 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>100</v>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" t="n">
         <v>12</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" t="n">
         <v>1.5</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" t="n">
         <v>15</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" t="n">
         <v>816.67</v>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>100</v>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" t="n">
         <v>1.5</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" t="n">
         <v>15</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" t="n">
         <v>400</v>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>100</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" t="n">
         <v>14</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" t="n">
         <v>2.5</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" t="n">
         <v>17</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" t="n">
         <v>221.43</v>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="D5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>100</v>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" t="n">
         <v>1.8</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" t="n">
         <v>14</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" t="n">
         <v>580</v>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>100</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" t="n">
         <v>25</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" t="n">
         <v>4</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" t="n">
         <v>18</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" t="n">
         <v>144</v>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>100</v>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" t="n">
         <v>18</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" t="n">
         <v>22</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" t="n">
         <v>133.33</v>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>100</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" t="n">
         <v>1.6</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" t="n">
         <v>16</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" t="n">
         <v>2454.55</v>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>100</v>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" t="n">
         <v>18</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" t="n">
         <v>22</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" t="n">
         <v>1166.67</v>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3" t="n">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" t="n">
         <v>20</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" t="n">
         <v>3.5</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" t="n">
         <v>19</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" t="n">
         <v>510</v>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>100</v>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" t="n">
         <v>20</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" t="n">
         <v>3.5</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" t="n">
         <v>19</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" t="n">
         <v>340</v>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" t="n">
         <v>28</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" t="n">
         <v>4.5</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" t="n">
         <v>20</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" t="n">
         <v>61.43</v>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="n">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>100</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" t="n">
         <v>28</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" t="n">
         <v>4.5</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" t="n">
         <v>20</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" t="n">
         <v>110.71</v>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>100</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" t="n">
         <v>8</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" t="n">
         <v>1.2</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" t="n">
         <v>12</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" t="n">
         <v>7250</v>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>100</v>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" t="n">
         <v>8</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" t="n">
         <v>1.2</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" t="n">
         <v>12</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" t="n">
         <v>168.75</v>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>100</v>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" t="n">
         <v>15</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" t="n">
         <v>15</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" t="n">
         <v>566.67</v>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>100</v>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" t="n">
         <v>15</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" t="n">
         <v>15</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" t="n">
         <v>453.33</v>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3" t="n">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>100</v>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" t="n">
         <v>15</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" t="n">
         <v>15</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" t="n">
         <v>613.33</v>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="n">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
         <v>100</v>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" t="n">
         <v>15</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" t="n">
         <v>10</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" t="n">
         <v>320</v>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="n">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>100</v>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" t="n">
         <v>15</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" t="n">
         <v>15</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" t="n">
         <v>80</v>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>100</v>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" t="n">
         <v>1.2</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" t="n">
         <v>12</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" t="n">
         <v>1775</v>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -3620,760 +3620,760 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" t="n">
         <v>9800</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" t="n">
         <v>9800</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>196000</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" t="n">
         <v>100</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" t="n">
         <v>9600</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>10000</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>4800</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" t="n">
         <v>4800</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>96000</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" t="n">
         <v>100</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>4700</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" t="n">
         <v>4900</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>3100</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" t="n">
         <v>3100</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>62000</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>3000</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>3200</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="B5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" t="n">
         <v>116000</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>5700</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>5900</v>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" t="n">
         <v>3600</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" t="n">
         <v>3600</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>72000</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>3500</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" t="n">
         <v>3700</v>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" t="n">
         <v>2400</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" t="n">
         <v>2400</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" t="n">
         <v>48000</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" t="n">
         <v>100</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>2400</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" t="n">
         <v>2400</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" t="n">
         <v>27000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" t="n">
         <v>27000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" t="n">
         <v>540000</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>26500</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>27500</v>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>21000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" t="n">
         <v>21000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" t="n">
         <v>420000</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>20600</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" t="n">
         <v>21400</v>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" t="n">
         <v>10200</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" t="n">
         <v>10200</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>204000</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" t="n">
         <v>10400</v>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" t="n">
         <v>6800</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" t="n">
         <v>6800</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" t="n">
         <v>136000</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>6700</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>6900</v>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" t="n">
         <v>1720</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" t="n">
         <v>1720</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" t="n">
         <v>34400</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>1700</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" t="n">
         <v>1800</v>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" t="n">
         <v>3100</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" t="n">
         <v>3100</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" t="n">
         <v>62000</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>3000</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" t="n">
         <v>3200</v>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" t="n">
         <v>58000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" t="n">
         <v>58000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" t="n">
         <v>1160000</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" t="n">
         <v>100</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>56800</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>59200</v>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" t="n">
         <v>1350</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" t="n">
         <v>1350</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" t="n">
         <v>27000</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" t="n">
         <v>100</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>1300</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" t="n">
         <v>1400</v>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" t="n">
         <v>8500</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" t="n">
         <v>8500</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" t="n">
         <v>170000</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" t="n">
         <v>100</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>8300</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" t="n">
         <v>8700</v>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" t="n">
         <v>6800</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" t="n">
         <v>6800</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" t="n">
         <v>136000</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" t="n">
         <v>100</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>6700</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>6900</v>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" t="n">
         <v>9200</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" t="n">
         <v>9200</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" t="n">
         <v>184000</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" t="n">
         <v>100</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>9000</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" t="n">
         <v>9400</v>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" t="n">
         <v>4800</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" t="n">
         <v>4800</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" t="n">
         <v>96000</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" t="n">
         <v>100</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>4700</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="n">
         <v>4900</v>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" t="n">
         <v>1200</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" t="n">
         <v>1200</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" t="n">
         <v>24000</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" t="n">
         <v>100</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>1200</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>1200</v>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J20" s="6" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" t="n">
         <v>14200</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" t="n">
         <v>14200</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" t="n">
         <v>284000</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" t="n">
         <v>100</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" t="n">
         <v>13900</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" t="n">
         <v>14500</v>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -4482,1120 +4482,1120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>816.67</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" t="n">
         <v>6533.33</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>1.5</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" t="n">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" t="n">
         <v>1.2</v>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>400</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" t="n">
         <v>3200</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" t="n">
         <v>15</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>221.43</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" t="n">
         <v>1240</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>14</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>2.5</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" t="n">
         <v>17</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" t="n">
         <v>0.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" t="n">
         <v>1.6</v>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="D5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" t="n">
         <v>580</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" t="n">
         <v>3222.22</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>10</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>1.8</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" t="n">
         <v>14</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" t="n">
         <v>0.4</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" t="n">
         <v>1.6</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>144</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" t="n">
         <v>900</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>25</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" t="n">
         <v>18</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" t="n">
         <v>0.4</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" t="n">
         <v>133.33</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" t="n">
         <v>800</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>18</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" t="n">
         <v>22</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" t="n">
         <v>0.4</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" t="n">
         <v>1.6</v>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" t="n">
         <v>2454.55</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" t="n">
         <v>16875</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>11</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>1.6</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" t="n">
         <v>16</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" t="n">
         <v>0.4</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" t="n">
         <v>1.6</v>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" t="n">
         <v>1166.67</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" t="n">
         <v>7000</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>18</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" t="n">
         <v>22</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" t="n">
         <v>0.4</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" t="n">
         <v>1.6</v>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>510</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" t="n">
         <v>2914.29</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>20</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" t="n">
         <v>3.5</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" t="n">
         <v>19</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" t="n">
         <v>0.4</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" t="n">
         <v>1.6</v>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" t="n">
         <v>340</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" t="n">
         <v>1942.86</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>20</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>3.5</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" t="n">
         <v>19</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="J11" t="n">
         <v>0.4</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" t="n">
         <v>1.6</v>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" t="n">
         <v>61.43</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" t="n">
         <v>382.22</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>28</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" t="n">
         <v>4.5</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" t="n">
         <v>20</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" t="n">
         <v>0.4</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" t="n">
         <v>1.6</v>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" t="n">
         <v>110.71</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" t="n">
         <v>688.89</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>28</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" t="n">
         <v>4.5</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" t="n">
         <v>20</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" t="n">
         <v>0.4</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" t="n">
         <v>1.6</v>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" t="n">
         <v>7250</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" t="n">
         <v>48333.33</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>1.2</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" t="n">
         <v>12</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" t="n">
         <v>0.55</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" t="n">
         <v>168.75</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" t="n">
         <v>1125</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" t="n">
         <v>1.2</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" t="n">
         <v>12</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" t="n">
         <v>0.55</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" t="n">
         <v>2</v>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" t="n">
         <v>566.67</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" t="n">
         <v>4250</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>15</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" t="n">
         <v>15</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J16" t="n">
         <v>0.4</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" t="n">
         <v>1.6</v>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" t="n">
         <v>453.33</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" t="n">
         <v>3400</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>15</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" t="n">
         <v>15</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="J17" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" t="n">
         <v>1.6</v>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" t="n">
         <v>613.33</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" t="n">
         <v>4600</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>15</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" t="n">
         <v>15</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="J18" t="n">
         <v>0.4</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" t="n">
         <v>1.6</v>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" t="n">
         <v>320</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" t="n">
         <v>2400</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>15</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" t="n">
         <v>10</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="J19" t="n">
         <v>0.4</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" t="n">
         <v>1.6</v>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" t="n">
         <v>80</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" t="n">
         <v>600</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>15</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" t="n">
         <v>15</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="J20" t="n">
         <v>0.4</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" t="n">
         <v>1.6</v>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" t="n">
         <v>1775</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" t="n">
         <v>11833.33</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" t="n">
         <v>8</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" t="n">
         <v>1.2</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" t="n">
         <v>12</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="J21" t="n">
         <v>0.55</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -5680,460 +5680,460 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>1280</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" t="n">
         <v>28</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Oversold - RSI rendah</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Bisa rebound jika commodity naik</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>9800</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" t="n">
         <v>32</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Turun mengikuti IHSG</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Konsumen stabil</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>1650</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" t="n">
         <v>35</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>RSI oversold</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Healthcare growth</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" t="n">
         <v>1150</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" t="n">
         <v>38</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Turun karena gas price</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Subsidi pemerintah</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>3200</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" t="n">
         <v>68</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Downtrend kuat</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Consumer lemah</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Sampoerna</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>2200</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" t="n">
         <v>-3.8</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" t="n">
         <v>62</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Regulasi rokok</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Tren menurun</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>9600</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" t="n">
         <v>48</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Stable bank</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Dividen menarik</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Telkom</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>3050</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" t="n">
         <v>52</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Sideways</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>5G rollout</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>56000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>-5.2</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" t="n">
         <v>25</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Anjlok dari high</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Nikel outlook bullish</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SPECULATIVE BUY</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Indocement</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>8800</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" t="n">
         <v>42</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Infrastructure push</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Pemerintah bangun infra</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -6150,7 +6150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6165,14 +6165,15 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Last Update: 2026-07-05 23:30</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Last Update: 2026-07-05 23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>IHSG Level</t>
         </is>
@@ -6184,7 +6185,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>IHSG Change</t>
         </is>
@@ -6196,7 +6197,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Top Sector</t>
         </is>
@@ -6208,7 +6209,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Worst Sector</t>
         </is>
@@ -6220,13 +6221,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BUY Signals</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0 (simulated)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>BUY Signals</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SELL Signals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6236,64 +6245,48 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>SELL Signals</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HOLD Signals</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0 (simulated)</t>
+          <t>20 (simulated)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>HOLD Signals</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Best Buy Today</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20 (simulated)</t>
+          <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/A (use update_saham.py)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Best Buy Today</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>N/A (use update_saham.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>N/A (use update_saham.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technical" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="IHSG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sektor" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Bluechip" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Technical" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fundamental" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Watchlist" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,1147 +562,1147 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F16" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F21" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F25" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F26" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F27" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F28" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F29" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F31" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F32" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -1781,328 +1781,328 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>-1.13</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>-0.85</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>1050</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="3" t="n">
         <v>-1.77</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>1150</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>-4.43</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>1420</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="3" t="n">
         <v>-1.34</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>UPTREND</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>980</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>2680</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>-2.81</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -2222,1320 +2222,1320 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="n">
         <v>816.67</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="n">
         <v>221.43</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="D5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3" t="n">
         <v>133.33</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="n">
         <v>2454.55</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="3" t="n">
         <v>1166.67</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="3" t="n">
         <v>510</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="3" t="n">
         <v>61.43</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="3" t="n">
         <v>110.71</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="3" t="n">
         <v>7250</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="3" t="n">
         <v>168.75</v>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="3" t="n">
         <v>566.67</v>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="3" t="n">
         <v>453.33</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="3" t="n">
         <v>613.33</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="3" t="n">
         <v>1775</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>simulated</t>
         </is>
@@ -3620,760 +3620,760 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>196000</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>9600</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>96000</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>4700</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>4900</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>62000</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>116000</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>5700</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>5900</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>72000</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>3500</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>3700</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>48000</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>540000</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>26500</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>27500</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>420000</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3" t="n">
         <v>20600</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>21400</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>204000</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>10400</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>136000</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="3" t="n">
         <v>6700</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="3" t="n">
         <v>6900</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="3" t="n">
         <v>34400</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>1700</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="3" t="n">
         <v>62000</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="3" t="n">
         <v>1160000</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="3" t="n">
         <v>56800</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="3" t="n">
         <v>59200</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3" t="n">
         <v>170000</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3" t="n">
         <v>8300</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="3" t="n">
         <v>8700</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="3" t="n">
         <v>136000</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="3" t="n">
         <v>6700</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="3" t="n">
         <v>6900</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="3" t="n">
         <v>184000</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="3" t="n">
         <v>9000</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="3" t="n">
         <v>9400</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="3" t="n">
         <v>96000</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="3" t="n">
         <v>4700</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="3" t="n">
         <v>4900</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="3" t="n">
         <v>24000</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="3" t="n">
         <v>284000</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="3" t="n">
         <v>13900</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="3" t="n">
         <v>14500</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>DOWNTREND 🔴</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -4482,1120 +4482,1120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Bank Central Asia</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>816.67</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>6533.33</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>BBRI.JK</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Bank Rakyat Indonesia</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Telekomunikasi Indonesia</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>221.43</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>1240</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ASII.JK</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Astra International</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>3222.22</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Unilever Indonesia</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>HM Sampoerna</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>133.33</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>UNTR.JK</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>United Tractors</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Heavy Equipment</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>2454.55</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>16875</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GGRM.JK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Gudang Garam</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>1166.67</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>7000</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10200</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>510</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>2914.29</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INDF.JK</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Indofood Sukses</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="3" t="n">
         <v>1942.86</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>1720</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="3" t="n">
         <v>61.43</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="3" t="n">
         <v>382.22</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MIKA.JK</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Methyl Indonesia</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="3" t="n">
         <v>110.71</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="3" t="n">
         <v>688.89</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Platinum Indonesia</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="3" t="n">
         <v>7250</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="3" t="n">
         <v>48333.33</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>1350</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="3" t="n">
         <v>168.75</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="3" t="n">
         <v>1125</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>INKP.JK</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Indah Kiat Pulp</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Pulp &amp; Paper</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8500</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3" t="n">
         <v>566.67</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="3" t="n">
         <v>4250</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>SMGR.JK</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Semen Indonesia</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="3" t="n">
         <v>453.33</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="3" t="n">
         <v>3400</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Indocement Tunggal</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="3" t="n">
         <v>613.33</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="3" t="n">
         <v>4600</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>JSMR.JK</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Jasa Marga</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>PTBA.JK</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>PT Bukit Asam</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>14200</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="3" t="n">
         <v>1775</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="3" t="n">
         <v>11833.33</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -5680,460 +5680,460 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ANTM.JK</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Aneka Tambang</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>1280</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Oversold - RSI rendah</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Bisa rebound jika commodity naik</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ICBP.JK</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Indofood CBP</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Turun mengikuti IHSG</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Konsumen stabil</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>KLBF.JK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Kalbe Farma</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>1650</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>RSI oversold</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Healthcare growth</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>PGAS.JK</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>PGN Gas</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>1150</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="3" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Turun karena gas price</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Subsidi pemerintah</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UNVR.JK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Downtrend kuat</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Consumer lemah</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>HMSP.JK</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Sampoerna</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>-3.8</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Regulasi rokok</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Tren menurun</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>BBCA.JK</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>9600</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Stable bank</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Dividen menarik</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>TLKM.JK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Telkom</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>3050</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Sideways</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>5G rollout</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>PTUN.JK</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>56000</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>-5.2</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Anjlok dari high</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Nikel outlook bullish</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>SPECULATIVE BUY</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>INTP.JK</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Indocement</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>8800</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Infrastructure push</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Pemerintah bangun infra</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -6150,7 +6150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6165,15 +6165,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Last Update: 2026-07-05 23:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Last Update: 2026-07-07 09:00</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>IHSG Level</t>
         </is>
@@ -6185,7 +6184,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>IHSG Change</t>
         </is>
@@ -6197,7 +6196,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Top Sector</t>
         </is>
@@ -6209,7 +6208,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Worst Sector</t>
         </is>
@@ -6221,72 +6220,80 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>0 (simulated)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>0 (simulated)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>HOLD Signals</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>20 (simulated)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Best Buy Today</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>N/A (use update_saham.py)</t>
         </is>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -564,7 +564,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -675,7 +675,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -749,7 +749,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -786,7 +786,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -823,7 +823,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -860,7 +860,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -897,7 +897,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -934,7 +934,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1008,7 +1008,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -1045,7 +1045,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -1082,7 +1082,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
@@ -1156,7 +1156,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -1193,7 +1193,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
@@ -1230,7 +1230,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -1267,7 +1267,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -1304,7 +1304,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -1341,7 +1341,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -1378,7 +1378,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -1415,7 +1415,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
@@ -1452,7 +1452,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -1489,7 +1489,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -1526,7 +1526,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -1563,7 +1563,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -1600,7 +1600,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1637,7 +1637,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -1674,7 +1674,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-07 09:00</t>
+          <t>Last Update: 2026-07-08 22:31</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -564,7 +564,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -675,7 +675,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -749,7 +749,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -786,7 +786,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -823,7 +823,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -860,7 +860,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -897,7 +897,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -934,7 +934,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1008,7 +1008,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -1045,7 +1045,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -1082,7 +1082,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
@@ -1156,7 +1156,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -1193,7 +1193,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
@@ -1230,7 +1230,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -1267,7 +1267,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -1304,7 +1304,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -1341,7 +1341,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -1378,7 +1378,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -1415,7 +1415,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
@@ -1452,7 +1452,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -1489,7 +1489,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -1526,7 +1526,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -1563,7 +1563,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -1600,7 +1600,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1637,7 +1637,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -1674,7 +1674,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-08 22:31</t>
+          <t>Last Update: 2026-07-09 08:30</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -564,7 +564,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -675,7 +675,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -749,7 +749,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -786,7 +786,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -823,7 +823,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -860,7 +860,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -897,7 +897,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -934,7 +934,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1008,7 +1008,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -1045,7 +1045,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -1082,7 +1082,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
@@ -1156,7 +1156,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -1193,7 +1193,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
@@ -1230,7 +1230,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -1267,7 +1267,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -1304,7 +1304,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -1341,7 +1341,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -1378,7 +1378,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -1415,7 +1415,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
@@ -1452,7 +1452,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -1489,7 +1489,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -1526,7 +1526,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -1563,7 +1563,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -1600,7 +1600,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1637,7 +1637,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -1674,7 +1674,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-09 08:30</t>
+          <t>Last Update: 2026-07-10 09:00</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-10 09:00</t>
+          <t>Last Update: 2026-07-10 15:45</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -564,7 +564,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -675,7 +675,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -749,7 +749,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -786,7 +786,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -823,7 +823,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -860,7 +860,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -897,7 +897,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -934,7 +934,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1008,7 +1008,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -1045,7 +1045,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -1082,7 +1082,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
@@ -1156,7 +1156,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -1193,7 +1193,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
@@ -1230,7 +1230,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -1267,7 +1267,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -1304,7 +1304,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -1341,7 +1341,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -1378,7 +1378,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -1415,7 +1415,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
@@ -1452,7 +1452,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -1489,7 +1489,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -1526,7 +1526,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -1563,7 +1563,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -1600,7 +1600,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1637,7 +1637,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -1674,7 +1674,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-10 15:45</t>
+          <t>Last Update: 2026-07-13 08:31</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -564,7 +564,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -675,7 +675,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -749,7 +749,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -786,7 +786,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -823,7 +823,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -860,7 +860,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -897,7 +897,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -934,7 +934,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1008,7 +1008,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -1045,7 +1045,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -1082,7 +1082,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
@@ -1156,7 +1156,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -1193,7 +1193,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
@@ -1230,7 +1230,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -1267,7 +1267,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -1304,7 +1304,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -1341,7 +1341,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -1378,7 +1378,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -1415,7 +1415,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
@@ -1452,7 +1452,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -1489,7 +1489,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -1526,7 +1526,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -1563,7 +1563,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -1600,7 +1600,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1637,7 +1637,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -1674,7 +1674,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-13 08:31</t>
+          <t>Last Update: 2026-07-15 22:45</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -564,7 +564,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -675,7 +675,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -749,7 +749,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -786,7 +786,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -823,7 +823,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -860,7 +860,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -897,7 +897,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -934,7 +934,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1008,7 +1008,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -1045,7 +1045,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -1082,7 +1082,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
@@ -1156,7 +1156,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -1193,7 +1193,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
@@ -1230,7 +1230,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -1267,7 +1267,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -1304,7 +1304,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -1341,7 +1341,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -1378,7 +1378,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -1415,7 +1415,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
@@ -1452,7 +1452,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -1489,7 +1489,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -1526,7 +1526,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -1563,7 +1563,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -1600,7 +1600,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1637,7 +1637,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -1674,7 +1674,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-15 22:45</t>
+          <t>Last Update: 2026-07-23 08:00</t>
         </is>
       </c>
     </row>

--- a/data/harga_saham_ihsg.xlsx
+++ b/data/harga_saham_ihsg.xlsx
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Last Update: 2026-07-23 08:00</t>
+          <t>Last Update: 2026-07-23 08:30</t>
         </is>
       </c>
     </row>
